--- a/data/cox_xlsx/SKAKO.CO.xlsx
+++ b/data/cox_xlsx/SKAKO.CO.xlsx
@@ -1287,7 +1287,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="[&gt;=100]#,###0.0\%;[&lt;=-100]-#,###0.0\%;#,###0.0\%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -1323,6 +1323,12 @@
     </font>
     <font>
       <b/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1401,7 +1407,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1468,22 +1474,25 @@
     <xf borderId="3" fillId="0" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="7" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="3" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="3" fillId="0" fontId="8" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="9" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="3" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="3" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1501,13 +1510,13 @@
     <xf borderId="3" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="7" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="3" fillId="0" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="7" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="3" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -2929,7 +2938,9 @@
       <c r="P30" s="18">
         <v>38.97</v>
       </c>
-      <c r="Q30" s="19"/>
+      <c r="Q30" s="22">
+        <v>122.53</v>
+      </c>
       <c r="R30" s="18">
         <v>67.69</v>
       </c>
@@ -3362,7 +3373,7 @@
       <c r="G38" s="19">
         <v>0.0</v>
       </c>
-      <c r="H38" s="22">
+      <c r="H38" s="23">
         <v>-1.71</v>
       </c>
       <c r="I38" s="18">
@@ -3394,7 +3405,7 @@
       <c r="G39" s="19">
         <v>0.0</v>
       </c>
-      <c r="H39" s="22">
+      <c r="H39" s="23">
         <v>-2.37</v>
       </c>
       <c r="I39" s="18">
@@ -3557,35 +3568,35 @@
       <c r="J44" s="19">
         <v>0.0</v>
       </c>
-      <c r="K44" s="22">
+      <c r="K44" s="23">
         <v>-0.02</v>
       </c>
-      <c r="L44" s="22">
+      <c r="L44" s="23">
         <v>-0.28</v>
       </c>
-      <c r="M44" s="22">
+      <c r="M44" s="23">
         <v>-0.08</v>
       </c>
-      <c r="N44" s="22">
+      <c r="N44" s="23">
         <v>-1.45</v>
       </c>
-      <c r="O44" s="22">
+      <c r="O44" s="23">
         <v>-1.07</v>
       </c>
       <c r="P44" s="19">
         <v>0.0</v>
       </c>
       <c r="Q44" s="19"/>
-      <c r="R44" s="22">
+      <c r="R44" s="23">
         <v>-0.08</v>
       </c>
-      <c r="S44" s="22">
+      <c r="S44" s="23">
         <v>-2.15</v>
       </c>
-      <c r="T44" s="22">
+      <c r="T44" s="23">
         <v>-3.64</v>
       </c>
-      <c r="U44" s="22">
+      <c r="U44" s="23">
         <v>-4.29</v>
       </c>
       <c r="V44" s="19">
@@ -3606,16 +3617,16 @@
       <c r="I45" s="19"/>
       <c r="J45" s="19"/>
       <c r="K45" s="19"/>
-      <c r="L45" s="22">
+      <c r="L45" s="23">
         <v>-0.28</v>
       </c>
-      <c r="M45" s="22">
+      <c r="M45" s="23">
         <v>-0.08</v>
       </c>
-      <c r="N45" s="22">
+      <c r="N45" s="23">
         <v>-0.11</v>
       </c>
-      <c r="O45" s="22">
+      <c r="O45" s="23">
         <v>-0.06</v>
       </c>
       <c r="P45" s="19"/>
@@ -3642,10 +3653,10 @@
       <c r="K46" s="19"/>
       <c r="L46" s="19"/>
       <c r="M46" s="19"/>
-      <c r="N46" s="22">
+      <c r="N46" s="23">
         <v>-1.34</v>
       </c>
-      <c r="O46" s="22">
+      <c r="O46" s="23">
         <v>-1.0</v>
       </c>
       <c r="P46" s="19"/>
@@ -3759,10 +3770,10 @@
         <v>98</v>
       </c>
       <c r="B49" s="19"/>
-      <c r="C49" s="23">
+      <c r="C49" s="24">
         <v>0.0</v>
       </c>
-      <c r="D49" s="23">
+      <c r="D49" s="24">
         <v>0.0</v>
       </c>
       <c r="E49" s="19"/>
@@ -3811,7 +3822,7 @@
       <c r="H50" s="21">
         <v>21.13</v>
       </c>
-      <c r="I50" s="24">
+      <c r="I50" s="25">
         <v>-4.89</v>
       </c>
       <c r="J50" s="21">
@@ -3823,7 +3834,7 @@
       <c r="L50" s="21">
         <v>1.48</v>
       </c>
-      <c r="M50" s="24">
+      <c r="M50" s="25">
         <v>-0.58</v>
       </c>
       <c r="N50" s="21">
@@ -3832,10 +3843,10 @@
       <c r="O50" s="21">
         <v>18.06</v>
       </c>
-      <c r="P50" s="24">
+      <c r="P50" s="25">
         <v>-15.82</v>
       </c>
-      <c r="Q50" s="24">
+      <c r="Q50" s="25">
         <v>-73.4</v>
       </c>
       <c r="R50" s="21">
@@ -3847,7 +3858,7 @@
       <c r="T50" s="21">
         <v>31.25</v>
       </c>
-      <c r="U50" s="24">
+      <c r="U50" s="25">
         <v>-40.36</v>
       </c>
       <c r="V50" s="21">
@@ -4004,7 +4015,7 @@
       </c>
       <c r="P54" s="19"/>
       <c r="Q54" s="19"/>
-      <c r="R54" s="22">
+      <c r="R54" s="23">
         <v>-0.35</v>
       </c>
       <c r="S54" s="19">
@@ -4018,50 +4029,50 @@
       <c r="A55" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="22">
+      <c r="B55" s="23">
         <v>-7.19</v>
       </c>
-      <c r="C55" s="22">
+      <c r="C55" s="23">
         <v>-8.41</v>
       </c>
-      <c r="D55" s="22">
+      <c r="D55" s="23">
         <v>-5.41</v>
       </c>
-      <c r="E55" s="22">
+      <c r="E55" s="23">
         <v>-7.69</v>
       </c>
-      <c r="F55" s="22">
+      <c r="F55" s="23">
         <v>-5.1</v>
       </c>
-      <c r="G55" s="22">
+      <c r="G55" s="23">
         <v>-3.74</v>
       </c>
-      <c r="H55" s="22">
+      <c r="H55" s="23">
         <v>-4.52</v>
       </c>
-      <c r="I55" s="22">
+      <c r="I55" s="23">
         <v>-3.57</v>
       </c>
-      <c r="J55" s="22">
+      <c r="J55" s="23">
         <v>-4.15</v>
       </c>
-      <c r="K55" s="22">
+      <c r="K55" s="23">
         <v>-4.34</v>
       </c>
-      <c r="L55" s="22">
+      <c r="L55" s="23">
         <v>-4.9</v>
       </c>
-      <c r="M55" s="22">
+      <c r="M55" s="23">
         <v>-4.74</v>
       </c>
-      <c r="N55" s="22">
+      <c r="N55" s="23">
         <v>-5.56</v>
       </c>
-      <c r="O55" s="22">
+      <c r="O55" s="23">
         <v>-4.56</v>
       </c>
       <c r="P55" s="19"/>
-      <c r="Q55" s="22">
+      <c r="Q55" s="23">
         <v>-0.49</v>
       </c>
       <c r="R55" s="19"/>
@@ -4086,10 +4097,10 @@
       <c r="K56" s="19"/>
       <c r="L56" s="19"/>
       <c r="M56" s="19"/>
-      <c r="N56" s="22">
+      <c r="N56" s="23">
         <v>-5.1</v>
       </c>
-      <c r="O56" s="22">
+      <c r="O56" s="23">
         <v>-4.22</v>
       </c>
       <c r="P56" s="19"/>
@@ -4104,34 +4115,34 @@
       <c r="A57" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B57" s="22">
+      <c r="B57" s="23">
         <v>-2.99</v>
       </c>
-      <c r="C57" s="22">
+      <c r="C57" s="23">
         <v>-3.08</v>
       </c>
-      <c r="D57" s="22">
+      <c r="D57" s="23">
         <v>-1.45</v>
       </c>
-      <c r="E57" s="22">
+      <c r="E57" s="23">
         <v>-1.65</v>
       </c>
-      <c r="F57" s="22">
+      <c r="F57" s="23">
         <v>-1.27</v>
       </c>
-      <c r="G57" s="22">
+      <c r="G57" s="23">
         <v>-1.29</v>
       </c>
-      <c r="H57" s="22">
+      <c r="H57" s="23">
         <v>-1.82</v>
       </c>
-      <c r="I57" s="22">
+      <c r="I57" s="23">
         <v>-1.27</v>
       </c>
-      <c r="J57" s="22">
+      <c r="J57" s="23">
         <v>-1.76</v>
       </c>
-      <c r="K57" s="22">
+      <c r="K57" s="23">
         <v>-4.18</v>
       </c>
       <c r="L57" s="19"/>
@@ -4150,22 +4161,22 @@
       <c r="A58" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B58" s="22">
+      <c r="B58" s="23">
         <v>-0.51</v>
       </c>
-      <c r="C58" s="22">
+      <c r="C58" s="23">
         <v>-0.16</v>
       </c>
-      <c r="D58" s="22">
+      <c r="D58" s="23">
         <v>-0.11</v>
       </c>
-      <c r="E58" s="22">
+      <c r="E58" s="23">
         <v>-0.22</v>
       </c>
-      <c r="F58" s="22">
+      <c r="F58" s="23">
         <v>-0.36</v>
       </c>
-      <c r="G58" s="22">
+      <c r="G58" s="23">
         <v>-0.16</v>
       </c>
       <c r="H58" s="19"/>
@@ -4188,28 +4199,28 @@
       <c r="A59" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B59" s="22">
+      <c r="B59" s="23">
         <v>-3.69</v>
       </c>
-      <c r="C59" s="22">
+      <c r="C59" s="23">
         <v>-5.18</v>
       </c>
-      <c r="D59" s="22">
+      <c r="D59" s="23">
         <v>-3.85</v>
       </c>
-      <c r="E59" s="22">
+      <c r="E59" s="23">
         <v>-5.82</v>
       </c>
-      <c r="F59" s="22">
+      <c r="F59" s="23">
         <v>-3.47</v>
       </c>
-      <c r="G59" s="22">
+      <c r="G59" s="23">
         <v>-2.29</v>
       </c>
-      <c r="H59" s="22">
+      <c r="H59" s="23">
         <v>-0.46</v>
       </c>
-      <c r="I59" s="22">
+      <c r="I59" s="23">
         <v>-0.8</v>
       </c>
       <c r="J59" s="19"/>
@@ -4236,19 +4247,19 @@
       <c r="E60" s="19"/>
       <c r="F60" s="19"/>
       <c r="G60" s="19"/>
-      <c r="H60" s="22">
+      <c r="H60" s="23">
         <v>-0.05</v>
       </c>
-      <c r="I60" s="23">
+      <c r="I60" s="24">
         <v>0.0</v>
       </c>
-      <c r="J60" s="22">
+      <c r="J60" s="23">
         <v>-0.11</v>
       </c>
-      <c r="K60" s="22">
+      <c r="K60" s="23">
         <v>-0.16</v>
       </c>
-      <c r="L60" s="22">
+      <c r="L60" s="23">
         <v>-0.22</v>
       </c>
       <c r="M60" s="19"/>
@@ -4278,29 +4289,29 @@
       <c r="K61" s="19"/>
       <c r="L61" s="19"/>
       <c r="M61" s="19"/>
-      <c r="N61" s="22">
+      <c r="N61" s="23">
         <v>-0.46</v>
       </c>
-      <c r="O61" s="22">
+      <c r="O61" s="23">
         <v>-0.34</v>
       </c>
-      <c r="P61" s="22">
+      <c r="P61" s="23">
         <v>-0.84</v>
       </c>
       <c r="Q61" s="19"/>
-      <c r="R61" s="22">
+      <c r="R61" s="23">
         <v>-2.08</v>
       </c>
-      <c r="S61" s="22">
+      <c r="S61" s="23">
         <v>-1.35</v>
       </c>
-      <c r="T61" s="22">
+      <c r="T61" s="23">
         <v>-0.69</v>
       </c>
-      <c r="U61" s="22">
+      <c r="U61" s="23">
         <v>-0.18</v>
       </c>
-      <c r="V61" s="22">
+      <c r="V61" s="23">
         <v>-1.22</v>
       </c>
     </row>
@@ -4314,19 +4325,19 @@
       <c r="E62" s="19"/>
       <c r="F62" s="19"/>
       <c r="G62" s="19"/>
-      <c r="H62" s="22">
+      <c r="H62" s="23">
         <v>-2.19</v>
       </c>
-      <c r="I62" s="22">
+      <c r="I62" s="23">
         <v>-1.5</v>
       </c>
-      <c r="J62" s="22">
+      <c r="J62" s="23">
         <v>-2.27</v>
       </c>
       <c r="K62" s="19">
         <v>0.0</v>
       </c>
-      <c r="L62" s="22">
+      <c r="L62" s="23">
         <v>-4.68</v>
       </c>
       <c r="M62" s="19"/>
@@ -4358,23 +4369,23 @@
       <c r="M63" s="19"/>
       <c r="N63" s="19"/>
       <c r="O63" s="19"/>
-      <c r="P63" s="22">
+      <c r="P63" s="23">
         <v>-4.59</v>
       </c>
       <c r="Q63" s="19"/>
-      <c r="R63" s="22">
+      <c r="R63" s="23">
         <v>-4.5</v>
       </c>
-      <c r="S63" s="22">
+      <c r="S63" s="23">
         <v>-3.62</v>
       </c>
-      <c r="T63" s="22">
+      <c r="T63" s="23">
         <v>-2.89</v>
       </c>
-      <c r="U63" s="22">
+      <c r="U63" s="23">
         <v>-2.03</v>
       </c>
-      <c r="V63" s="22">
+      <c r="V63" s="23">
         <v>-2.17</v>
       </c>
     </row>
@@ -4440,10 +4451,10 @@
       <c r="S65" s="19">
         <v>0.0</v>
       </c>
-      <c r="T65" s="22">
+      <c r="T65" s="23">
         <v>-4.4</v>
       </c>
-      <c r="U65" s="22">
+      <c r="U65" s="23">
         <v>-5.38</v>
       </c>
       <c r="V65" s="19"/>
@@ -4452,55 +4463,55 @@
       <c r="A66" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="B66" s="24">
+      <c r="B66" s="25">
         <v>-4.66</v>
       </c>
-      <c r="C66" s="24">
+      <c r="C66" s="25">
         <v>-5.1</v>
       </c>
-      <c r="D66" s="24">
+      <c r="D66" s="25">
         <v>-3.02</v>
       </c>
-      <c r="E66" s="24">
+      <c r="E66" s="25">
         <v>-6.7</v>
       </c>
-      <c r="F66" s="24">
+      <c r="F66" s="25">
         <v>-4.44</v>
       </c>
-      <c r="G66" s="24">
+      <c r="G66" s="25">
         <v>-3.42</v>
       </c>
-      <c r="H66" s="24">
+      <c r="H66" s="25">
         <v>-4.44</v>
       </c>
-      <c r="I66" s="24">
+      <c r="I66" s="25">
         <v>-3.54</v>
       </c>
-      <c r="J66" s="24">
+      <c r="J66" s="25">
         <v>-4.07</v>
       </c>
-      <c r="K66" s="24">
+      <c r="K66" s="25">
         <v>-3.76</v>
       </c>
-      <c r="L66" s="24">
+      <c r="L66" s="25">
         <v>-4.6</v>
       </c>
-      <c r="M66" s="24">
+      <c r="M66" s="25">
         <v>-4.47</v>
       </c>
-      <c r="N66" s="24">
+      <c r="N66" s="25">
         <v>-4.93</v>
       </c>
-      <c r="O66" s="24">
+      <c r="O66" s="25">
         <v>-2.16</v>
       </c>
-      <c r="P66" s="24">
+      <c r="P66" s="25">
         <v>-5.09</v>
       </c>
-      <c r="Q66" s="24">
+      <c r="Q66" s="25">
         <v>-0.49</v>
       </c>
-      <c r="R66" s="24">
+      <c r="R66" s="25">
         <v>-1.98</v>
       </c>
       <c r="S66" s="21">
@@ -4522,7 +4533,7 @@
       </c>
       <c r="B67" s="19"/>
       <c r="C67" s="19"/>
-      <c r="D67" s="23">
+      <c r="D67" s="24">
         <v>0.0</v>
       </c>
       <c r="E67" s="19"/>
@@ -4532,7 +4543,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="19"/>
       <c r="K67" s="19"/>
-      <c r="L67" s="23">
+      <c r="L67" s="24">
         <v>0.0</v>
       </c>
       <c r="M67" s="19"/>
@@ -4571,7 +4582,7 @@
       <c r="H68" s="21">
         <v>16.7</v>
       </c>
-      <c r="I68" s="24">
+      <c r="I68" s="25">
         <v>-8.42</v>
       </c>
       <c r="J68" s="21">
@@ -4580,10 +4591,10 @@
       <c r="K68" s="21">
         <v>15.68</v>
       </c>
-      <c r="L68" s="24">
+      <c r="L68" s="25">
         <v>-3.12</v>
       </c>
-      <c r="M68" s="24">
+      <c r="M68" s="25">
         <v>-5.05</v>
       </c>
       <c r="N68" s="21">
@@ -4592,10 +4603,10 @@
       <c r="O68" s="21">
         <v>15.9</v>
       </c>
-      <c r="P68" s="24">
+      <c r="P68" s="25">
         <v>-20.91</v>
       </c>
-      <c r="Q68" s="24">
+      <c r="Q68" s="25">
         <v>-73.9</v>
       </c>
       <c r="R68" s="21">
@@ -4607,7 +4618,7 @@
       <c r="T68" s="21">
         <v>38.12</v>
       </c>
-      <c r="U68" s="24">
+      <c r="U68" s="25">
         <v>-28.95</v>
       </c>
       <c r="V68" s="21">
@@ -4639,13 +4650,13 @@
       <c r="H69" s="18">
         <v>0.33</v>
       </c>
-      <c r="I69" s="22">
+      <c r="I69" s="23">
         <v>-0.69</v>
       </c>
-      <c r="J69" s="22">
+      <c r="J69" s="23">
         <v>-4.23</v>
       </c>
-      <c r="K69" s="22">
+      <c r="K69" s="23">
         <v>-0.2</v>
       </c>
       <c r="L69" s="18">
@@ -4675,7 +4686,7 @@
       <c r="T69" s="18">
         <v>12.87</v>
       </c>
-      <c r="U69" s="22">
+      <c r="U69" s="23">
         <v>-6.31</v>
       </c>
       <c r="V69" s="18">
@@ -4730,10 +4741,10 @@
       <c r="K71" s="19"/>
       <c r="L71" s="19"/>
       <c r="M71" s="19"/>
-      <c r="N71" s="22">
+      <c r="N71" s="23">
         <v>-2.13</v>
       </c>
-      <c r="O71" s="22">
+      <c r="O71" s="23">
         <v>-2.07</v>
       </c>
       <c r="P71" s="18">
@@ -4803,13 +4814,13 @@
       <c r="H73" s="21">
         <v>0.33</v>
       </c>
-      <c r="I73" s="24">
+      <c r="I73" s="25">
         <v>-0.69</v>
       </c>
-      <c r="J73" s="24">
+      <c r="J73" s="25">
         <v>-4.23</v>
       </c>
-      <c r="K73" s="24">
+      <c r="K73" s="25">
         <v>-0.2</v>
       </c>
       <c r="L73" s="21">
@@ -4839,7 +4850,7 @@
       <c r="T73" s="21">
         <v>12.87</v>
       </c>
-      <c r="U73" s="24">
+      <c r="U73" s="25">
         <v>-6.31</v>
       </c>
       <c r="V73" s="21">
@@ -4871,7 +4882,7 @@
       <c r="H74" s="21">
         <v>16.36</v>
       </c>
-      <c r="I74" s="24">
+      <c r="I74" s="25">
         <v>-7.73</v>
       </c>
       <c r="J74" s="21">
@@ -4880,10 +4891,10 @@
       <c r="K74" s="21">
         <v>15.88</v>
       </c>
-      <c r="L74" s="24">
+      <c r="L74" s="25">
         <v>-7.62</v>
       </c>
-      <c r="M74" s="24">
+      <c r="M74" s="25">
         <v>-10.43</v>
       </c>
       <c r="N74" s="21">
@@ -4892,22 +4903,22 @@
       <c r="O74" s="21">
         <v>12.14</v>
       </c>
-      <c r="P74" s="24">
+      <c r="P74" s="25">
         <v>-23.41</v>
       </c>
-      <c r="Q74" s="24">
+      <c r="Q74" s="25">
         <v>-74.81</v>
       </c>
-      <c r="R74" s="24">
+      <c r="R74" s="25">
         <v>-17.81</v>
       </c>
-      <c r="S74" s="24">
+      <c r="S74" s="25">
         <v>-6.74</v>
       </c>
       <c r="T74" s="21">
         <v>25.25</v>
       </c>
-      <c r="U74" s="24">
+      <c r="U74" s="25">
         <v>-22.64</v>
       </c>
       <c r="V74" s="21">
@@ -4939,7 +4950,7 @@
       <c r="H75" s="21">
         <v>16.36</v>
       </c>
-      <c r="I75" s="24">
+      <c r="I75" s="25">
         <v>-7.73</v>
       </c>
       <c r="J75" s="21">
@@ -4948,10 +4959,10 @@
       <c r="K75" s="21">
         <v>15.88</v>
       </c>
-      <c r="L75" s="24">
+      <c r="L75" s="25">
         <v>-7.62</v>
       </c>
-      <c r="M75" s="24">
+      <c r="M75" s="25">
         <v>-10.43</v>
       </c>
       <c r="N75" s="21">
@@ -4960,22 +4971,22 @@
       <c r="O75" s="21">
         <v>12.14</v>
       </c>
-      <c r="P75" s="24">
+      <c r="P75" s="25">
         <v>-23.41</v>
       </c>
-      <c r="Q75" s="24">
+      <c r="Q75" s="25">
         <v>-74.81</v>
       </c>
-      <c r="R75" s="24">
+      <c r="R75" s="25">
         <v>-17.81</v>
       </c>
-      <c r="S75" s="24">
+      <c r="S75" s="25">
         <v>-6.74</v>
       </c>
       <c r="T75" s="21">
         <v>25.25</v>
       </c>
-      <c r="U75" s="24">
+      <c r="U75" s="25">
         <v>-22.64</v>
       </c>
       <c r="V75" s="21">
@@ -4986,7 +4997,7 @@
       <c r="A76" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B76" s="22">
+      <c r="B76" s="23">
         <v>-4.04</v>
       </c>
       <c r="C76" s="15">
@@ -5002,7 +5013,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="19"/>
       <c r="K76" s="19"/>
-      <c r="L76" s="22">
+      <c r="L76" s="23">
         <v>-0.76</v>
       </c>
       <c r="M76" s="18">
@@ -5011,10 +5022,10 @@
       <c r="N76" s="18">
         <v>2.91</v>
       </c>
-      <c r="O76" s="22">
+      <c r="O76" s="23">
         <v>-45.08</v>
       </c>
-      <c r="P76" s="22">
+      <c r="P76" s="23">
         <v>-39.05</v>
       </c>
       <c r="Q76" s="19"/>
@@ -5060,7 +5071,7 @@
       <c r="A78" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B78" s="24">
+      <c r="B78" s="25">
         <v>-4.04</v>
       </c>
       <c r="C78" s="17">
@@ -5076,7 +5087,7 @@
       <c r="I78" s="20"/>
       <c r="J78" s="20"/>
       <c r="K78" s="20"/>
-      <c r="L78" s="24">
+      <c r="L78" s="25">
         <v>-0.76</v>
       </c>
       <c r="M78" s="21">
@@ -5085,10 +5096,10 @@
       <c r="N78" s="21">
         <v>2.91</v>
       </c>
-      <c r="O78" s="24">
+      <c r="O78" s="25">
         <v>-45.08</v>
       </c>
-      <c r="P78" s="24">
+      <c r="P78" s="25">
         <v>-39.05</v>
       </c>
       <c r="Q78" s="20"/>
@@ -5189,7 +5200,7 @@
       <c r="H81" s="21">
         <v>16.36</v>
       </c>
-      <c r="I81" s="24">
+      <c r="I81" s="25">
         <v>-7.73</v>
       </c>
       <c r="J81" s="21">
@@ -5198,28 +5209,28 @@
       <c r="K81" s="21">
         <v>15.88</v>
       </c>
-      <c r="L81" s="24">
+      <c r="L81" s="25">
         <v>-8.38</v>
       </c>
-      <c r="M81" s="24">
+      <c r="M81" s="25">
         <v>-8.9</v>
       </c>
       <c r="N81" s="21">
         <v>7.77</v>
       </c>
-      <c r="O81" s="24">
+      <c r="O81" s="25">
         <v>-32.94</v>
       </c>
-      <c r="P81" s="24">
+      <c r="P81" s="25">
         <v>-62.45</v>
       </c>
-      <c r="Q81" s="24">
+      <c r="Q81" s="25">
         <v>-74.81</v>
       </c>
-      <c r="R81" s="24">
+      <c r="R81" s="25">
         <v>-17.81</v>
       </c>
-      <c r="S81" s="24">
+      <c r="S81" s="25">
         <v>-6.74</v>
       </c>
       <c r="T81" s="21">
@@ -5257,7 +5268,7 @@
       <c r="H82" s="21">
         <v>16.36</v>
       </c>
-      <c r="I82" s="24">
+      <c r="I82" s="25">
         <v>-7.73</v>
       </c>
       <c r="J82" s="21">
@@ -5266,10 +5277,10 @@
       <c r="K82" s="21">
         <v>15.88</v>
       </c>
-      <c r="L82" s="24">
+      <c r="L82" s="25">
         <v>-7.62</v>
       </c>
-      <c r="M82" s="24">
+      <c r="M82" s="25">
         <v>-10.43</v>
       </c>
       <c r="N82" s="21">
@@ -5278,22 +5289,22 @@
       <c r="O82" s="21">
         <v>12.14</v>
       </c>
-      <c r="P82" s="24">
+      <c r="P82" s="25">
         <v>-23.41</v>
       </c>
-      <c r="Q82" s="24">
+      <c r="Q82" s="25">
         <v>-74.81</v>
       </c>
-      <c r="R82" s="24">
+      <c r="R82" s="25">
         <v>-17.81</v>
       </c>
-      <c r="S82" s="24">
+      <c r="S82" s="25">
         <v>-6.74</v>
       </c>
       <c r="T82" s="21">
         <v>25.25</v>
       </c>
-      <c r="U82" s="24">
+      <c r="U82" s="25">
         <v>-27.8</v>
       </c>
       <c r="V82" s="21">
@@ -5325,7 +5336,7 @@
       <c r="H83" s="21">
         <v>16.36</v>
       </c>
-      <c r="I83" s="24">
+      <c r="I83" s="25">
         <v>-7.73</v>
       </c>
       <c r="J83" s="21">
@@ -5334,28 +5345,28 @@
       <c r="K83" s="21">
         <v>15.88</v>
       </c>
-      <c r="L83" s="24">
+      <c r="L83" s="25">
         <v>-8.38</v>
       </c>
-      <c r="M83" s="24">
+      <c r="M83" s="25">
         <v>-8.9</v>
       </c>
       <c r="N83" s="21">
         <v>7.77</v>
       </c>
-      <c r="O83" s="24">
+      <c r="O83" s="25">
         <v>-32.94</v>
       </c>
-      <c r="P83" s="24">
+      <c r="P83" s="25">
         <v>-62.45</v>
       </c>
-      <c r="Q83" s="24">
+      <c r="Q83" s="25">
         <v>-74.81</v>
       </c>
-      <c r="R83" s="24">
+      <c r="R83" s="25">
         <v>-17.81</v>
       </c>
-      <c r="S83" s="24">
+      <c r="S83" s="25">
         <v>-6.74</v>
       </c>
       <c r="T83" s="21">
@@ -5433,7 +5444,7 @@
       <c r="H85" s="18">
         <v>16.36</v>
       </c>
-      <c r="I85" s="22">
+      <c r="I85" s="23">
         <v>-7.73</v>
       </c>
       <c r="J85" s="18">
@@ -5442,28 +5453,28 @@
       <c r="K85" s="18">
         <v>15.88</v>
       </c>
-      <c r="L85" s="22">
+      <c r="L85" s="23">
         <v>-8.38</v>
       </c>
-      <c r="M85" s="22">
+      <c r="M85" s="23">
         <v>-8.9</v>
       </c>
       <c r="N85" s="18">
         <v>7.76</v>
       </c>
-      <c r="O85" s="22">
+      <c r="O85" s="23">
         <v>-32.94</v>
       </c>
-      <c r="P85" s="22">
+      <c r="P85" s="23">
         <v>-62.45</v>
       </c>
-      <c r="Q85" s="22">
+      <c r="Q85" s="23">
         <v>-74.81</v>
       </c>
-      <c r="R85" s="22">
+      <c r="R85" s="23">
         <v>-17.81</v>
       </c>
-      <c r="S85" s="22">
+      <c r="S85" s="23">
         <v>-6.74</v>
       </c>
       <c r="T85" s="18">
@@ -5501,7 +5512,7 @@
       <c r="H86" s="18">
         <v>16.36</v>
       </c>
-      <c r="I86" s="22">
+      <c r="I86" s="23">
         <v>-7.73</v>
       </c>
       <c r="J86" s="18">
@@ -5510,32 +5521,32 @@
       <c r="K86" s="18">
         <v>15.88</v>
       </c>
-      <c r="L86" s="22">
+      <c r="L86" s="23">
         <v>-7.62</v>
       </c>
-      <c r="M86" s="22">
+      <c r="M86" s="23">
         <v>-10.43</v>
       </c>
       <c r="N86" s="19"/>
       <c r="O86" s="18">
         <v>12.14</v>
       </c>
-      <c r="P86" s="22">
+      <c r="P86" s="23">
         <v>-23.41</v>
       </c>
-      <c r="Q86" s="22">
+      <c r="Q86" s="23">
         <v>-74.81</v>
       </c>
-      <c r="R86" s="22">
+      <c r="R86" s="23">
         <v>-17.81</v>
       </c>
-      <c r="S86" s="22">
+      <c r="S86" s="23">
         <v>-6.74</v>
       </c>
       <c r="T86" s="18">
         <v>25.25</v>
       </c>
-      <c r="U86" s="22">
+      <c r="U86" s="23">
         <v>-27.8</v>
       </c>
       <c r="V86" s="18">
@@ -5567,7 +5578,7 @@
       <c r="H87" s="18">
         <v>5.31</v>
       </c>
-      <c r="I87" s="22">
+      <c r="I87" s="23">
         <v>-2.51</v>
       </c>
       <c r="J87" s="18">
@@ -5576,10 +5587,10 @@
       <c r="K87" s="18">
         <v>5.16</v>
       </c>
-      <c r="L87" s="22">
+      <c r="L87" s="23">
         <v>-2.48</v>
       </c>
-      <c r="M87" s="22">
+      <c r="M87" s="23">
         <v>-4.15</v>
       </c>
       <c r="N87" s="18">
@@ -5588,22 +5599,22 @@
       <c r="O87" s="18">
         <v>5.42</v>
       </c>
-      <c r="P87" s="22">
+      <c r="P87" s="23">
         <v>-10.5</v>
       </c>
-      <c r="Q87" s="22">
+      <c r="Q87" s="23">
         <v>-33.49</v>
       </c>
-      <c r="R87" s="22">
+      <c r="R87" s="23">
         <v>-7.85</v>
       </c>
-      <c r="S87" s="22">
+      <c r="S87" s="23">
         <v>-2.96</v>
       </c>
       <c r="T87" s="18">
         <v>11.1</v>
       </c>
-      <c r="U87" s="22">
+      <c r="U87" s="23">
         <v>-12.23</v>
       </c>
       <c r="V87" s="18">
@@ -5635,7 +5646,7 @@
       <c r="H88" s="18">
         <v>5.31</v>
       </c>
-      <c r="I88" s="22">
+      <c r="I88" s="23">
         <v>-2.51</v>
       </c>
       <c r="J88" s="18">
@@ -5644,28 +5655,28 @@
       <c r="K88" s="18">
         <v>5.16</v>
       </c>
-      <c r="L88" s="22">
+      <c r="L88" s="23">
         <v>-2.48</v>
       </c>
-      <c r="M88" s="22">
+      <c r="M88" s="23">
         <v>-4.15</v>
       </c>
       <c r="N88" s="18">
         <v>2.51</v>
       </c>
-      <c r="O88" s="22">
+      <c r="O88" s="23">
         <v>-14.71</v>
       </c>
-      <c r="P88" s="22">
+      <c r="P88" s="23">
         <v>-27.95</v>
       </c>
-      <c r="Q88" s="22">
+      <c r="Q88" s="23">
         <v>-33.49</v>
       </c>
-      <c r="R88" s="22">
+      <c r="R88" s="23">
         <v>-7.85</v>
       </c>
-      <c r="S88" s="22">
+      <c r="S88" s="23">
         <v>-2.96</v>
       </c>
       <c r="T88" s="18">
@@ -5839,7 +5850,7 @@
       <c r="H91" s="18">
         <v>5.31</v>
       </c>
-      <c r="I91" s="22">
+      <c r="I91" s="23">
         <v>-2.51</v>
       </c>
       <c r="J91" s="18">
@@ -5848,10 +5859,10 @@
       <c r="K91" s="18">
         <v>5.16</v>
       </c>
-      <c r="L91" s="22">
+      <c r="L91" s="23">
         <v>-2.48</v>
       </c>
-      <c r="M91" s="22">
+      <c r="M91" s="23">
         <v>-4.15</v>
       </c>
       <c r="N91" s="18">
@@ -5860,22 +5871,22 @@
       <c r="O91" s="18">
         <v>5.42</v>
       </c>
-      <c r="P91" s="22">
+      <c r="P91" s="23">
         <v>-10.5</v>
       </c>
-      <c r="Q91" s="22">
+      <c r="Q91" s="23">
         <v>-33.49</v>
       </c>
-      <c r="R91" s="22">
+      <c r="R91" s="23">
         <v>-7.85</v>
       </c>
-      <c r="S91" s="22">
+      <c r="S91" s="23">
         <v>-2.96</v>
       </c>
       <c r="T91" s="18">
         <v>11.1</v>
       </c>
-      <c r="U91" s="22">
+      <c r="U91" s="23">
         <v>-12.23</v>
       </c>
       <c r="V91" s="18">
@@ -5907,7 +5918,7 @@
       <c r="H92" s="18">
         <v>5.31</v>
       </c>
-      <c r="I92" s="22">
+      <c r="I92" s="23">
         <v>-2.51</v>
       </c>
       <c r="J92" s="18">
@@ -5916,28 +5927,28 @@
       <c r="K92" s="18">
         <v>5.16</v>
       </c>
-      <c r="L92" s="22">
+      <c r="L92" s="23">
         <v>-2.48</v>
       </c>
-      <c r="M92" s="22">
+      <c r="M92" s="23">
         <v>-4.15</v>
       </c>
       <c r="N92" s="18">
         <v>3.21</v>
       </c>
-      <c r="O92" s="22">
+      <c r="O92" s="23">
         <v>-14.71</v>
       </c>
-      <c r="P92" s="22">
+      <c r="P92" s="23">
         <v>-27.95</v>
       </c>
-      <c r="Q92" s="22">
+      <c r="Q92" s="23">
         <v>-33.49</v>
       </c>
-      <c r="R92" s="22">
+      <c r="R92" s="23">
         <v>-7.85</v>
       </c>
-      <c r="S92" s="22">
+      <c r="S92" s="23">
         <v>-2.96</v>
       </c>
       <c r="T92" s="18">
@@ -6947,7 +6958,7 @@
       <c r="H115" s="18">
         <v>5.31</v>
       </c>
-      <c r="I115" s="22">
+      <c r="I115" s="23">
         <v>-2.51</v>
       </c>
       <c r="J115" s="18">
@@ -6956,28 +6967,28 @@
       <c r="K115" s="18">
         <v>5.16</v>
       </c>
-      <c r="L115" s="22">
+      <c r="L115" s="23">
         <v>-2.48</v>
       </c>
-      <c r="M115" s="22">
+      <c r="M115" s="23">
         <v>-4.15</v>
       </c>
       <c r="N115" s="18">
         <v>3.21</v>
       </c>
-      <c r="O115" s="22">
+      <c r="O115" s="23">
         <v>-14.71</v>
       </c>
-      <c r="P115" s="22">
+      <c r="P115" s="23">
         <v>-27.95</v>
       </c>
-      <c r="Q115" s="22">
+      <c r="Q115" s="23">
         <v>-33.49</v>
       </c>
-      <c r="R115" s="22">
+      <c r="R115" s="23">
         <v>-7.85</v>
       </c>
-      <c r="S115" s="22">
+      <c r="S115" s="23">
         <v>-2.96</v>
       </c>
       <c r="T115" s="18">
@@ -7015,7 +7026,7 @@
       <c r="H116" s="18">
         <v>5.31</v>
       </c>
-      <c r="I116" s="22">
+      <c r="I116" s="23">
         <v>-2.51</v>
       </c>
       <c r="J116" s="18">
@@ -7024,28 +7035,28 @@
       <c r="K116" s="18">
         <v>5.16</v>
       </c>
-      <c r="L116" s="22">
+      <c r="L116" s="23">
         <v>-2.48</v>
       </c>
-      <c r="M116" s="22">
+      <c r="M116" s="23">
         <v>-4.15</v>
       </c>
       <c r="N116" s="18">
         <v>2.51</v>
       </c>
-      <c r="O116" s="22">
+      <c r="O116" s="23">
         <v>-14.71</v>
       </c>
-      <c r="P116" s="22">
+      <c r="P116" s="23">
         <v>-27.95</v>
       </c>
-      <c r="Q116" s="22">
+      <c r="Q116" s="23">
         <v>-33.49</v>
       </c>
-      <c r="R116" s="22">
+      <c r="R116" s="23">
         <v>-7.85</v>
       </c>
-      <c r="S116" s="22">
+      <c r="S116" s="23">
         <v>-2.96</v>
       </c>
       <c r="T116" s="18">
@@ -7083,7 +7094,7 @@
       <c r="H117" s="18">
         <v>5.31</v>
       </c>
-      <c r="I117" s="22">
+      <c r="I117" s="23">
         <v>-2.51</v>
       </c>
       <c r="J117" s="18">
@@ -7092,10 +7103,10 @@
       <c r="K117" s="18">
         <v>5.16</v>
       </c>
-      <c r="L117" s="22">
+      <c r="L117" s="23">
         <v>-2.48</v>
       </c>
-      <c r="M117" s="22">
+      <c r="M117" s="23">
         <v>-4.15</v>
       </c>
       <c r="N117" s="18">
@@ -7104,22 +7115,22 @@
       <c r="O117" s="18">
         <v>5.42</v>
       </c>
-      <c r="P117" s="22">
+      <c r="P117" s="23">
         <v>-10.5</v>
       </c>
-      <c r="Q117" s="22">
+      <c r="Q117" s="23">
         <v>-33.49</v>
       </c>
-      <c r="R117" s="22">
+      <c r="R117" s="23">
         <v>-7.85</v>
       </c>
-      <c r="S117" s="22">
+      <c r="S117" s="23">
         <v>-2.96</v>
       </c>
       <c r="T117" s="18">
         <v>11.1</v>
       </c>
-      <c r="U117" s="22">
+      <c r="U117" s="23">
         <v>-12.23</v>
       </c>
       <c r="V117" s="18">
@@ -7151,7 +7162,7 @@
       <c r="H118" s="18">
         <v>5.31</v>
       </c>
-      <c r="I118" s="22">
+      <c r="I118" s="23">
         <v>-2.51</v>
       </c>
       <c r="J118" s="18">
@@ -7160,10 +7171,10 @@
       <c r="K118" s="18">
         <v>5.16</v>
       </c>
-      <c r="L118" s="22">
+      <c r="L118" s="23">
         <v>-2.48</v>
       </c>
-      <c r="M118" s="22">
+      <c r="M118" s="23">
         <v>-4.15</v>
       </c>
       <c r="N118" s="18">
@@ -7172,22 +7183,22 @@
       <c r="O118" s="18">
         <v>5.42</v>
       </c>
-      <c r="P118" s="22">
+      <c r="P118" s="23">
         <v>-10.5</v>
       </c>
-      <c r="Q118" s="22">
+      <c r="Q118" s="23">
         <v>-33.49</v>
       </c>
-      <c r="R118" s="22">
+      <c r="R118" s="23">
         <v>-7.85</v>
       </c>
-      <c r="S118" s="22">
+      <c r="S118" s="23">
         <v>-2.96</v>
       </c>
       <c r="T118" s="18">
         <v>11.1</v>
       </c>
-      <c r="U118" s="22">
+      <c r="U118" s="23">
         <v>-12.23</v>
       </c>
       <c r="V118" s="18">
@@ -7219,7 +7230,7 @@
       <c r="H119" s="18">
         <v>16.36</v>
       </c>
-      <c r="I119" s="22">
+      <c r="I119" s="23">
         <v>-7.73</v>
       </c>
       <c r="J119" s="18">
@@ -7228,28 +7239,28 @@
       <c r="K119" s="18">
         <v>15.88</v>
       </c>
-      <c r="L119" s="22">
+      <c r="L119" s="23">
         <v>-8.38</v>
       </c>
-      <c r="M119" s="22">
+      <c r="M119" s="23">
         <v>-8.9</v>
       </c>
       <c r="N119" s="18">
         <v>7.77</v>
       </c>
-      <c r="O119" s="22">
+      <c r="O119" s="23">
         <v>-32.94</v>
       </c>
-      <c r="P119" s="22">
+      <c r="P119" s="23">
         <v>-62.45</v>
       </c>
-      <c r="Q119" s="22">
+      <c r="Q119" s="23">
         <v>-74.81</v>
       </c>
-      <c r="R119" s="22">
+      <c r="R119" s="23">
         <v>-17.81</v>
       </c>
-      <c r="S119" s="22">
+      <c r="S119" s="23">
         <v>-6.74</v>
       </c>
       <c r="T119" s="18">
@@ -7287,7 +7298,7 @@
       <c r="H120" s="18">
         <v>16.36</v>
       </c>
-      <c r="I120" s="22">
+      <c r="I120" s="23">
         <v>-7.73</v>
       </c>
       <c r="J120" s="18">
@@ -7296,28 +7307,28 @@
       <c r="K120" s="18">
         <v>15.88</v>
       </c>
-      <c r="L120" s="22">
+      <c r="L120" s="23">
         <v>-8.38</v>
       </c>
-      <c r="M120" s="22">
+      <c r="M120" s="23">
         <v>-8.9</v>
       </c>
       <c r="N120" s="18">
         <v>7.76</v>
       </c>
-      <c r="O120" s="22">
+      <c r="O120" s="23">
         <v>-32.94</v>
       </c>
-      <c r="P120" s="22">
+      <c r="P120" s="23">
         <v>-62.45</v>
       </c>
-      <c r="Q120" s="22">
+      <c r="Q120" s="23">
         <v>-74.81</v>
       </c>
-      <c r="R120" s="22">
+      <c r="R120" s="23">
         <v>-17.81</v>
       </c>
-      <c r="S120" s="22">
+      <c r="S120" s="23">
         <v>-6.74</v>
       </c>
       <c r="T120" s="18">
@@ -7355,7 +7366,7 @@
       <c r="H121" s="18">
         <v>16.36</v>
       </c>
-      <c r="I121" s="22">
+      <c r="I121" s="23">
         <v>-7.73</v>
       </c>
       <c r="J121" s="18">
@@ -7364,10 +7375,10 @@
       <c r="K121" s="18">
         <v>15.88</v>
       </c>
-      <c r="L121" s="22">
+      <c r="L121" s="23">
         <v>-7.62</v>
       </c>
-      <c r="M121" s="22">
+      <c r="M121" s="23">
         <v>-10.43</v>
       </c>
       <c r="N121" s="18">
@@ -7376,22 +7387,22 @@
       <c r="O121" s="18">
         <v>12.14</v>
       </c>
-      <c r="P121" s="22">
+      <c r="P121" s="23">
         <v>-23.41</v>
       </c>
-      <c r="Q121" s="22">
+      <c r="Q121" s="23">
         <v>-74.81</v>
       </c>
-      <c r="R121" s="22">
+      <c r="R121" s="23">
         <v>-17.81</v>
       </c>
-      <c r="S121" s="22">
+      <c r="S121" s="23">
         <v>-6.74</v>
       </c>
       <c r="T121" s="18">
         <v>25.25</v>
       </c>
-      <c r="U121" s="22">
+      <c r="U121" s="23">
         <v>-27.8</v>
       </c>
       <c r="V121" s="18">
@@ -7423,7 +7434,7 @@
       <c r="H122" s="18">
         <v>16.36</v>
       </c>
-      <c r="I122" s="22">
+      <c r="I122" s="23">
         <v>-7.73</v>
       </c>
       <c r="J122" s="18">
@@ -7432,32 +7443,32 @@
       <c r="K122" s="18">
         <v>15.88</v>
       </c>
-      <c r="L122" s="22">
+      <c r="L122" s="23">
         <v>-7.62</v>
       </c>
-      <c r="M122" s="22">
+      <c r="M122" s="23">
         <v>-10.43</v>
       </c>
       <c r="N122" s="19"/>
       <c r="O122" s="18">
         <v>12.14</v>
       </c>
-      <c r="P122" s="22">
+      <c r="P122" s="23">
         <v>-23.41</v>
       </c>
-      <c r="Q122" s="22">
+      <c r="Q122" s="23">
         <v>-74.81</v>
       </c>
-      <c r="R122" s="22">
+      <c r="R122" s="23">
         <v>-17.81</v>
       </c>
-      <c r="S122" s="22">
+      <c r="S122" s="23">
         <v>-6.74</v>
       </c>
       <c r="T122" s="18">
         <v>25.25</v>
       </c>
-      <c r="U122" s="22">
+      <c r="U122" s="23">
         <v>-27.8</v>
       </c>
       <c r="V122" s="18">
@@ -7616,7 +7627,7 @@
       <c r="K125" s="19"/>
       <c r="L125" s="19"/>
       <c r="M125" s="19"/>
-      <c r="N125" s="22">
+      <c r="N125" s="23">
         <v>-0.01</v>
       </c>
       <c r="O125" s="19"/>
@@ -9217,7 +9228,7 @@
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="26" t="s">
         <v>179</v>
       </c>
       <c r="B22" s="19"/>
@@ -9748,10 +9759,10 @@
       <c r="O31" s="19"/>
       <c r="P31" s="19"/>
       <c r="Q31" s="19"/>
-      <c r="R31" s="22">
+      <c r="R31" s="23">
         <v>-9.46</v>
       </c>
-      <c r="S31" s="22">
+      <c r="S31" s="23">
         <v>-17.48</v>
       </c>
       <c r="T31" s="19"/>
@@ -10291,25 +10302,25 @@
       <c r="L43" s="19"/>
       <c r="M43" s="19"/>
       <c r="N43" s="19"/>
-      <c r="O43" s="22">
+      <c r="O43" s="23">
         <v>-59.52</v>
       </c>
-      <c r="P43" s="22">
+      <c r="P43" s="23">
         <v>-60.45</v>
       </c>
-      <c r="Q43" s="22">
+      <c r="Q43" s="23">
         <v>-86.82</v>
       </c>
-      <c r="R43" s="26">
+      <c r="R43" s="27">
         <v>-104.07</v>
       </c>
-      <c r="S43" s="22">
+      <c r="S43" s="23">
         <v>-88.2</v>
       </c>
-      <c r="T43" s="22">
+      <c r="T43" s="23">
         <v>-88.72</v>
       </c>
-      <c r="U43" s="22">
+      <c r="U43" s="23">
         <v>-81.94</v>
       </c>
       <c r="V43" s="19"/>
@@ -10371,17 +10382,17 @@
       <c r="L45" s="19"/>
       <c r="M45" s="19"/>
       <c r="N45" s="19"/>
-      <c r="O45" s="22">
+      <c r="O45" s="23">
         <v>-14.88</v>
       </c>
       <c r="P45" s="19"/>
-      <c r="Q45" s="22">
+      <c r="Q45" s="23">
         <v>-12.43</v>
       </c>
-      <c r="R45" s="22">
+      <c r="R45" s="23">
         <v>-12.62</v>
       </c>
-      <c r="S45" s="22">
+      <c r="S45" s="23">
         <v>-15.32</v>
       </c>
       <c r="T45" s="19"/>
@@ -10791,17 +10802,17 @@
       <c r="L54" s="19"/>
       <c r="M54" s="19"/>
       <c r="N54" s="19"/>
-      <c r="O54" s="22">
+      <c r="O54" s="23">
         <v>-23.36</v>
       </c>
       <c r="P54" s="19"/>
-      <c r="Q54" s="22">
+      <c r="Q54" s="23">
         <v>-43.9</v>
       </c>
-      <c r="R54" s="22">
+      <c r="R54" s="23">
         <v>-55.65</v>
       </c>
-      <c r="S54" s="22">
+      <c r="S54" s="23">
         <v>-44.61</v>
       </c>
       <c r="T54" s="19"/>
@@ -10975,25 +10986,25 @@
       <c r="L59" s="19"/>
       <c r="M59" s="19"/>
       <c r="N59" s="19"/>
-      <c r="O59" s="22">
+      <c r="O59" s="23">
         <v>-21.57</v>
       </c>
-      <c r="P59" s="22">
+      <c r="P59" s="23">
         <v>-21.78</v>
       </c>
-      <c r="Q59" s="22">
+      <c r="Q59" s="23">
         <v>-22.16</v>
       </c>
-      <c r="R59" s="22">
+      <c r="R59" s="23">
         <v>-24.67</v>
       </c>
-      <c r="S59" s="22">
+      <c r="S59" s="23">
         <v>-19.18</v>
       </c>
-      <c r="T59" s="22">
+      <c r="T59" s="23">
         <v>-18.62</v>
       </c>
-      <c r="U59" s="22">
+      <c r="U59" s="23">
         <v>-17.07</v>
       </c>
       <c r="V59" s="19"/>
@@ -11055,17 +11066,17 @@
       <c r="L61" s="19"/>
       <c r="M61" s="19"/>
       <c r="N61" s="19"/>
-      <c r="O61" s="22">
+      <c r="O61" s="23">
         <v>-21.57</v>
       </c>
       <c r="P61" s="19"/>
-      <c r="Q61" s="22">
+      <c r="Q61" s="23">
         <v>-20.98</v>
       </c>
-      <c r="R61" s="22">
+      <c r="R61" s="23">
         <v>-23.55</v>
       </c>
-      <c r="S61" s="22">
+      <c r="S61" s="23">
         <v>-18.49</v>
       </c>
       <c r="T61" s="19"/>
@@ -11199,13 +11210,13 @@
       <c r="N65" s="19"/>
       <c r="O65" s="19"/>
       <c r="P65" s="19"/>
-      <c r="Q65" s="22">
+      <c r="Q65" s="23">
         <v>-1.18</v>
       </c>
-      <c r="R65" s="22">
+      <c r="R65" s="23">
         <v>-1.12</v>
       </c>
-      <c r="S65" s="22">
+      <c r="S65" s="23">
         <v>-0.69</v>
       </c>
       <c r="T65" s="19"/>
@@ -11404,7 +11415,7 @@
       <c r="A71" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B71" s="24">
         <v>0.0</v>
       </c>
       <c r="C71" s="19"/>
@@ -12237,7 +12248,7 @@
         <v>242</v>
       </c>
       <c r="B88" s="19"/>
-      <c r="C88" s="23">
+      <c r="C88" s="24">
         <v>0.0</v>
       </c>
       <c r="D88" s="19"/>
@@ -12978,7 +12989,7 @@
       <c r="A103" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="B103" s="22">
+      <c r="B103" s="23">
         <v>-0.24</v>
       </c>
       <c r="C103" s="18">
@@ -12987,19 +12998,19 @@
       <c r="D103" s="18">
         <v>0.12</v>
       </c>
-      <c r="E103" s="22">
+      <c r="E103" s="23">
         <v>-0.61</v>
       </c>
-      <c r="F103" s="22">
+      <c r="F103" s="23">
         <v>-1.72</v>
       </c>
       <c r="G103" s="18">
         <v>0.3</v>
       </c>
-      <c r="H103" s="22">
+      <c r="H103" s="23">
         <v>-0.19</v>
       </c>
-      <c r="I103" s="22">
+      <c r="I103" s="23">
         <v>-0.52</v>
       </c>
       <c r="J103" s="18">
@@ -13008,34 +13019,34 @@
       <c r="K103" s="18">
         <v>0.32</v>
       </c>
-      <c r="L103" s="22">
+      <c r="L103" s="23">
         <v>-0.79</v>
       </c>
-      <c r="M103" s="22">
+      <c r="M103" s="23">
         <v>-1.48</v>
       </c>
-      <c r="N103" s="22">
+      <c r="N103" s="23">
         <v>-1.31</v>
       </c>
-      <c r="O103" s="22">
+      <c r="O103" s="23">
         <v>-1.65</v>
       </c>
-      <c r="P103" s="22">
+      <c r="P103" s="23">
         <v>-1.42</v>
       </c>
-      <c r="Q103" s="22">
+      <c r="Q103" s="23">
         <v>-2.19</v>
       </c>
-      <c r="R103" s="22">
+      <c r="R103" s="23">
         <v>-2.57</v>
       </c>
-      <c r="S103" s="22">
+      <c r="S103" s="23">
         <v>-1.64</v>
       </c>
-      <c r="T103" s="22">
+      <c r="T103" s="23">
         <v>-0.79</v>
       </c>
-      <c r="U103" s="22">
+      <c r="U103" s="23">
         <v>-0.67</v>
       </c>
       <c r="V103" s="18">
@@ -13052,10 +13063,10 @@
       <c r="C104" s="19">
         <v>0.0</v>
       </c>
-      <c r="D104" s="22">
+      <c r="D104" s="23">
         <v>-0.07</v>
       </c>
-      <c r="E104" s="22">
+      <c r="E104" s="23">
         <v>-0.07</v>
       </c>
       <c r="F104" s="18">
@@ -13064,28 +13075,28 @@
       <c r="G104" s="18">
         <v>0.05</v>
       </c>
-      <c r="H104" s="22">
+      <c r="H104" s="23">
         <v>-0.2</v>
       </c>
-      <c r="I104" s="22">
+      <c r="I104" s="23">
         <v>-0.04</v>
       </c>
       <c r="J104" s="18">
         <v>0.06</v>
       </c>
-      <c r="K104" s="22">
+      <c r="K104" s="23">
         <v>-0.14</v>
       </c>
-      <c r="L104" s="22">
+      <c r="L104" s="23">
         <v>-0.29</v>
       </c>
-      <c r="M104" s="22">
+      <c r="M104" s="23">
         <v>-0.05</v>
       </c>
-      <c r="N104" s="22">
+      <c r="N104" s="23">
         <v>-0.06</v>
       </c>
-      <c r="O104" s="22">
+      <c r="O104" s="23">
         <v>-0.61</v>
       </c>
       <c r="P104" s="19">
@@ -13276,11 +13287,11 @@
       <c r="I108" s="19"/>
       <c r="J108" s="19"/>
       <c r="K108" s="19"/>
-      <c r="L108" s="23">
+      <c r="L108" s="24">
         <v>0.0</v>
       </c>
       <c r="M108" s="19"/>
-      <c r="N108" s="23">
+      <c r="N108" s="24">
         <v>0.0</v>
       </c>
       <c r="O108" s="19"/>
@@ -13471,7 +13482,7 @@
       <c r="H112" s="19"/>
       <c r="I112" s="19"/>
       <c r="J112" s="19"/>
-      <c r="K112" s="23">
+      <c r="K112" s="24">
         <v>0.0</v>
       </c>
       <c r="L112" s="19">
@@ -13819,22 +13830,22 @@
       <c r="L118" s="19"/>
       <c r="M118" s="19"/>
       <c r="N118" s="19"/>
-      <c r="O118" s="22">
+      <c r="O118" s="23">
         <v>-0.19</v>
       </c>
-      <c r="P118" s="22">
+      <c r="P118" s="23">
         <v>-0.04</v>
       </c>
-      <c r="Q118" s="22">
+      <c r="Q118" s="23">
         <v>-0.1</v>
       </c>
-      <c r="R118" s="22">
+      <c r="R118" s="23">
         <v>-0.08</v>
       </c>
-      <c r="S118" s="22">
+      <c r="S118" s="23">
         <v>-0.12</v>
       </c>
-      <c r="T118" s="22">
+      <c r="T118" s="23">
         <v>-0.03</v>
       </c>
       <c r="U118" s="19"/>
@@ -15850,7 +15861,7 @@
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" s="19"/>
-      <c r="O20" s="22">
+      <c r="O20" s="23">
         <v>-0.06</v>
       </c>
       <c r="P20" s="19">
@@ -15860,16 +15871,16 @@
       <c r="R20" s="19">
         <v>0.0</v>
       </c>
-      <c r="S20" s="22">
+      <c r="S20" s="23">
         <v>-2.15</v>
       </c>
-      <c r="T20" s="22">
+      <c r="T20" s="23">
         <v>-2.96</v>
       </c>
-      <c r="U20" s="22">
+      <c r="U20" s="23">
         <v>-90.29</v>
       </c>
-      <c r="V20" s="26">
+      <c r="V20" s="27">
         <v>-119.77</v>
       </c>
     </row>
@@ -15925,10 +15936,10 @@
       <c r="K22" s="18">
         <v>33.07</v>
       </c>
-      <c r="L22" s="22">
+      <c r="L22" s="23">
         <v>-19.2</v>
       </c>
-      <c r="M22" s="22">
+      <c r="M22" s="23">
         <v>-2.52</v>
       </c>
       <c r="N22" s="18">
@@ -15968,7 +15979,7 @@
       <c r="H23" s="18">
         <v>16.7</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="23">
         <v>-8.42</v>
       </c>
       <c r="J23" s="18">
@@ -15977,10 +15988,10 @@
       <c r="K23" s="18">
         <v>15.68</v>
       </c>
-      <c r="L23" s="22">
+      <c r="L23" s="23">
         <v>-3.12</v>
       </c>
-      <c r="M23" s="22">
+      <c r="M23" s="23">
         <v>-5.05</v>
       </c>
       <c r="N23" s="18">
@@ -15989,10 +16000,10 @@
       <c r="O23" s="18">
         <v>15.9</v>
       </c>
-      <c r="P23" s="22">
+      <c r="P23" s="23">
         <v>-20.91</v>
       </c>
-      <c r="Q23" s="22">
+      <c r="Q23" s="23">
         <v>-73.9</v>
       </c>
       <c r="R23" s="18">
@@ -16004,7 +16015,7 @@
       <c r="T23" s="18">
         <v>38.12</v>
       </c>
-      <c r="U23" s="22">
+      <c r="U23" s="23">
         <v>-28.95</v>
       </c>
       <c r="V23" s="15">
@@ -16015,10 +16026,10 @@
       <c r="A24" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="23">
         <v>-14.21</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="27">
         <v>-102.72</v>
       </c>
       <c r="D24" s="18">
@@ -16033,7 +16044,7 @@
       <c r="G24" s="18">
         <v>9.45</v>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="23">
         <v>-2.77</v>
       </c>
       <c r="I24" s="18">
@@ -16124,32 +16135,32 @@
       <c r="J26" s="18">
         <v>3.7</v>
       </c>
-      <c r="K26" s="22">
+      <c r="K26" s="23">
         <v>-0.16</v>
       </c>
       <c r="L26" s="19"/>
       <c r="M26" s="19"/>
       <c r="N26" s="19"/>
       <c r="O26" s="19"/>
-      <c r="P26" s="22">
+      <c r="P26" s="23">
         <v>-2.61</v>
       </c>
-      <c r="Q26" s="22">
+      <c r="Q26" s="23">
         <v>-3.51</v>
       </c>
       <c r="R26" s="18">
         <v>2.63</v>
       </c>
-      <c r="S26" s="22">
+      <c r="S26" s="23">
         <v>-2.03</v>
       </c>
-      <c r="T26" s="22">
+      <c r="T26" s="23">
         <v>-3.36</v>
       </c>
-      <c r="U26" s="22">
+      <c r="U26" s="23">
         <v>-6.43</v>
       </c>
-      <c r="V26" s="22">
+      <c r="V26" s="23">
         <v>-15.95</v>
       </c>
     </row>
@@ -16202,7 +16213,7 @@
       <c r="J28" s="18">
         <v>0.07</v>
       </c>
-      <c r="K28" s="22">
+      <c r="K28" s="23">
         <v>-0.21</v>
       </c>
       <c r="L28" s="19"/>
@@ -16231,10 +16242,10 @@
       <c r="I29" s="19"/>
       <c r="J29" s="19"/>
       <c r="K29" s="19"/>
-      <c r="L29" s="22">
+      <c r="L29" s="23">
         <v>-23.58</v>
       </c>
-      <c r="M29" s="22">
+      <c r="M29" s="23">
         <v>-4.12</v>
       </c>
       <c r="N29" s="18">
@@ -16260,7 +16271,7 @@
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="19"/>
-      <c r="G30" s="23">
+      <c r="G30" s="24">
         <v>0.0</v>
       </c>
       <c r="H30" s="19"/>
@@ -16285,40 +16296,40 @@
       <c r="A31" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="B31" s="22">
+      <c r="B31" s="23">
         <v>-13.48</v>
       </c>
       <c r="C31" s="18">
         <v>69.23</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="23">
         <v>-35.14</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="23">
         <v>-0.14</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="23">
         <v>-2.2</v>
       </c>
       <c r="G31" s="18">
         <v>26.84</v>
       </c>
-      <c r="H31" s="22">
+      <c r="H31" s="23">
         <v>-6.47</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31" s="23">
         <v>-34.23</v>
       </c>
-      <c r="J31" s="22">
+      <c r="J31" s="23">
         <v>-6.47</v>
       </c>
-      <c r="K31" s="22">
+      <c r="K31" s="23">
         <v>-10.17</v>
       </c>
       <c r="L31" s="19"/>
       <c r="M31" s="19"/>
       <c r="N31" s="19"/>
-      <c r="O31" s="22">
+      <c r="O31" s="23">
         <v>-25.54</v>
       </c>
       <c r="P31" s="18">
@@ -16330,7 +16341,7 @@
       <c r="R31" s="18">
         <v>7.33</v>
       </c>
-      <c r="S31" s="22">
+      <c r="S31" s="23">
         <v>-36.74</v>
       </c>
       <c r="T31" s="18">
@@ -16345,28 +16356,28 @@
       <c r="A32" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="23">
         <v>-6.37</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="23">
         <v>-6.7</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="23">
         <v>-12.71</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="23">
         <v>-15.04</v>
       </c>
       <c r="F32" s="18">
         <v>6.73</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="23">
         <v>-10.32</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="23">
         <v>-8.43</v>
       </c>
-      <c r="I32" s="22">
+      <c r="I32" s="23">
         <v>-5.81</v>
       </c>
       <c r="J32" s="18">
@@ -16390,10 +16401,10 @@
       <c r="R32" s="18">
         <v>7.88</v>
       </c>
-      <c r="S32" s="22">
+      <c r="S32" s="23">
         <v>-31.14</v>
       </c>
-      <c r="T32" s="22">
+      <c r="T32" s="23">
         <v>-23.89</v>
       </c>
       <c r="U32" s="18">
@@ -16405,10 +16416,10 @@
       <c r="A33" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B33" s="22">
+      <c r="B33" s="23">
         <v>-27.86</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="23">
         <v>-93.98</v>
       </c>
       <c r="D33" s="18">
@@ -16417,10 +16428,10 @@
       <c r="E33" s="18">
         <v>24.31</v>
       </c>
-      <c r="F33" s="22">
+      <c r="F33" s="23">
         <v>-25.8</v>
       </c>
-      <c r="G33" s="22">
+      <c r="G33" s="23">
         <v>-11.39</v>
       </c>
       <c r="H33" s="18">
@@ -16429,7 +16440,7 @@
       <c r="I33" s="18">
         <v>13.86</v>
       </c>
-      <c r="J33" s="22">
+      <c r="J33" s="23">
         <v>-2.7</v>
       </c>
       <c r="K33" s="18">
@@ -16453,37 +16464,37 @@
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="19"/>
-      <c r="D34" s="22">
+      <c r="D34" s="23">
         <v>-6.39</v>
       </c>
-      <c r="E34" s="22">
+      <c r="E34" s="23">
         <v>-6.7</v>
       </c>
-      <c r="F34" s="22">
+      <c r="F34" s="23">
         <v>-4.44</v>
       </c>
-      <c r="G34" s="22">
+      <c r="G34" s="23">
         <v>-3.42</v>
       </c>
-      <c r="H34" s="22">
+      <c r="H34" s="23">
         <v>-4.44</v>
       </c>
-      <c r="I34" s="22">
+      <c r="I34" s="23">
         <v>-3.54</v>
       </c>
-      <c r="J34" s="22">
+      <c r="J34" s="23">
         <v>-4.07</v>
       </c>
-      <c r="K34" s="22">
+      <c r="K34" s="23">
         <v>-3.76</v>
       </c>
       <c r="L34" s="19"/>
       <c r="M34" s="19"/>
       <c r="N34" s="19"/>
-      <c r="O34" s="22">
+      <c r="O34" s="23">
         <v>-2.41</v>
       </c>
-      <c r="P34" s="22">
+      <c r="P34" s="23">
         <v>-0.34</v>
       </c>
       <c r="Q34" s="19"/>
@@ -16497,43 +16508,43 @@
       <c r="A35" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="B35" s="22">
+      <c r="B35" s="23">
         <v>-11.97</v>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="23">
         <v>-1.98</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="23">
         <v>-2.86</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="23">
         <v>-2.21</v>
       </c>
-      <c r="F35" s="22">
+      <c r="F35" s="23">
         <v>-0.82</v>
       </c>
       <c r="G35" s="18">
         <v>0.75</v>
       </c>
-      <c r="H35" s="22">
+      <c r="H35" s="23">
         <v>-0.38</v>
       </c>
-      <c r="I35" s="22">
+      <c r="I35" s="23">
         <v>-1.29</v>
       </c>
-      <c r="J35" s="22">
+      <c r="J35" s="23">
         <v>-0.81</v>
       </c>
-      <c r="K35" s="22">
+      <c r="K35" s="23">
         <v>-0.7</v>
       </c>
-      <c r="L35" s="22">
+      <c r="L35" s="23">
         <v>-2.88</v>
       </c>
-      <c r="M35" s="22">
+      <c r="M35" s="23">
         <v>-6.11</v>
       </c>
-      <c r="N35" s="22">
+      <c r="N35" s="23">
         <v>-4.56</v>
       </c>
       <c r="O35" s="18">
@@ -16542,22 +16553,22 @@
       <c r="P35" s="18">
         <v>3.36</v>
       </c>
-      <c r="Q35" s="22">
+      <c r="Q35" s="23">
         <v>-10.8</v>
       </c>
-      <c r="R35" s="22">
+      <c r="R35" s="23">
         <v>-9.77</v>
       </c>
-      <c r="S35" s="22">
+      <c r="S35" s="23">
         <v>-10.76</v>
       </c>
-      <c r="T35" s="22">
+      <c r="T35" s="23">
         <v>-4.41</v>
       </c>
-      <c r="U35" s="22">
+      <c r="U35" s="23">
         <v>-30.88</v>
       </c>
-      <c r="V35" s="22">
+      <c r="V35" s="23">
         <v>-7.25</v>
       </c>
     </row>
@@ -16623,37 +16634,37 @@
       <c r="I37" s="19"/>
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
-      <c r="L37" s="22">
+      <c r="L37" s="23">
         <v>-5.67</v>
       </c>
-      <c r="M37" s="22">
+      <c r="M37" s="23">
         <v>-4.48</v>
       </c>
-      <c r="N37" s="22">
+      <c r="N37" s="23">
         <v>-3.89</v>
       </c>
-      <c r="O37" s="22">
+      <c r="O37" s="23">
         <v>-4.89</v>
       </c>
-      <c r="P37" s="22">
+      <c r="P37" s="23">
         <v>-5.07</v>
       </c>
-      <c r="Q37" s="22">
+      <c r="Q37" s="23">
         <v>-4.93</v>
       </c>
-      <c r="R37" s="22">
+      <c r="R37" s="23">
         <v>-5.08</v>
       </c>
-      <c r="S37" s="22">
+      <c r="S37" s="23">
         <v>-3.45</v>
       </c>
-      <c r="T37" s="22">
+      <c r="T37" s="23">
         <v>-3.58</v>
       </c>
-      <c r="U37" s="22">
+      <c r="U37" s="23">
         <v>-9.07</v>
       </c>
-      <c r="V37" s="22">
+      <c r="V37" s="23">
         <v>-19.45</v>
       </c>
     </row>
@@ -16673,10 +16684,10 @@
       <c r="K38" s="18">
         <v>29.31</v>
       </c>
-      <c r="L38" s="22">
+      <c r="L38" s="23">
         <v>-24.57</v>
       </c>
-      <c r="M38" s="22">
+      <c r="M38" s="23">
         <v>-6.73</v>
       </c>
       <c r="N38" s="18">
@@ -16704,7 +16715,7 @@
       <c r="H39" s="19">
         <v>0.0</v>
       </c>
-      <c r="I39" s="22">
+      <c r="I39" s="23">
         <v>-12.36</v>
       </c>
       <c r="J39" s="19"/>
@@ -16738,22 +16749,22 @@
       <c r="L40" s="19"/>
       <c r="M40" s="19"/>
       <c r="N40" s="19"/>
-      <c r="O40" s="22">
+      <c r="O40" s="23">
         <v>-1.92</v>
       </c>
-      <c r="P40" s="22">
+      <c r="P40" s="23">
         <v>-0.54</v>
       </c>
-      <c r="Q40" s="22">
+      <c r="Q40" s="23">
         <v>-0.19</v>
       </c>
       <c r="R40" s="19">
         <v>0.0</v>
       </c>
-      <c r="S40" s="22">
+      <c r="S40" s="23">
         <v>-0.66</v>
       </c>
-      <c r="T40" s="22">
+      <c r="T40" s="23">
         <v>-1.14</v>
       </c>
       <c r="U40" s="19"/>
@@ -16776,25 +16787,25 @@
       <c r="L41" s="19"/>
       <c r="M41" s="19"/>
       <c r="N41" s="19"/>
-      <c r="O41" s="22">
+      <c r="O41" s="23">
         <v>-0.02</v>
       </c>
       <c r="P41" s="19">
         <v>0.0</v>
       </c>
-      <c r="Q41" s="22">
+      <c r="Q41" s="23">
         <v>-4.61</v>
       </c>
       <c r="R41" s="19">
         <v>0.0</v>
       </c>
-      <c r="S41" s="22">
+      <c r="S41" s="23">
         <v>-0.02</v>
       </c>
       <c r="T41" s="18">
         <v>4.01</v>
       </c>
-      <c r="U41" s="22">
+      <c r="U41" s="23">
         <v>-0.94</v>
       </c>
       <c r="V41" s="18">
@@ -16824,22 +16835,22 @@
       <c r="N42" s="19"/>
       <c r="O42" s="19"/>
       <c r="P42" s="19"/>
-      <c r="Q42" s="22">
+      <c r="Q42" s="23">
         <v>-4.52</v>
       </c>
-      <c r="R42" s="22">
+      <c r="R42" s="23">
         <v>-4.96</v>
       </c>
-      <c r="S42" s="22">
+      <c r="S42" s="23">
         <v>-6.33</v>
       </c>
-      <c r="T42" s="22">
+      <c r="T42" s="23">
         <v>-14.85</v>
       </c>
-      <c r="U42" s="22">
+      <c r="U42" s="23">
         <v>-21.81</v>
       </c>
-      <c r="V42" s="22">
+      <c r="V42" s="23">
         <v>-25.5</v>
       </c>
     </row>
@@ -16863,7 +16874,7 @@
       <c r="O43" s="18">
         <v>1.44</v>
       </c>
-      <c r="P43" s="22">
+      <c r="P43" s="23">
         <v>-37.27</v>
       </c>
       <c r="Q43" s="19"/>
@@ -16877,10 +16888,10 @@
       <c r="A44" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="B44" s="22">
+      <c r="B44" s="23">
         <v>-7.19</v>
       </c>
-      <c r="C44" s="22">
+      <c r="C44" s="23">
         <v>-8.41</v>
       </c>
       <c r="D44" s="19"/>
@@ -17041,7 +17052,7 @@
       <c r="A49" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="B49" s="24">
+      <c r="B49" s="25">
         <v>-50.2</v>
       </c>
       <c r="C49" s="21">
@@ -17062,7 +17073,7 @@
       <c r="H49" s="21">
         <v>11.48</v>
       </c>
-      <c r="I49" s="24">
+      <c r="I49" s="25">
         <v>-11.37</v>
       </c>
       <c r="J49" s="21">
@@ -17071,10 +17082,10 @@
       <c r="K49" s="21">
         <v>28.61</v>
       </c>
-      <c r="L49" s="24">
+      <c r="L49" s="25">
         <v>-27.44</v>
       </c>
-      <c r="M49" s="24">
+      <c r="M49" s="25">
         <v>-12.84</v>
       </c>
       <c r="N49" s="21">
@@ -17086,10 +17097,10 @@
       <c r="P49" s="21">
         <v>32.39</v>
       </c>
-      <c r="Q49" s="24">
+      <c r="Q49" s="25">
         <v>-67.17</v>
       </c>
-      <c r="R49" s="24">
+      <c r="R49" s="25">
         <v>-12.86</v>
       </c>
       <c r="S49" s="21">
@@ -17179,7 +17190,7 @@
       <c r="M51" s="18">
         <v>0.01</v>
       </c>
-      <c r="N51" s="22">
+      <c r="N51" s="23">
         <v>-0.02</v>
       </c>
       <c r="O51" s="18">
@@ -17188,22 +17199,22 @@
       <c r="P51" s="18">
         <v>0.13</v>
       </c>
-      <c r="Q51" s="22">
+      <c r="Q51" s="23">
         <v>-0.1</v>
       </c>
       <c r="R51" s="18">
         <v>0.11</v>
       </c>
-      <c r="S51" s="22">
+      <c r="S51" s="23">
         <v>-0.06</v>
       </c>
       <c r="T51" s="18">
         <v>0.73</v>
       </c>
-      <c r="U51" s="22">
+      <c r="U51" s="23">
         <v>-0.06</v>
       </c>
-      <c r="V51" s="22">
+      <c r="V51" s="23">
         <v>-3.54</v>
       </c>
     </row>
@@ -17224,7 +17235,7 @@
       <c r="L52" s="19">
         <v>0.0</v>
       </c>
-      <c r="M52" s="22">
+      <c r="M52" s="23">
         <v>-0.08</v>
       </c>
       <c r="N52" s="19"/>
@@ -17243,67 +17254,67 @@
       <c r="A53" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="B53" s="22">
+      <c r="B53" s="23">
         <v>-0.33</v>
       </c>
-      <c r="C53" s="22">
+      <c r="C53" s="23">
         <v>-0.86</v>
       </c>
-      <c r="D53" s="22">
+      <c r="D53" s="23">
         <v>-5.64</v>
       </c>
-      <c r="E53" s="22">
+      <c r="E53" s="23">
         <v>-5.41</v>
       </c>
-      <c r="F53" s="22">
+      <c r="F53" s="23">
         <v>-3.93</v>
       </c>
-      <c r="G53" s="22">
+      <c r="G53" s="23">
         <v>-3.56</v>
       </c>
-      <c r="H53" s="22">
+      <c r="H53" s="23">
         <v>-1.83</v>
       </c>
-      <c r="I53" s="22">
+      <c r="I53" s="23">
         <v>-3.77</v>
       </c>
-      <c r="J53" s="22">
+      <c r="J53" s="23">
         <v>-6.28</v>
       </c>
-      <c r="K53" s="22">
+      <c r="K53" s="23">
         <v>-0.86</v>
       </c>
-      <c r="L53" s="22">
+      <c r="L53" s="23">
         <v>-0.51</v>
       </c>
-      <c r="M53" s="22">
+      <c r="M53" s="23">
         <v>-0.8</v>
       </c>
-      <c r="N53" s="22">
+      <c r="N53" s="23">
         <v>-1.95</v>
       </c>
       <c r="O53" s="19">
         <v>0.0</v>
       </c>
-      <c r="P53" s="22">
+      <c r="P53" s="23">
         <v>-0.54</v>
       </c>
-      <c r="Q53" s="22">
+      <c r="Q53" s="23">
         <v>-2.37</v>
       </c>
-      <c r="R53" s="22">
+      <c r="R53" s="23">
         <v>-0.49</v>
       </c>
-      <c r="S53" s="22">
+      <c r="S53" s="23">
         <v>-0.35</v>
       </c>
-      <c r="T53" s="22">
+      <c r="T53" s="23">
         <v>-0.43</v>
       </c>
-      <c r="U53" s="22">
+      <c r="U53" s="23">
         <v>-0.16</v>
       </c>
-      <c r="V53" s="22">
+      <c r="V53" s="23">
         <v>-1.58</v>
       </c>
     </row>
@@ -17311,67 +17322,67 @@
       <c r="A54" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B54" s="22">
+      <c r="B54" s="23">
         <v>-7.99</v>
       </c>
-      <c r="C54" s="22">
+      <c r="C54" s="23">
         <v>-16.23</v>
       </c>
-      <c r="D54" s="22">
+      <c r="D54" s="23">
         <v>-8.38</v>
       </c>
-      <c r="E54" s="22">
+      <c r="E54" s="23">
         <v>-4.79</v>
       </c>
-      <c r="F54" s="22">
+      <c r="F54" s="23">
         <v>-8.43</v>
       </c>
-      <c r="G54" s="22">
+      <c r="G54" s="23">
         <v>-12.42</v>
       </c>
-      <c r="H54" s="22">
+      <c r="H54" s="23">
         <v>-2.73</v>
       </c>
-      <c r="I54" s="22">
+      <c r="I54" s="23">
         <v>-5.62</v>
       </c>
-      <c r="J54" s="22">
+      <c r="J54" s="23">
         <v>-1.02</v>
       </c>
-      <c r="K54" s="22">
+      <c r="K54" s="23">
         <v>-0.63</v>
       </c>
-      <c r="L54" s="22">
+      <c r="L54" s="23">
         <v>-2.45</v>
       </c>
-      <c r="M54" s="22">
+      <c r="M54" s="23">
         <v>-2.53</v>
       </c>
-      <c r="N54" s="22">
+      <c r="N54" s="23">
         <v>-2.03</v>
       </c>
-      <c r="O54" s="22">
+      <c r="O54" s="23">
         <v>-2.07</v>
       </c>
-      <c r="P54" s="22">
+      <c r="P54" s="23">
         <v>-0.98</v>
       </c>
-      <c r="Q54" s="22">
+      <c r="Q54" s="23">
         <v>-27.19</v>
       </c>
-      <c r="R54" s="22">
+      <c r="R54" s="23">
         <v>-44.77</v>
       </c>
-      <c r="S54" s="22">
+      <c r="S54" s="23">
         <v>-5.89</v>
       </c>
-      <c r="T54" s="22">
+      <c r="T54" s="23">
         <v>-2.96</v>
       </c>
-      <c r="U54" s="22">
+      <c r="U54" s="23">
         <v>-6.66</v>
       </c>
-      <c r="V54" s="22">
+      <c r="V54" s="23">
         <v>-71.01</v>
       </c>
     </row>
@@ -17405,7 +17416,7 @@
       <c r="S55" s="18">
         <v>26.46</v>
       </c>
-      <c r="T55" s="26">
+      <c r="T55" s="27">
         <v>-107.13</v>
       </c>
       <c r="U55" s="18">
@@ -17529,7 +17540,7 @@
       <c r="A59" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="B59" s="22">
+      <c r="B59" s="23">
         <v>-4.04</v>
       </c>
       <c r="C59" s="15">
@@ -17565,10 +17576,10 @@
       <c r="E60" s="19">
         <v>0.0</v>
       </c>
-      <c r="F60" s="22">
+      <c r="F60" s="23">
         <v>-6.49</v>
       </c>
-      <c r="G60" s="22">
+      <c r="G60" s="23">
         <v>-43.77</v>
       </c>
       <c r="H60" s="19"/>
@@ -17584,7 +17595,7 @@
       <c r="R60" s="19"/>
       <c r="S60" s="19"/>
       <c r="T60" s="19"/>
-      <c r="U60" s="22">
+      <c r="U60" s="23">
         <v>-21.96</v>
       </c>
       <c r="V60" s="19">
@@ -17635,7 +17646,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="19"/>
       <c r="K62" s="19"/>
-      <c r="L62" s="23">
+      <c r="L62" s="24">
         <v>0.0</v>
       </c>
       <c r="M62" s="19">
@@ -17643,19 +17654,19 @@
       </c>
       <c r="N62" s="19"/>
       <c r="O62" s="19"/>
-      <c r="P62" s="22">
+      <c r="P62" s="23">
         <v>-0.02</v>
       </c>
-      <c r="Q62" s="22">
+      <c r="Q62" s="23">
         <v>-0.02</v>
       </c>
-      <c r="R62" s="22">
+      <c r="R62" s="23">
         <v>-0.02</v>
       </c>
-      <c r="S62" s="22">
+      <c r="S62" s="23">
         <v>-0.02</v>
       </c>
-      <c r="T62" s="22">
+      <c r="T62" s="23">
         <v>-0.02</v>
       </c>
       <c r="U62" s="19"/>
@@ -17665,34 +17676,34 @@
       <c r="A63" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="B63" s="24">
+      <c r="B63" s="25">
         <v>-9.4</v>
       </c>
       <c r="C63" s="17">
         <v>247.86</v>
       </c>
-      <c r="D63" s="24">
+      <c r="D63" s="25">
         <v>-11.72</v>
       </c>
-      <c r="E63" s="24">
+      <c r="E63" s="25">
         <v>-10.2</v>
       </c>
-      <c r="F63" s="24">
+      <c r="F63" s="25">
         <v>-18.84</v>
       </c>
-      <c r="G63" s="24">
+      <c r="G63" s="25">
         <v>-59.75</v>
       </c>
       <c r="H63" s="21">
         <v>26.62</v>
       </c>
-      <c r="I63" s="24">
+      <c r="I63" s="25">
         <v>-9.39</v>
       </c>
-      <c r="J63" s="24">
+      <c r="J63" s="25">
         <v>-7.3</v>
       </c>
-      <c r="K63" s="24">
+      <c r="K63" s="25">
         <v>-1.49</v>
       </c>
       <c r="L63" s="21">
@@ -17701,10 +17712,10 @@
       <c r="M63" s="21">
         <v>6.68</v>
       </c>
-      <c r="N63" s="24">
+      <c r="N63" s="25">
         <v>-1.44</v>
       </c>
-      <c r="O63" s="24">
+      <c r="O63" s="25">
         <v>-1.49</v>
       </c>
       <c r="P63" s="21">
@@ -17713,13 +17724,13 @@
       <c r="Q63" s="21">
         <v>1.61</v>
       </c>
-      <c r="R63" s="24">
+      <c r="R63" s="25">
         <v>-14.44</v>
       </c>
       <c r="S63" s="21">
         <v>24.68</v>
       </c>
-      <c r="T63" s="24">
+      <c r="T63" s="25">
         <v>-94.8</v>
       </c>
       <c r="U63" s="17">
@@ -17751,49 +17762,49 @@
       <c r="G64" s="18">
         <v>46.89</v>
       </c>
-      <c r="H64" s="22">
+      <c r="H64" s="23">
         <v>-12.03</v>
       </c>
-      <c r="I64" s="22">
+      <c r="I64" s="23">
         <v>-3.08</v>
       </c>
-      <c r="J64" s="22">
+      <c r="J64" s="23">
         <v>-2.98</v>
       </c>
       <c r="K64" s="18">
         <v>1.97</v>
       </c>
-      <c r="L64" s="22">
+      <c r="L64" s="23">
         <v>-3.59</v>
       </c>
-      <c r="M64" s="22">
+      <c r="M64" s="23">
         <v>-3.97</v>
       </c>
-      <c r="N64" s="22">
+      <c r="N64" s="23">
         <v>-3.82</v>
       </c>
-      <c r="O64" s="22">
+      <c r="O64" s="23">
         <v>-3.96</v>
       </c>
-      <c r="P64" s="22">
+      <c r="P64" s="23">
         <v>-4.07</v>
       </c>
-      <c r="Q64" s="22">
+      <c r="Q64" s="23">
         <v>-2.03</v>
       </c>
-      <c r="R64" s="22">
+      <c r="R64" s="23">
         <v>-0.26</v>
       </c>
-      <c r="S64" s="22">
+      <c r="S64" s="23">
         <v>-0.37</v>
       </c>
-      <c r="T64" s="22">
+      <c r="T64" s="23">
         <v>-1.61</v>
       </c>
-      <c r="U64" s="22">
+      <c r="U64" s="23">
         <v>-5.98</v>
       </c>
-      <c r="V64" s="22">
+      <c r="V64" s="23">
         <v>-30.8</v>
       </c>
     </row>
@@ -17831,22 +17842,22 @@
       <c r="A66" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="B66" s="22">
+      <c r="B66" s="23">
         <v>-10.67</v>
       </c>
-      <c r="C66" s="22">
+      <c r="C66" s="23">
         <v>-20.4</v>
       </c>
-      <c r="D66" s="22">
+      <c r="D66" s="23">
         <v>-2.81</v>
       </c>
-      <c r="E66" s="22">
+      <c r="E66" s="23">
         <v>-18.76</v>
       </c>
-      <c r="F66" s="22">
+      <c r="F66" s="23">
         <v>-12.06</v>
       </c>
-      <c r="G66" s="22">
+      <c r="G66" s="23">
         <v>-4.15</v>
       </c>
       <c r="H66" s="19"/>
@@ -17872,7 +17883,7 @@
       <c r="B67" s="18">
         <v>65.14</v>
       </c>
-      <c r="C67" s="22">
+      <c r="C67" s="23">
         <v>-53.36</v>
       </c>
       <c r="D67" s="18">
@@ -17887,7 +17898,7 @@
       <c r="G67" s="18">
         <v>5.52</v>
       </c>
-      <c r="H67" s="22">
+      <c r="H67" s="23">
         <v>-15.91</v>
       </c>
       <c r="I67" s="18">
@@ -18013,19 +18024,19 @@
       <c r="A71" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="B71" s="26">
+      <c r="B71" s="27">
         <v>-212.73</v>
       </c>
-      <c r="C71" s="22">
+      <c r="C71" s="23">
         <v>-23.79</v>
       </c>
-      <c r="D71" s="22">
+      <c r="D71" s="23">
         <v>-16.74</v>
       </c>
-      <c r="E71" s="22">
+      <c r="E71" s="23">
         <v>-12.64</v>
       </c>
-      <c r="F71" s="22">
+      <c r="F71" s="23">
         <v>-8.88</v>
       </c>
       <c r="G71" s="19"/>
@@ -18043,19 +18054,19 @@
       <c r="Q71" s="19">
         <v>0.0</v>
       </c>
-      <c r="R71" s="22">
+      <c r="R71" s="23">
         <v>-18.84</v>
       </c>
-      <c r="S71" s="22">
+      <c r="S71" s="23">
         <v>-48.92</v>
       </c>
-      <c r="T71" s="26">
+      <c r="T71" s="27">
         <v>-367.46</v>
       </c>
-      <c r="U71" s="26">
+      <c r="U71" s="27">
         <v>-342.84</v>
       </c>
-      <c r="V71" s="26">
+      <c r="V71" s="27">
         <v>-102.33</v>
       </c>
     </row>
@@ -18075,7 +18086,7 @@
       <c r="K72" s="19"/>
       <c r="L72" s="19"/>
       <c r="M72" s="19"/>
-      <c r="N72" s="22">
+      <c r="N72" s="23">
         <v>-0.48</v>
       </c>
       <c r="O72" s="18">
@@ -18084,13 +18095,13 @@
       <c r="P72" s="19">
         <v>0.0</v>
       </c>
-      <c r="Q72" s="22">
+      <c r="Q72" s="23">
         <v>-0.82</v>
       </c>
-      <c r="R72" s="22">
+      <c r="R72" s="23">
         <v>-3.87</v>
       </c>
-      <c r="S72" s="23">
+      <c r="S72" s="24">
         <v>0.0</v>
       </c>
       <c r="T72" s="19">
@@ -18122,7 +18133,7 @@
       <c r="R73" s="19"/>
       <c r="S73" s="19"/>
       <c r="T73" s="19"/>
-      <c r="U73" s="22">
+      <c r="U73" s="23">
         <v>-2.8</v>
       </c>
       <c r="V73" s="19">
@@ -18171,16 +18182,16 @@
       <c r="A75" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="B75" s="27">
+      <c r="B75" s="28">
         <v>-144.81</v>
       </c>
-      <c r="C75" s="24">
+      <c r="C75" s="25">
         <v>-96.67</v>
       </c>
-      <c r="D75" s="24">
+      <c r="D75" s="25">
         <v>-16.64</v>
       </c>
-      <c r="E75" s="24">
+      <c r="E75" s="25">
         <v>-22.96</v>
       </c>
       <c r="F75" s="21">
@@ -18189,49 +18200,49 @@
       <c r="G75" s="21">
         <v>48.26</v>
       </c>
-      <c r="H75" s="24">
+      <c r="H75" s="25">
         <v>-27.94</v>
       </c>
       <c r="I75" s="21">
         <v>12.81</v>
       </c>
-      <c r="J75" s="24">
+      <c r="J75" s="25">
         <v>-2.98</v>
       </c>
       <c r="K75" s="21">
         <v>1.97</v>
       </c>
-      <c r="L75" s="24">
+      <c r="L75" s="25">
         <v>-3.59</v>
       </c>
-      <c r="M75" s="24">
+      <c r="M75" s="25">
         <v>-3.88</v>
       </c>
-      <c r="N75" s="24">
+      <c r="N75" s="25">
         <v>-4.3</v>
       </c>
       <c r="O75" s="21">
         <v>11.46</v>
       </c>
-      <c r="P75" s="24">
+      <c r="P75" s="25">
         <v>-4.06</v>
       </c>
       <c r="Q75" s="21">
         <v>40.79</v>
       </c>
-      <c r="R75" s="24">
+      <c r="R75" s="25">
         <v>-22.95</v>
       </c>
-      <c r="S75" s="24">
+      <c r="S75" s="25">
         <v>-49.27</v>
       </c>
-      <c r="T75" s="27">
+      <c r="T75" s="28">
         <v>-368.65</v>
       </c>
-      <c r="U75" s="27">
+      <c r="U75" s="28">
         <v>-351.62</v>
       </c>
-      <c r="V75" s="24">
+      <c r="V75" s="25">
         <v>-79.04</v>
       </c>
     </row>
@@ -18249,13 +18260,13 @@
       <c r="I76" s="19"/>
       <c r="J76" s="19"/>
       <c r="K76" s="19"/>
-      <c r="L76" s="22">
+      <c r="L76" s="23">
         <v>-4.55</v>
       </c>
       <c r="M76" s="18">
         <v>1.2</v>
       </c>
-      <c r="N76" s="22">
+      <c r="N76" s="23">
         <v>-3.07</v>
       </c>
       <c r="O76" s="19"/>
@@ -18281,13 +18292,13 @@
       <c r="I77" s="20"/>
       <c r="J77" s="20"/>
       <c r="K77" s="20"/>
-      <c r="L77" s="24">
+      <c r="L77" s="25">
         <v>-4.55</v>
       </c>
       <c r="M77" s="21">
         <v>1.2</v>
       </c>
-      <c r="N77" s="24">
+      <c r="N77" s="25">
         <v>-3.07</v>
       </c>
       <c r="O77" s="20"/>
@@ -18313,10 +18324,10 @@
       <c r="I78" s="19"/>
       <c r="J78" s="19"/>
       <c r="K78" s="19"/>
-      <c r="L78" s="22">
+      <c r="L78" s="23">
         <v>-28.91</v>
       </c>
-      <c r="M78" s="22">
+      <c r="M78" s="23">
         <v>-10.04</v>
       </c>
       <c r="N78" s="18">
@@ -18339,25 +18350,25 @@
       <c r="C79" s="19">
         <v>0.0</v>
       </c>
-      <c r="D79" s="22">
+      <c r="D79" s="23">
         <v>-2.56</v>
       </c>
-      <c r="E79" s="22">
+      <c r="E79" s="23">
         <v>-0.49</v>
       </c>
-      <c r="F79" s="22">
+      <c r="F79" s="23">
         <v>-0.67</v>
       </c>
       <c r="G79" s="18">
         <v>0.11</v>
       </c>
-      <c r="H79" s="22">
+      <c r="H79" s="23">
         <v>-0.21</v>
       </c>
-      <c r="I79" s="22">
+      <c r="I79" s="23">
         <v>-0.11</v>
       </c>
-      <c r="J79" s="22">
+      <c r="J79" s="23">
         <v>-0.09</v>
       </c>
       <c r="K79" s="18">
@@ -18366,7 +18377,7 @@
       <c r="L79" s="18">
         <v>0.19</v>
       </c>
-      <c r="M79" s="22">
+      <c r="M79" s="23">
         <v>-0.26</v>
       </c>
       <c r="N79" s="18">
@@ -18375,22 +18386,22 @@
       <c r="O79" s="18">
         <v>0.01</v>
       </c>
-      <c r="P79" s="22">
+      <c r="P79" s="23">
         <v>-0.01</v>
       </c>
       <c r="Q79" s="18">
         <v>0.07</v>
       </c>
-      <c r="R79" s="22">
+      <c r="R79" s="23">
         <v>-0.55</v>
       </c>
-      <c r="S79" s="22">
+      <c r="S79" s="23">
         <v>-0.56</v>
       </c>
-      <c r="T79" s="22">
+      <c r="T79" s="23">
         <v>-0.02</v>
       </c>
-      <c r="U79" s="22">
+      <c r="U79" s="23">
         <v>-1.0</v>
       </c>
       <c r="V79" s="19">
@@ -18425,28 +18436,28 @@
       <c r="I80" s="18">
         <v>12.52</v>
       </c>
-      <c r="J80" s="22">
+      <c r="J80" s="23">
         <v>-18.46</v>
       </c>
-      <c r="K80" s="22">
+      <c r="K80" s="23">
         <v>-51.14</v>
       </c>
-      <c r="L80" s="22">
+      <c r="L80" s="23">
         <v>-3.46</v>
       </c>
       <c r="M80" s="18">
         <v>6.52</v>
       </c>
-      <c r="N80" s="22">
+      <c r="N80" s="23">
         <v>-5.4</v>
       </c>
-      <c r="O80" s="22">
+      <c r="O80" s="23">
         <v>-23.39</v>
       </c>
-      <c r="P80" s="22">
+      <c r="P80" s="23">
         <v>-52.26</v>
       </c>
-      <c r="Q80" s="22">
+      <c r="Q80" s="23">
         <v>-32.27</v>
       </c>
       <c r="R80" s="18">
@@ -18493,31 +18504,31 @@
       <c r="I81" s="18">
         <v>4.01</v>
       </c>
-      <c r="J81" s="22">
+      <c r="J81" s="23">
         <v>-8.01</v>
       </c>
-      <c r="K81" s="22">
+      <c r="K81" s="23">
         <v>-19.42</v>
       </c>
-      <c r="L81" s="22">
+      <c r="L81" s="23">
         <v>-39.49</v>
       </c>
-      <c r="M81" s="22">
+      <c r="M81" s="23">
         <v>-3.18</v>
       </c>
       <c r="N81" s="18">
         <v>5.74</v>
       </c>
-      <c r="O81" s="22">
+      <c r="O81" s="23">
         <v>-5.71</v>
       </c>
-      <c r="P81" s="22">
+      <c r="P81" s="23">
         <v>-23.49</v>
       </c>
-      <c r="Q81" s="22">
+      <c r="Q81" s="23">
         <v>-55.75</v>
       </c>
-      <c r="R81" s="22">
+      <c r="R81" s="23">
         <v>-37.76</v>
       </c>
       <c r="S81" s="18">
@@ -18537,7 +18548,7 @@
       <c r="A82" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="B82" s="26">
+      <c r="B82" s="27">
         <v>-204.42</v>
       </c>
       <c r="C82" s="15">
@@ -18558,7 +18569,7 @@
       <c r="H82" s="18">
         <v>10.15</v>
       </c>
-      <c r="I82" s="22">
+      <c r="I82" s="23">
         <v>-7.95</v>
       </c>
       <c r="J82" s="18">
@@ -18567,10 +18578,10 @@
       <c r="K82" s="18">
         <v>29.09</v>
       </c>
-      <c r="L82" s="22">
+      <c r="L82" s="23">
         <v>-33.47</v>
       </c>
-      <c r="M82" s="22">
+      <c r="M82" s="23">
         <v>-8.84</v>
       </c>
       <c r="N82" s="18">
@@ -18589,7 +18600,7 @@
       <c r="A83" s="16" t="s">
         <v>343</v>
       </c>
-      <c r="B83" s="27">
+      <c r="B83" s="28">
         <v>-204.42</v>
       </c>
       <c r="C83" s="17">
@@ -18610,7 +18621,7 @@
       <c r="H83" s="21">
         <v>9.94</v>
       </c>
-      <c r="I83" s="24">
+      <c r="I83" s="25">
         <v>-8.07</v>
       </c>
       <c r="J83" s="21">
@@ -18619,10 +18630,10 @@
       <c r="K83" s="21">
         <v>29.58</v>
       </c>
-      <c r="L83" s="24">
+      <c r="L83" s="25">
         <v>-33.28</v>
       </c>
-      <c r="M83" s="24">
+      <c r="M83" s="25">
         <v>-9.09</v>
       </c>
       <c r="N83" s="21">
@@ -18634,16 +18645,16 @@
       <c r="P83" s="21">
         <v>66.88</v>
       </c>
-      <c r="Q83" s="24">
+      <c r="Q83" s="25">
         <v>-24.7</v>
       </c>
-      <c r="R83" s="24">
+      <c r="R83" s="25">
         <v>-50.81</v>
       </c>
-      <c r="S83" s="24">
+      <c r="S83" s="25">
         <v>-1.61</v>
       </c>
-      <c r="T83" s="27">
+      <c r="T83" s="28">
         <v>-457.29</v>
       </c>
       <c r="U83" s="17">
@@ -18671,7 +18682,7 @@
       <c r="M84" s="19"/>
       <c r="N84" s="19"/>
       <c r="O84" s="19"/>
-      <c r="P84" s="22">
+      <c r="P84" s="23">
         <v>-37.27</v>
       </c>
       <c r="Q84" s="19"/>
@@ -18727,7 +18738,7 @@
       <c r="M86" s="19"/>
       <c r="N86" s="19"/>
       <c r="O86" s="19"/>
-      <c r="P86" s="22">
+      <c r="P86" s="23">
         <v>-0.09</v>
       </c>
       <c r="Q86" s="19"/>
@@ -18756,7 +18767,7 @@
       <c r="N87" s="19"/>
       <c r="O87" s="19"/>
       <c r="P87" s="19"/>
-      <c r="Q87" s="22">
+      <c r="Q87" s="23">
         <v>-84.82</v>
       </c>
       <c r="R87" s="18">
@@ -18791,10 +18802,10 @@
       <c r="Q88" s="18">
         <v>17.65</v>
       </c>
-      <c r="R88" s="22">
+      <c r="R88" s="23">
         <v>-15.61</v>
       </c>
-      <c r="S88" s="22">
+      <c r="S88" s="23">
         <v>-6.07</v>
       </c>
       <c r="T88" s="19"/>
@@ -18821,19 +18832,19 @@
       <c r="O89" s="18">
         <v>0.26</v>
       </c>
-      <c r="P89" s="22">
+      <c r="P89" s="23">
         <v>-1.24</v>
       </c>
-      <c r="Q89" s="22">
+      <c r="Q89" s="23">
         <v>-54.05</v>
       </c>
-      <c r="R89" s="22">
+      <c r="R89" s="23">
         <v>-30.81</v>
       </c>
       <c r="S89" s="18">
         <v>61.81</v>
       </c>
-      <c r="T89" s="22">
+      <c r="T89" s="23">
         <v>-16.03</v>
       </c>
       <c r="U89" s="18">
@@ -20556,3430 +20567,3430 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="29" t="s">
         <v>368</v>
       </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="29"/>
-      <c r="Y20" s="29"/>
-      <c r="Z20" s="29"/>
-      <c r="AA20" s="29"/>
-      <c r="AB20" s="29"/>
-      <c r="AC20" s="29"/>
-      <c r="AD20" s="29"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="30"/>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="31" t="s">
         <v>368</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="32">
         <v>462.82</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="33">
         <v>97.62</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <v>203.2</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <v>182.49</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <v>194.46</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <v>161.58</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <v>135.59</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="32">
         <v>270.94</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="32">
         <v>242.93</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="32">
         <v>152.38</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="32">
         <v>116.88</v>
       </c>
-      <c r="M21" s="32">
+      <c r="M21" s="33">
         <v>88.4</v>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="33">
         <v>86.3</v>
       </c>
-      <c r="O21" s="32">
+      <c r="O21" s="33">
         <v>84.2</v>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="33">
         <v>99.0</v>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="32">
         <v>127.41</v>
       </c>
-      <c r="R21" s="31">
+      <c r="R21" s="32">
         <v>176.1</v>
       </c>
-      <c r="S21" s="31">
+      <c r="S21" s="32">
         <v>170.1</v>
       </c>
-      <c r="T21" s="31">
+      <c r="T21" s="32">
         <v>395.27</v>
       </c>
-      <c r="U21" s="33">
+      <c r="U21" s="34">
         <v>-79.18</v>
       </c>
-      <c r="V21" s="31">
+      <c r="V21" s="32">
         <v>312.57</v>
       </c>
-      <c r="W21" s="31">
+      <c r="W21" s="32">
         <v>581.68</v>
       </c>
-      <c r="X21" s="31">
+      <c r="X21" s="32">
         <v>570.48</v>
       </c>
-      <c r="Y21" s="31">
+      <c r="Y21" s="32">
         <v>350.37</v>
       </c>
-      <c r="Z21" s="31">
+      <c r="Z21" s="32">
         <v>2145.28</v>
       </c>
-      <c r="AA21" s="31">
+      <c r="AA21" s="32">
         <v>1829.76</v>
       </c>
-      <c r="AB21" s="31">
+      <c r="AB21" s="32">
         <v>720.33</v>
       </c>
-      <c r="AC21" s="31">
+      <c r="AC21" s="32">
         <v>572.79</v>
       </c>
-      <c r="AD21" s="31">
+      <c r="AD21" s="32">
         <v>190.83</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="31" t="s">
         <v>369</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="32">
         <v>244.94</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <v>181.69</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <v>181.23</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <v>189.39</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <v>215.82</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <v>196.8</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="32">
         <v>191.18</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="32">
         <v>184.48</v>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="32">
         <v>141.87</v>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="32">
         <v>118.96</v>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="32">
         <v>106.51</v>
       </c>
-      <c r="M22" s="31">
+      <c r="M22" s="32">
         <v>102.11</v>
       </c>
-      <c r="N22" s="31">
+      <c r="N22" s="32">
         <v>100.91</v>
       </c>
-      <c r="O22" s="31">
+      <c r="O22" s="32">
         <v>121.71</v>
       </c>
-      <c r="P22" s="31">
+      <c r="P22" s="32">
         <v>180.19</v>
       </c>
-      <c r="Q22" s="31">
+      <c r="Q22" s="32">
         <v>154.59</v>
       </c>
-      <c r="R22" s="31">
+      <c r="R22" s="32">
         <v>224.69</v>
       </c>
-      <c r="S22" s="31">
+      <c r="S22" s="32">
         <v>264.37</v>
       </c>
-      <c r="T22" s="31">
+      <c r="T22" s="32">
         <v>367.43</v>
       </c>
-      <c r="U22" s="31">
+      <c r="U22" s="32">
         <v>349.82</v>
       </c>
-      <c r="V22" s="31">
+      <c r="V22" s="32">
         <v>807.59</v>
       </c>
-      <c r="W22" s="31">
+      <c r="W22" s="32">
         <v>1137.62</v>
       </c>
-      <c r="X22" s="31">
+      <c r="X22" s="32">
         <v>1006.51</v>
       </c>
-      <c r="Y22" s="31">
+      <c r="Y22" s="32">
         <v>1090.32</v>
       </c>
-      <c r="Z22" s="31">
+      <c r="Z22" s="32">
         <v>1093.22</v>
       </c>
-      <c r="AA22" s="34"/>
-      <c r="AB22" s="34"/>
-      <c r="AC22" s="34"/>
-      <c r="AD22" s="34"/>
+      <c r="AA22" s="35"/>
+      <c r="AB22" s="35"/>
+      <c r="AC22" s="35"/>
+      <c r="AD22" s="35"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="29" t="s">
         <v>370</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
-      <c r="Y23" s="29"/>
-      <c r="Z23" s="29"/>
-      <c r="AA23" s="29"/>
-      <c r="AB23" s="29"/>
-      <c r="AC23" s="29"/>
-      <c r="AD23" s="29"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="30"/>
+      <c r="AB23" s="30"/>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="31" t="s">
         <v>370</v>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="32">
         <v>403.96</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <v>303.91</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <v>173.59</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <v>146.15</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <v>137.87</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <v>118.93</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <v>128.36</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="32">
         <v>236.7</v>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="32">
         <v>222.39</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="32">
         <v>113.32</v>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="33">
         <v>52.04</v>
       </c>
-      <c r="M24" s="32">
+      <c r="M24" s="33">
         <v>60.89</v>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="33">
         <v>46.45</v>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="33">
         <v>27.92</v>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="33">
         <v>40.47</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="33">
         <v>69.96</v>
       </c>
-      <c r="R24" s="31">
+      <c r="R24" s="32">
         <v>199.07</v>
       </c>
-      <c r="S24" s="31">
+      <c r="S24" s="32">
         <v>267.24</v>
       </c>
-      <c r="T24" s="31">
+      <c r="T24" s="32">
         <v>524.23</v>
       </c>
-      <c r="U24" s="31">
+      <c r="U24" s="32">
         <v>391.52</v>
       </c>
-      <c r="V24" s="31">
+      <c r="V24" s="32">
         <v>601.43</v>
       </c>
-      <c r="W24" s="31">
+      <c r="W24" s="32">
         <v>437.87</v>
       </c>
-      <c r="X24" s="31">
+      <c r="X24" s="32">
         <v>317.38</v>
       </c>
-      <c r="Y24" s="31">
+      <c r="Y24" s="32">
         <v>357.37</v>
       </c>
-      <c r="Z24" s="31">
+      <c r="Z24" s="32">
         <v>942.78</v>
       </c>
-      <c r="AA24" s="31">
+      <c r="AA24" s="32">
         <v>848.99</v>
       </c>
-      <c r="AB24" s="31">
+      <c r="AB24" s="32">
         <v>701.3</v>
       </c>
-      <c r="AC24" s="31">
+      <c r="AC24" s="32">
         <v>414.76</v>
       </c>
-      <c r="AD24" s="31">
+      <c r="AD24" s="32">
         <v>156.5</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="31" t="s">
         <v>371</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="32">
         <v>248.73</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <v>186.77</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <v>145.69</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="32">
         <v>154.15</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="32">
         <v>181.84</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="32">
         <v>167.59</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <v>156.18</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="32">
         <v>144.52</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="32">
         <v>101.36</v>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="33">
         <v>66.75</v>
       </c>
-      <c r="L25" s="32">
+      <c r="L25" s="33">
         <v>51.01</v>
       </c>
-      <c r="M25" s="32">
+      <c r="M25" s="33">
         <v>51.42</v>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="33">
         <v>64.59</v>
       </c>
-      <c r="O25" s="31">
+      <c r="O25" s="32">
         <v>110.74</v>
       </c>
-      <c r="P25" s="31">
+      <c r="P25" s="32">
         <v>204.9</v>
       </c>
-      <c r="Q25" s="31">
+      <c r="Q25" s="32">
         <v>291.44</v>
       </c>
-      <c r="R25" s="31">
+      <c r="R25" s="32">
         <v>466.31</v>
       </c>
-      <c r="S25" s="31">
+      <c r="S25" s="32">
         <v>430.5</v>
       </c>
-      <c r="T25" s="31">
+      <c r="T25" s="32">
         <v>462.59</v>
       </c>
-      <c r="U25" s="31">
+      <c r="U25" s="32">
         <v>418.52</v>
       </c>
-      <c r="V25" s="31">
+      <c r="V25" s="32">
         <v>540.71</v>
       </c>
-      <c r="W25" s="31">
+      <c r="W25" s="32">
         <v>603.8</v>
       </c>
-      <c r="X25" s="31">
+      <c r="X25" s="32">
         <v>564.09</v>
       </c>
-      <c r="Y25" s="31">
+      <c r="Y25" s="32">
         <v>630.25</v>
       </c>
-      <c r="Z25" s="31">
+      <c r="Z25" s="32">
         <v>609.28</v>
       </c>
-      <c r="AA25" s="34"/>
-      <c r="AB25" s="34"/>
-      <c r="AC25" s="34"/>
-      <c r="AD25" s="34"/>
+      <c r="AA25" s="35"/>
+      <c r="AB25" s="35"/>
+      <c r="AC25" s="35"/>
+      <c r="AD25" s="35"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="29" t="s">
         <v>372</v>
       </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="29"/>
-      <c r="AC26" s="29"/>
-      <c r="AD26" s="29"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="31" t="s">
         <v>373</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="32">
         <v>128.14</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <v>97.83</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="33">
         <v>55.88</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="33">
         <v>47.05</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="33">
         <v>44.38</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="33">
         <v>38.28</v>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="33">
         <v>41.32</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="33">
         <v>76.2</v>
       </c>
-      <c r="J27" s="32">
+      <c r="J27" s="33">
         <v>71.59</v>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="33">
         <v>36.48</v>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="33">
         <v>16.75</v>
       </c>
-      <c r="M27" s="32">
+      <c r="M27" s="33">
         <v>19.6</v>
       </c>
-      <c r="N27" s="32">
+      <c r="N27" s="33">
         <v>19.07</v>
       </c>
-      <c r="O27" s="32">
+      <c r="O27" s="33">
         <v>11.46</v>
       </c>
-      <c r="P27" s="32">
+      <c r="P27" s="33">
         <v>17.8</v>
       </c>
-      <c r="Q27" s="32">
+      <c r="Q27" s="33">
         <v>30.77</v>
       </c>
-      <c r="R27" s="32">
+      <c r="R27" s="33">
         <v>87.54</v>
       </c>
-      <c r="S27" s="31">
+      <c r="S27" s="32">
         <v>117.52</v>
       </c>
-      <c r="T27" s="31">
+      <c r="T27" s="32">
         <v>230.53</v>
       </c>
-      <c r="U27" s="31">
+      <c r="U27" s="32">
         <v>172.17</v>
       </c>
-      <c r="V27" s="31">
+      <c r="V27" s="32">
         <v>264.48</v>
       </c>
-      <c r="W27" s="31">
+      <c r="W27" s="32">
         <v>192.56</v>
       </c>
-      <c r="X27" s="31">
+      <c r="X27" s="32">
         <v>139.57</v>
       </c>
-      <c r="Y27" s="31">
+      <c r="Y27" s="32">
         <v>108.57</v>
       </c>
-      <c r="Z27" s="31">
+      <c r="Z27" s="32">
         <v>238.47</v>
       </c>
-      <c r="AA27" s="31">
+      <c r="AA27" s="32">
         <v>192.21</v>
       </c>
-      <c r="AB27" s="31">
+      <c r="AB27" s="32">
         <v>158.77</v>
       </c>
-      <c r="AC27" s="31">
+      <c r="AC27" s="32">
         <v>170.33</v>
       </c>
-      <c r="AD27" s="31">
+      <c r="AD27" s="32">
         <v>152.68</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="33">
         <v>79.69</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <v>60.13</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="33">
         <v>46.9</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="33">
         <v>49.62</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="33">
         <v>58.54</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="33">
         <v>53.95</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="33">
         <v>50.28</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="33">
         <v>46.52</v>
       </c>
-      <c r="J28" s="32">
+      <c r="J28" s="33">
         <v>33.65</v>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="33">
         <v>23.17</v>
       </c>
-      <c r="L28" s="32">
+      <c r="L28" s="33">
         <v>19.12</v>
       </c>
-      <c r="M28" s="32">
+      <c r="M28" s="33">
         <v>20.69</v>
       </c>
-      <c r="N28" s="32">
+      <c r="N28" s="33">
         <v>27.98</v>
       </c>
-      <c r="O28" s="32">
+      <c r="O28" s="33">
         <v>48.54</v>
       </c>
-      <c r="P28" s="32">
+      <c r="P28" s="33">
         <v>90.11</v>
       </c>
-      <c r="Q28" s="31">
+      <c r="Q28" s="32">
         <v>128.16</v>
       </c>
-      <c r="R28" s="31">
+      <c r="R28" s="32">
         <v>205.06</v>
       </c>
-      <c r="S28" s="31">
+      <c r="S28" s="32">
         <v>189.31</v>
       </c>
-      <c r="T28" s="31">
+      <c r="T28" s="32">
         <v>203.43</v>
       </c>
-      <c r="U28" s="31">
+      <c r="U28" s="32">
         <v>174.34</v>
       </c>
-      <c r="V28" s="31">
+      <c r="V28" s="32">
         <v>192.5</v>
       </c>
-      <c r="W28" s="31">
+      <c r="W28" s="32">
         <v>181.86</v>
       </c>
-      <c r="X28" s="31">
+      <c r="X28" s="32">
         <v>150.74</v>
       </c>
-      <c r="Y28" s="31">
+      <c r="Y28" s="32">
         <v>168.29</v>
       </c>
-      <c r="Z28" s="31">
+      <c r="Z28" s="32">
         <v>182.45</v>
       </c>
-      <c r="AA28" s="34"/>
-      <c r="AB28" s="34"/>
-      <c r="AC28" s="34"/>
-      <c r="AD28" s="34"/>
+      <c r="AA28" s="35"/>
+      <c r="AB28" s="35"/>
+      <c r="AC28" s="35"/>
+      <c r="AD28" s="35"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="29" t="s">
         <v>375</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29"/>
-      <c r="Y29" s="29"/>
-      <c r="Z29" s="29"/>
-      <c r="AA29" s="29"/>
-      <c r="AB29" s="29"/>
-      <c r="AC29" s="29"/>
-      <c r="AD29" s="29"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="31" t="s">
         <v>376</v>
       </c>
-      <c r="B30" s="35">
+      <c r="B30" s="36">
         <v>-14.66</v>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="37">
         <v>0.48</v>
       </c>
-      <c r="D30" s="36">
+      <c r="D30" s="37">
         <v>14.6</v>
       </c>
-      <c r="E30" s="36">
+      <c r="E30" s="37">
         <v>21.17</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="36">
         <v>-3.89</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="37">
         <v>13.76</v>
       </c>
-      <c r="H30" s="36">
+      <c r="H30" s="37">
         <v>5.59</v>
       </c>
-      <c r="I30" s="35">
+      <c r="I30" s="36">
         <v>-9.32</v>
       </c>
-      <c r="J30" s="36">
+      <c r="J30" s="37">
         <v>6.09</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="37">
         <v>25.89</v>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="36">
         <v>-63.25</v>
       </c>
-      <c r="M30" s="35">
+      <c r="M30" s="36">
         <v>-34.61</v>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="37">
         <v>26.94</v>
       </c>
-      <c r="O30" s="36">
+      <c r="O30" s="37">
         <v>15.78</v>
       </c>
-      <c r="P30" s="36">
+      <c r="P30" s="37">
         <v>91.78</v>
       </c>
-      <c r="Q30" s="35">
+      <c r="Q30" s="36">
         <v>-133.78</v>
       </c>
-      <c r="R30" s="35">
+      <c r="R30" s="36">
         <v>-34.54</v>
       </c>
-      <c r="S30" s="36">
+      <c r="S30" s="37">
         <v>6.41</v>
       </c>
-      <c r="T30" s="36">
+      <c r="T30" s="37">
         <v>0.55</v>
       </c>
-      <c r="U30" s="36">
+      <c r="U30" s="37">
         <v>18.02</v>
       </c>
-      <c r="V30" s="36">
+      <c r="V30" s="37">
         <v>15.04</v>
       </c>
-      <c r="W30" s="36">
+      <c r="W30" s="37">
         <v>25.35</v>
       </c>
-      <c r="X30" s="36">
+      <c r="X30" s="37">
         <v>45.83</v>
       </c>
-      <c r="Y30" s="36">
+      <c r="Y30" s="37">
         <v>7.58</v>
       </c>
-      <c r="Z30" s="35">
+      <c r="Z30" s="36">
         <v>-12.91</v>
       </c>
-      <c r="AA30" s="35">
+      <c r="AA30" s="36">
         <v>-7.69</v>
       </c>
-      <c r="AB30" s="36">
+      <c r="AB30" s="37">
         <v>13.72</v>
       </c>
-      <c r="AC30" s="36">
+      <c r="AC30" s="37">
         <v>9.56</v>
       </c>
-      <c r="AD30" s="36">
+      <c r="AD30" s="37">
         <v>3.26</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="31" t="s">
         <v>377</v>
       </c>
-      <c r="B31" s="36">
+      <c r="B31" s="37">
         <v>0.14</v>
       </c>
-      <c r="C31" s="36">
+      <c r="C31" s="37">
         <v>8.12</v>
       </c>
-      <c r="D31" s="36">
+      <c r="D31" s="37">
         <v>10.64</v>
       </c>
-      <c r="E31" s="36">
+      <c r="E31" s="37">
         <v>3.55</v>
       </c>
-      <c r="F31" s="36">
+      <c r="F31" s="37">
         <v>1.31</v>
       </c>
-      <c r="G31" s="36">
+      <c r="G31" s="37">
         <v>5.51</v>
       </c>
-      <c r="H31" s="35">
+      <c r="H31" s="36">
         <v>-0.76</v>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="36">
         <v>-5.26</v>
       </c>
-      <c r="J31" s="36">
+      <c r="J31" s="37">
         <v>0.97</v>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="36">
         <v>-0.55</v>
       </c>
-      <c r="L31" s="36">
+      <c r="L31" s="37">
         <v>9.89</v>
       </c>
-      <c r="M31" s="35">
+      <c r="M31" s="36">
         <v>-22.05</v>
       </c>
-      <c r="N31" s="35">
+      <c r="N31" s="36">
         <v>-26.4</v>
       </c>
-      <c r="O31" s="35">
+      <c r="O31" s="36">
         <v>-15.28</v>
       </c>
-      <c r="P31" s="35">
+      <c r="P31" s="36">
         <v>-8.41</v>
       </c>
-      <c r="Q31" s="35">
+      <c r="Q31" s="36">
         <v>-3.98</v>
       </c>
-      <c r="R31" s="36">
+      <c r="R31" s="37">
         <v>6.35</v>
       </c>
-      <c r="S31" s="36">
+      <c r="S31" s="37">
         <v>13.09</v>
       </c>
-      <c r="T31" s="36">
+      <c r="T31" s="37">
         <v>18.95</v>
       </c>
-      <c r="U31" s="36">
+      <c r="U31" s="37">
         <v>22.25</v>
       </c>
-      <c r="V31" s="36">
+      <c r="V31" s="37">
         <v>14.32</v>
       </c>
-      <c r="W31" s="36">
+      <c r="W31" s="37">
         <v>9.28</v>
       </c>
-      <c r="X31" s="36">
+      <c r="X31" s="37">
         <v>6.47</v>
       </c>
-      <c r="Y31" s="35">
+      <c r="Y31" s="36">
         <v>-0.05</v>
       </c>
-      <c r="Z31" s="35">
+      <c r="Z31" s="36">
         <v>-0.42</v>
       </c>
-      <c r="AA31" s="36"/>
-      <c r="AB31" s="36"/>
-      <c r="AC31" s="36"/>
-      <c r="AD31" s="36"/>
+      <c r="AA31" s="37"/>
+      <c r="AB31" s="37"/>
+      <c r="AC31" s="37"/>
+      <c r="AD31" s="37"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="29" t="s">
         <v>378</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="29"/>
-      <c r="Z32" s="29"/>
-      <c r="AA32" s="29"/>
-      <c r="AB32" s="29"/>
-      <c r="AC32" s="29"/>
-      <c r="AD32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="31" t="s">
         <v>379</v>
       </c>
-      <c r="B33" s="36">
+      <c r="B33" s="37">
         <v>6.16</v>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="37">
         <v>7.67</v>
       </c>
-      <c r="D33" s="36">
+      <c r="D33" s="37">
         <v>10.09</v>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="37">
         <v>8.59</v>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="37">
         <v>6.34</v>
       </c>
-      <c r="G33" s="36">
+      <c r="G33" s="37">
         <v>0.0</v>
       </c>
-      <c r="H33" s="36">
+      <c r="H33" s="37">
         <v>0.0</v>
       </c>
-      <c r="I33" s="36">
+      <c r="I33" s="37">
         <v>0.0</v>
       </c>
-      <c r="J33" s="36">
+      <c r="J33" s="37">
         <v>0.0</v>
       </c>
-      <c r="K33" s="36">
+      <c r="K33" s="37">
         <v>0.0</v>
       </c>
-      <c r="L33" s="36">
+      <c r="L33" s="37">
         <v>0.0</v>
       </c>
-      <c r="M33" s="36">
+      <c r="M33" s="37">
         <v>0.0</v>
       </c>
-      <c r="N33" s="36">
+      <c r="N33" s="37">
         <v>0.0</v>
       </c>
-      <c r="O33" s="36">
+      <c r="O33" s="37">
         <v>0.0</v>
       </c>
-      <c r="P33" s="36">
+      <c r="P33" s="37">
         <v>0.0</v>
       </c>
-      <c r="Q33" s="36">
+      <c r="Q33" s="37">
         <v>0.0</v>
       </c>
-      <c r="R33" s="36">
+      <c r="R33" s="37">
         <v>8.05</v>
       </c>
-      <c r="S33" s="36">
+      <c r="S33" s="37">
         <v>13.04</v>
       </c>
-      <c r="T33" s="36">
+      <c r="T33" s="37">
         <v>86.17</v>
       </c>
-      <c r="U33" s="36">
+      <c r="U33" s="37">
         <v>64.93</v>
       </c>
-      <c r="V33" s="36">
+      <c r="V33" s="37">
         <v>12.07</v>
       </c>
-      <c r="W33" s="36">
+      <c r="W33" s="37">
         <v>2.7</v>
       </c>
-      <c r="X33" s="36">
+      <c r="X33" s="37">
         <v>3.24</v>
       </c>
-      <c r="Y33" s="36">
+      <c r="Y33" s="37">
         <v>4.55</v>
       </c>
-      <c r="Z33" s="36">
+      <c r="Z33" s="37">
         <v>2.23</v>
       </c>
-      <c r="AA33" s="36">
+      <c r="AA33" s="37">
         <v>1.35</v>
       </c>
-      <c r="AB33" s="36">
+      <c r="AB33" s="37">
         <v>1.58</v>
       </c>
-      <c r="AC33" s="36">
+      <c r="AC33" s="37">
         <v>1.14</v>
       </c>
-      <c r="AD33" s="36">
+      <c r="AD33" s="37">
         <v>1.07</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="31" t="s">
         <v>380</v>
       </c>
-      <c r="B34" s="36">
+      <c r="B34" s="37">
         <v>7.53</v>
       </c>
-      <c r="C34" s="36">
+      <c r="C34" s="37">
         <v>6.99</v>
       </c>
-      <c r="D34" s="36">
+      <c r="D34" s="37">
         <v>5.41</v>
       </c>
-      <c r="E34" s="36">
+      <c r="E34" s="37">
         <v>2.71</v>
       </c>
-      <c r="F34" s="36">
+      <c r="F34" s="37">
         <v>0.96</v>
       </c>
-      <c r="G34" s="36">
+      <c r="G34" s="37">
         <v>0.0</v>
       </c>
-      <c r="H34" s="36">
+      <c r="H34" s="37">
         <v>0.0</v>
       </c>
-      <c r="I34" s="36">
+      <c r="I34" s="37">
         <v>0.0</v>
       </c>
-      <c r="J34" s="36">
+      <c r="J34" s="37">
         <v>0.0</v>
       </c>
-      <c r="K34" s="36">
+      <c r="K34" s="37">
         <v>0.0</v>
       </c>
-      <c r="L34" s="36">
+      <c r="L34" s="37">
         <v>0.0</v>
       </c>
-      <c r="M34" s="36">
+      <c r="M34" s="37">
         <v>0.0</v>
       </c>
-      <c r="N34" s="36">
+      <c r="N34" s="37">
         <v>3.8</v>
       </c>
-      <c r="O34" s="36">
+      <c r="O34" s="37">
         <v>8.49</v>
       </c>
-      <c r="P34" s="36">
+      <c r="P34" s="37">
         <v>46.35</v>
       </c>
-      <c r="Q34" s="36">
+      <c r="Q34" s="37">
         <v>52.92</v>
       </c>
-      <c r="R34" s="36">
+      <c r="R34" s="37">
         <v>42.37</v>
       </c>
-      <c r="S34" s="36">
+      <c r="S34" s="37">
         <v>37.34</v>
       </c>
-      <c r="T34" s="36">
+      <c r="T34" s="37">
         <v>34.98</v>
       </c>
-      <c r="U34" s="36">
+      <c r="U34" s="37">
         <v>18.06</v>
       </c>
-      <c r="V34" s="36">
+      <c r="V34" s="37">
         <v>5.46</v>
       </c>
-      <c r="W34" s="36">
+      <c r="W34" s="37">
         <v>2.6</v>
       </c>
-      <c r="X34" s="36">
+      <c r="X34" s="37">
         <v>2.41</v>
       </c>
-      <c r="Y34" s="36">
+      <c r="Y34" s="37">
         <v>2.0</v>
       </c>
-      <c r="Z34" s="36">
+      <c r="Z34" s="37">
         <v>1.53</v>
       </c>
-      <c r="AA34" s="36"/>
-      <c r="AB34" s="36"/>
-      <c r="AC34" s="36"/>
-      <c r="AD34" s="36"/>
+      <c r="AA34" s="37"/>
+      <c r="AB34" s="37"/>
+      <c r="AC34" s="37"/>
+      <c r="AD34" s="37"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="30" t="s">
+      <c r="A35" s="31" t="s">
         <v>381</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="37">
         <v>6.16</v>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="37">
         <v>7.67</v>
       </c>
-      <c r="D35" s="36">
+      <c r="D35" s="37">
         <v>10.09</v>
       </c>
-      <c r="E35" s="36">
+      <c r="E35" s="37">
         <v>8.59</v>
       </c>
-      <c r="F35" s="36">
+      <c r="F35" s="37">
         <v>6.34</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <v>0.0</v>
       </c>
-      <c r="H35" s="36">
+      <c r="H35" s="37">
         <v>0.0</v>
       </c>
-      <c r="I35" s="36">
+      <c r="I35" s="37">
         <v>0.0</v>
       </c>
-      <c r="J35" s="36">
+      <c r="J35" s="37">
         <v>0.0</v>
       </c>
-      <c r="K35" s="36">
+      <c r="K35" s="37">
         <v>0.0</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <v>0.0</v>
       </c>
-      <c r="M35" s="36">
+      <c r="M35" s="37">
         <v>0.0</v>
       </c>
-      <c r="N35" s="36">
+      <c r="N35" s="37">
         <v>0.0</v>
       </c>
-      <c r="O35" s="36">
+      <c r="O35" s="37">
         <v>0.0</v>
       </c>
-      <c r="P35" s="36">
+      <c r="P35" s="37">
         <v>0.0</v>
       </c>
-      <c r="Q35" s="36">
+      <c r="Q35" s="37">
         <v>0.0</v>
       </c>
-      <c r="R35" s="36">
+      <c r="R35" s="37">
         <v>11.18</v>
       </c>
-      <c r="S35" s="36">
+      <c r="S35" s="37">
         <v>18.11</v>
       </c>
-      <c r="T35" s="36">
+      <c r="T35" s="37">
         <v>119.68</v>
       </c>
-      <c r="U35" s="36">
+      <c r="U35" s="37">
         <v>90.19</v>
       </c>
-      <c r="V35" s="36">
+      <c r="V35" s="37">
         <v>16.76</v>
       </c>
-      <c r="W35" s="36">
+      <c r="W35" s="37">
         <v>3.74</v>
       </c>
-      <c r="X35" s="36">
+      <c r="X35" s="37">
         <v>4.49</v>
       </c>
-      <c r="Y35" s="36">
+      <c r="Y35" s="37">
         <v>6.32</v>
       </c>
-      <c r="Z35" s="36">
+      <c r="Z35" s="37">
         <v>2.97</v>
       </c>
-      <c r="AA35" s="36">
+      <c r="AA35" s="37">
         <v>1.81</v>
       </c>
-      <c r="AB35" s="36">
+      <c r="AB35" s="37">
         <v>2.11</v>
       </c>
-      <c r="AC35" s="36">
+      <c r="AC35" s="37">
         <v>1.52</v>
       </c>
-      <c r="AD35" s="36">
+      <c r="AD35" s="37">
         <v>1.43</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="31" t="s">
         <v>382</v>
       </c>
-      <c r="B36" s="36">
+      <c r="B36" s="37">
         <v>7.53</v>
       </c>
-      <c r="C36" s="36">
+      <c r="C36" s="37">
         <v>6.99</v>
       </c>
-      <c r="D36" s="36">
+      <c r="D36" s="37">
         <v>5.41</v>
       </c>
-      <c r="E36" s="36">
+      <c r="E36" s="37">
         <v>2.71</v>
       </c>
-      <c r="F36" s="36">
+      <c r="F36" s="37">
         <v>0.96</v>
       </c>
-      <c r="G36" s="36">
+      <c r="G36" s="37">
         <v>0.0</v>
       </c>
-      <c r="H36" s="36">
+      <c r="H36" s="37">
         <v>0.0</v>
       </c>
-      <c r="I36" s="36">
+      <c r="I36" s="37">
         <v>0.0</v>
       </c>
-      <c r="J36" s="36">
+      <c r="J36" s="37">
         <v>0.0</v>
       </c>
-      <c r="K36" s="36">
+      <c r="K36" s="37">
         <v>0.0</v>
       </c>
-      <c r="L36" s="36">
+      <c r="L36" s="37">
         <v>0.0</v>
       </c>
-      <c r="M36" s="36">
+      <c r="M36" s="37">
         <v>0.0</v>
       </c>
-      <c r="N36" s="36">
+      <c r="N36" s="37">
         <v>5.28</v>
       </c>
-      <c r="O36" s="36">
+      <c r="O36" s="37">
         <v>11.79</v>
       </c>
-      <c r="P36" s="36">
+      <c r="P36" s="37">
         <v>64.38</v>
       </c>
-      <c r="Q36" s="36">
+      <c r="Q36" s="37">
         <v>73.5</v>
       </c>
-      <c r="R36" s="36">
+      <c r="R36" s="37">
         <v>58.85</v>
       </c>
-      <c r="S36" s="36">
+      <c r="S36" s="37">
         <v>51.86</v>
       </c>
-      <c r="T36" s="36">
+      <c r="T36" s="37">
         <v>48.59</v>
       </c>
-      <c r="U36" s="36">
+      <c r="U36" s="37">
         <v>25.09</v>
       </c>
-      <c r="V36" s="36">
+      <c r="V36" s="37">
         <v>7.55</v>
       </c>
-      <c r="W36" s="36">
+      <c r="W36" s="37">
         <v>3.57</v>
       </c>
-      <c r="X36" s="36">
+      <c r="X36" s="37">
         <v>3.28</v>
       </c>
-      <c r="Y36" s="36">
+      <c r="Y36" s="37">
         <v>2.7</v>
       </c>
-      <c r="Z36" s="36">
+      <c r="Z36" s="37">
         <v>2.04</v>
       </c>
-      <c r="AA36" s="36"/>
-      <c r="AB36" s="36"/>
-      <c r="AC36" s="36"/>
-      <c r="AD36" s="36"/>
+      <c r="AA36" s="37"/>
+      <c r="AB36" s="37"/>
+      <c r="AC36" s="37"/>
+      <c r="AD36" s="37"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="29" t="s">
         <v>383</v>
       </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29"/>
-      <c r="Y37" s="29"/>
-      <c r="Z37" s="29"/>
-      <c r="AA37" s="29"/>
-      <c r="AB37" s="29"/>
-      <c r="AC37" s="29"/>
-      <c r="AD37" s="29"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
+      <c r="AA37" s="30"/>
+      <c r="AB37" s="30"/>
+      <c r="AC37" s="30"/>
+      <c r="AD37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="30" t="s">
+      <c r="A38" s="31" t="s">
         <v>384</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="33">
         <v>2.91</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="33">
         <v>0.93</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="33">
         <v>0.84</v>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="33">
         <v>0.81</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="33">
         <v>0.76</v>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="33">
         <v>0.72</v>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="33">
         <v>0.88</v>
       </c>
-      <c r="I38" s="32">
+      <c r="I38" s="33">
         <v>1.85</v>
       </c>
-      <c r="J38" s="32">
+      <c r="J38" s="33">
         <v>1.76</v>
       </c>
-      <c r="K38" s="32">
+      <c r="K38" s="33">
         <v>1.03</v>
       </c>
-      <c r="L38" s="32">
+      <c r="L38" s="33">
         <v>0.6</v>
       </c>
-      <c r="M38" s="32">
+      <c r="M38" s="33">
         <v>0.54</v>
       </c>
-      <c r="N38" s="32">
+      <c r="N38" s="33">
         <v>0.63</v>
       </c>
-      <c r="O38" s="32">
+      <c r="O38" s="33">
         <v>0.41</v>
       </c>
-      <c r="P38" s="32">
+      <c r="P38" s="33">
         <v>0.4</v>
       </c>
-      <c r="Q38" s="32">
+      <c r="Q38" s="33">
         <v>0.4</v>
       </c>
-      <c r="R38" s="32">
+      <c r="R38" s="33">
         <v>0.69</v>
       </c>
-      <c r="S38" s="32">
+      <c r="S38" s="33">
         <v>0.99</v>
       </c>
-      <c r="T38" s="32">
+      <c r="T38" s="33">
         <v>1.55</v>
       </c>
-      <c r="U38" s="32">
+      <c r="U38" s="33">
         <v>0.6</v>
       </c>
-      <c r="V38" s="32">
+      <c r="V38" s="33">
         <v>0.63</v>
       </c>
-      <c r="W38" s="32">
+      <c r="W38" s="33">
         <v>0.49</v>
       </c>
-      <c r="X38" s="32">
+      <c r="X38" s="33">
         <v>0.41</v>
       </c>
-      <c r="Y38" s="34"/>
-      <c r="Z38" s="34"/>
-      <c r="AA38" s="34"/>
-      <c r="AB38" s="34"/>
-      <c r="AC38" s="34"/>
-      <c r="AD38" s="34"/>
+      <c r="Y38" s="35"/>
+      <c r="Z38" s="35"/>
+      <c r="AA38" s="35"/>
+      <c r="AB38" s="35"/>
+      <c r="AC38" s="35"/>
+      <c r="AD38" s="35"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="31" t="s">
         <v>385</v>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="33">
         <v>1.1</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="33">
         <v>0.83</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="33">
         <v>0.8</v>
       </c>
-      <c r="E39" s="32">
+      <c r="E39" s="33">
         <v>0.96</v>
       </c>
-      <c r="F39" s="32">
+      <c r="F39" s="33">
         <v>1.15</v>
       </c>
-      <c r="G39" s="32">
+      <c r="G39" s="33">
         <v>1.22</v>
       </c>
-      <c r="H39" s="32">
+      <c r="H39" s="33">
         <v>1.26</v>
       </c>
-      <c r="I39" s="32">
+      <c r="I39" s="33">
         <v>1.2</v>
       </c>
-      <c r="J39" s="32">
+      <c r="J39" s="33">
         <v>0.94</v>
       </c>
-      <c r="K39" s="32">
+      <c r="K39" s="33">
         <v>0.64</v>
       </c>
-      <c r="L39" s="32">
+      <c r="L39" s="33">
         <v>0.51</v>
       </c>
-      <c r="M39" s="32">
+      <c r="M39" s="33">
         <v>0.46</v>
       </c>
-      <c r="N39" s="32">
+      <c r="N39" s="33">
         <v>0.54</v>
       </c>
-      <c r="O39" s="32">
+      <c r="O39" s="33">
         <v>0.67</v>
       </c>
-      <c r="P39" s="32">
+      <c r="P39" s="33">
         <v>0.95</v>
       </c>
-      <c r="Q39" s="32">
+      <c r="Q39" s="33">
         <v>0.84</v>
       </c>
-      <c r="R39" s="32">
+      <c r="R39" s="33">
         <v>0.79</v>
       </c>
-      <c r="S39" s="32">
+      <c r="S39" s="33">
         <v>0.71</v>
       </c>
-      <c r="T39" s="32">
+      <c r="T39" s="33">
         <v>0.62</v>
       </c>
-      <c r="U39" s="34"/>
-      <c r="V39" s="34"/>
-      <c r="W39" s="34"/>
-      <c r="X39" s="34"/>
-      <c r="Y39" s="34"/>
-      <c r="Z39" s="34"/>
-      <c r="AA39" s="34"/>
-      <c r="AB39" s="34"/>
-      <c r="AC39" s="34"/>
-      <c r="AD39" s="34"/>
+      <c r="U39" s="35"/>
+      <c r="V39" s="35"/>
+      <c r="W39" s="35"/>
+      <c r="X39" s="35"/>
+      <c r="Y39" s="35"/>
+      <c r="Z39" s="35"/>
+      <c r="AA39" s="35"/>
+      <c r="AB39" s="35"/>
+      <c r="AC39" s="35"/>
+      <c r="AD39" s="35"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="29" t="s">
         <v>386</v>
       </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29"/>
-      <c r="AA40" s="29"/>
-      <c r="AB40" s="29"/>
-      <c r="AC40" s="29"/>
-      <c r="AD40" s="29"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="30"/>
+      <c r="AA40" s="30"/>
+      <c r="AB40" s="30"/>
+      <c r="AC40" s="30"/>
+      <c r="AD40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="30" t="s">
+      <c r="A41" s="31" t="s">
         <v>387</v>
       </c>
-      <c r="B41" s="32">
+      <c r="B41" s="33">
         <v>4.13</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="33">
         <v>1.07</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="33">
         <v>1.16</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="33">
         <v>1.2</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="33">
         <v>1.13</v>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="33">
         <v>1.09</v>
       </c>
-      <c r="H41" s="32">
+      <c r="H41" s="33">
         <v>0.95</v>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="33">
         <v>2.02</v>
       </c>
-      <c r="J41" s="32">
+      <c r="J41" s="33">
         <v>1.87</v>
       </c>
-      <c r="K41" s="32">
+      <c r="K41" s="33">
         <v>1.05</v>
       </c>
-      <c r="L41" s="32">
+      <c r="L41" s="33">
         <v>0.61</v>
       </c>
-      <c r="M41" s="32">
+      <c r="M41" s="33">
         <v>0.56</v>
       </c>
-      <c r="N41" s="32">
+      <c r="N41" s="33">
         <v>0.65</v>
       </c>
-      <c r="O41" s="32">
+      <c r="O41" s="33">
         <v>0.41</v>
       </c>
-      <c r="P41" s="32">
+      <c r="P41" s="33">
         <v>0.41</v>
       </c>
-      <c r="Q41" s="32">
+      <c r="Q41" s="33">
         <v>0.41</v>
       </c>
-      <c r="R41" s="32">
+      <c r="R41" s="33">
         <v>0.7</v>
       </c>
-      <c r="S41" s="32">
+      <c r="S41" s="33">
         <v>0.99</v>
       </c>
-      <c r="T41" s="32">
+      <c r="T41" s="33">
         <v>1.56</v>
       </c>
-      <c r="U41" s="32">
+      <c r="U41" s="33">
         <v>0.6</v>
       </c>
-      <c r="V41" s="32">
+      <c r="V41" s="33">
         <v>0.63</v>
       </c>
-      <c r="W41" s="32">
+      <c r="W41" s="33">
         <v>0.49</v>
       </c>
-      <c r="X41" s="32">
+      <c r="X41" s="33">
         <v>0.42</v>
       </c>
-      <c r="Y41" s="32">
+      <c r="Y41" s="33">
         <v>1.34</v>
       </c>
-      <c r="Z41" s="32">
+      <c r="Z41" s="33">
         <v>1.64</v>
       </c>
-      <c r="AA41" s="32">
+      <c r="AA41" s="33">
         <v>1.59</v>
       </c>
-      <c r="AB41" s="32">
+      <c r="AB41" s="33">
         <v>2.68</v>
       </c>
-      <c r="AC41" s="32">
+      <c r="AC41" s="33">
         <v>1.66</v>
       </c>
-      <c r="AD41" s="32">
+      <c r="AD41" s="33">
         <v>4.05</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="31" t="s">
         <v>388</v>
       </c>
-      <c r="B42" s="32">
+      <c r="B42" s="33">
         <v>1.47</v>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="33">
         <v>1.12</v>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="33">
         <v>1.1</v>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="33">
         <v>1.27</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="33">
         <v>1.41</v>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="33">
         <v>1.4</v>
       </c>
-      <c r="H42" s="32">
+      <c r="H42" s="33">
         <v>1.33</v>
       </c>
-      <c r="I42" s="32">
+      <c r="I42" s="33">
         <v>1.25</v>
       </c>
-      <c r="J42" s="32">
+      <c r="J42" s="33">
         <v>0.97</v>
       </c>
-      <c r="K42" s="32">
+      <c r="K42" s="33">
         <v>0.66</v>
       </c>
-      <c r="L42" s="32">
+      <c r="L42" s="33">
         <v>0.52</v>
       </c>
-      <c r="M42" s="32">
+      <c r="M42" s="33">
         <v>0.47</v>
       </c>
-      <c r="N42" s="32">
+      <c r="N42" s="33">
         <v>0.54</v>
       </c>
-      <c r="O42" s="32">
+      <c r="O42" s="33">
         <v>0.68</v>
       </c>
-      <c r="P42" s="32">
+      <c r="P42" s="33">
         <v>0.96</v>
       </c>
-      <c r="Q42" s="32">
+      <c r="Q42" s="33">
         <v>0.85</v>
       </c>
-      <c r="R42" s="32">
+      <c r="R42" s="33">
         <v>0.8</v>
       </c>
-      <c r="S42" s="32">
+      <c r="S42" s="33">
         <v>0.72</v>
       </c>
-      <c r="T42" s="32">
+      <c r="T42" s="33">
         <v>0.63</v>
       </c>
-      <c r="U42" s="32">
+      <c r="U42" s="33">
         <v>0.58</v>
       </c>
-      <c r="V42" s="32">
+      <c r="V42" s="33">
         <v>0.68</v>
       </c>
-      <c r="W42" s="32">
+      <c r="W42" s="33">
         <v>0.8</v>
       </c>
-      <c r="X42" s="32">
+      <c r="X42" s="33">
         <v>1.09</v>
       </c>
-      <c r="Y42" s="32">
+      <c r="Y42" s="33">
         <v>1.69</v>
       </c>
-      <c r="Z42" s="32">
+      <c r="Z42" s="33">
         <v>1.95</v>
       </c>
-      <c r="AA42" s="34"/>
-      <c r="AB42" s="34"/>
-      <c r="AC42" s="34"/>
-      <c r="AD42" s="34"/>
+      <c r="AA42" s="35"/>
+      <c r="AB42" s="35"/>
+      <c r="AC42" s="35"/>
+      <c r="AD42" s="35"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="29" t="s">
         <v>389</v>
       </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
-      <c r="X43" s="29"/>
-      <c r="Y43" s="29"/>
-      <c r="Z43" s="29"/>
-      <c r="AA43" s="29"/>
-      <c r="AB43" s="29"/>
-      <c r="AC43" s="29"/>
-      <c r="AD43" s="29"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="30"/>
+      <c r="Y43" s="30"/>
+      <c r="Z43" s="30"/>
+      <c r="AA43" s="30"/>
+      <c r="AB43" s="30"/>
+      <c r="AC43" s="30"/>
+      <c r="AD43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="30" t="s">
+      <c r="A44" s="31" t="s">
         <v>390</v>
       </c>
-      <c r="B44" s="32">
+      <c r="B44" s="33">
         <v>1.08</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <v>0.84</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="33">
         <v>0.53</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="33">
         <v>0.3</v>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="33">
         <v>0.29</v>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="33">
         <v>0.25</v>
       </c>
-      <c r="H44" s="32">
+      <c r="H44" s="33">
         <v>0.28</v>
       </c>
-      <c r="I44" s="32">
+      <c r="I44" s="33">
         <v>0.51</v>
       </c>
-      <c r="J44" s="32">
+      <c r="J44" s="33">
         <v>0.59</v>
       </c>
-      <c r="K44" s="32">
+      <c r="K44" s="33">
         <v>0.27</v>
       </c>
-      <c r="L44" s="32">
+      <c r="L44" s="33">
         <v>0.12</v>
       </c>
-      <c r="M44" s="32">
+      <c r="M44" s="33">
         <v>0.13</v>
       </c>
-      <c r="N44" s="32">
+      <c r="N44" s="33">
         <v>0.17</v>
       </c>
-      <c r="O44" s="32">
+      <c r="O44" s="33">
         <v>0.07</v>
       </c>
-      <c r="P44" s="32">
+      <c r="P44" s="33">
         <v>0.12</v>
       </c>
-      <c r="Q44" s="32">
+      <c r="Q44" s="33">
         <v>0.15</v>
       </c>
-      <c r="R44" s="32">
+      <c r="R44" s="33">
         <v>0.21</v>
       </c>
-      <c r="S44" s="32">
+      <c r="S44" s="33">
         <v>0.4</v>
       </c>
-      <c r="T44" s="32">
+      <c r="T44" s="33">
         <v>0.86</v>
       </c>
-      <c r="U44" s="32">
+      <c r="U44" s="33">
         <v>0.71</v>
       </c>
-      <c r="V44" s="32">
+      <c r="V44" s="33">
         <v>1.24</v>
       </c>
-      <c r="W44" s="32">
+      <c r="W44" s="33">
         <v>0.22</v>
       </c>
-      <c r="X44" s="32">
+      <c r="X44" s="33">
         <v>0.14</v>
       </c>
-      <c r="Y44" s="32">
+      <c r="Y44" s="33">
         <v>0.4</v>
       </c>
-      <c r="Z44" s="32">
+      <c r="Z44" s="33">
         <v>0.3</v>
       </c>
-      <c r="AA44" s="32">
+      <c r="AA44" s="33">
         <v>0.34</v>
       </c>
-      <c r="AB44" s="32">
+      <c r="AB44" s="33">
         <v>0.52</v>
       </c>
-      <c r="AC44" s="32">
+      <c r="AC44" s="33">
         <v>0.76</v>
       </c>
-      <c r="AD44" s="32">
+      <c r="AD44" s="33">
         <v>1.5</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="30" t="s">
+      <c r="A45" s="31" t="s">
         <v>391</v>
       </c>
-      <c r="B45" s="32">
+      <c r="B45" s="33">
         <v>0.56</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="33">
         <v>0.41</v>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="33">
         <v>0.32</v>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="33">
         <v>0.33</v>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="33">
         <v>0.38</v>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="33">
         <v>0.38</v>
       </c>
-      <c r="H45" s="32">
+      <c r="H45" s="33">
         <v>0.35</v>
       </c>
-      <c r="I45" s="32">
+      <c r="I45" s="33">
         <v>0.31</v>
       </c>
-      <c r="J45" s="32">
+      <c r="J45" s="33">
         <v>0.24</v>
       </c>
-      <c r="K45" s="32">
+      <c r="K45" s="33">
         <v>0.15</v>
       </c>
-      <c r="L45" s="32">
+      <c r="L45" s="33">
         <v>0.12</v>
       </c>
-      <c r="M45" s="32">
+      <c r="M45" s="33">
         <v>0.13</v>
       </c>
-      <c r="N45" s="32">
+      <c r="N45" s="33">
         <v>0.16</v>
       </c>
-      <c r="O45" s="32">
+      <c r="O45" s="33">
         <v>0.22</v>
       </c>
-      <c r="P45" s="32">
+      <c r="P45" s="33">
         <v>0.37</v>
       </c>
-      <c r="Q45" s="32">
+      <c r="Q45" s="33">
         <v>0.46</v>
       </c>
-      <c r="R45" s="32">
+      <c r="R45" s="33">
         <v>0.62</v>
       </c>
-      <c r="S45" s="32">
+      <c r="S45" s="33">
         <v>0.52</v>
       </c>
-      <c r="T45" s="32">
+      <c r="T45" s="33">
         <v>0.38</v>
       </c>
-      <c r="U45" s="32">
+      <c r="U45" s="33">
         <v>0.33</v>
       </c>
-      <c r="V45" s="32">
+      <c r="V45" s="33">
         <v>0.3</v>
       </c>
-      <c r="W45" s="32">
+      <c r="W45" s="33">
         <v>0.25</v>
       </c>
-      <c r="X45" s="32">
+      <c r="X45" s="33">
         <v>0.28</v>
       </c>
-      <c r="Y45" s="32">
+      <c r="Y45" s="33">
         <v>0.4</v>
       </c>
-      <c r="Z45" s="32">
+      <c r="Z45" s="33">
         <v>0.46</v>
       </c>
-      <c r="AA45" s="34"/>
-      <c r="AB45" s="34"/>
-      <c r="AC45" s="34"/>
-      <c r="AD45" s="34"/>
+      <c r="AA45" s="35"/>
+      <c r="AB45" s="35"/>
+      <c r="AC45" s="35"/>
+      <c r="AD45" s="35"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
+      <c r="A46" s="29" t="s">
         <v>392</v>
       </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="29"/>
-      <c r="Y46" s="29"/>
-      <c r="Z46" s="29"/>
-      <c r="AA46" s="29"/>
-      <c r="AB46" s="29"/>
-      <c r="AC46" s="29"/>
-      <c r="AD46" s="29"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
+      <c r="AA46" s="30"/>
+      <c r="AB46" s="30"/>
+      <c r="AC46" s="30"/>
+      <c r="AD46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="31" t="s">
         <v>393</v>
       </c>
-      <c r="B47" s="34"/>
-      <c r="C47" s="31">
+      <c r="B47" s="35"/>
+      <c r="C47" s="32">
         <v>209.27</v>
       </c>
-      <c r="D47" s="32">
+      <c r="D47" s="33">
         <v>6.85</v>
       </c>
-      <c r="E47" s="32">
+      <c r="E47" s="33">
         <v>4.72</v>
       </c>
-      <c r="F47" s="34"/>
-      <c r="G47" s="32">
+      <c r="F47" s="35"/>
+      <c r="G47" s="33">
         <v>7.26</v>
       </c>
-      <c r="H47" s="32">
+      <c r="H47" s="33">
         <v>17.88</v>
       </c>
-      <c r="I47" s="34"/>
-      <c r="J47" s="32">
+      <c r="I47" s="35"/>
+      <c r="J47" s="33">
         <v>16.41</v>
       </c>
-      <c r="K47" s="32">
+      <c r="K47" s="33">
         <v>3.86</v>
       </c>
-      <c r="L47" s="34"/>
-      <c r="M47" s="34"/>
-      <c r="N47" s="32">
+      <c r="L47" s="35"/>
+      <c r="M47" s="35"/>
+      <c r="N47" s="33">
         <v>3.71</v>
       </c>
-      <c r="O47" s="32">
+      <c r="O47" s="33">
         <v>6.34</v>
       </c>
-      <c r="P47" s="32">
+      <c r="P47" s="33">
         <v>1.09</v>
       </c>
-      <c r="Q47" s="34"/>
-      <c r="R47" s="34"/>
-      <c r="S47" s="32">
+      <c r="Q47" s="35"/>
+      <c r="R47" s="35"/>
+      <c r="S47" s="33">
         <v>15.59</v>
       </c>
-      <c r="T47" s="31">
+      <c r="T47" s="32">
         <v>183.12</v>
       </c>
-      <c r="U47" s="32">
+      <c r="U47" s="33">
         <v>5.55</v>
       </c>
-      <c r="V47" s="32">
+      <c r="V47" s="33">
         <v>6.65</v>
       </c>
-      <c r="W47" s="32">
+      <c r="W47" s="33">
         <v>3.94</v>
       </c>
-      <c r="X47" s="32">
+      <c r="X47" s="33">
         <v>2.18</v>
       </c>
-      <c r="Y47" s="32">
+      <c r="Y47" s="33">
         <v>13.2</v>
       </c>
-      <c r="Z47" s="34"/>
-      <c r="AA47" s="34"/>
-      <c r="AB47" s="32">
+      <c r="Z47" s="35"/>
+      <c r="AA47" s="35"/>
+      <c r="AB47" s="33">
         <v>7.29</v>
       </c>
-      <c r="AC47" s="32">
+      <c r="AC47" s="33">
         <v>10.46</v>
       </c>
-      <c r="AD47" s="32">
+      <c r="AD47" s="33">
         <v>30.64</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="31" t="s">
         <v>394</v>
       </c>
-      <c r="B48" s="31">
+      <c r="B48" s="32">
         <v>703.11</v>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="33">
         <v>12.32</v>
       </c>
-      <c r="D48" s="32">
+      <c r="D48" s="33">
         <v>9.4</v>
       </c>
-      <c r="E48" s="32">
+      <c r="E48" s="33">
         <v>28.15</v>
       </c>
-      <c r="F48" s="32">
+      <c r="F48" s="33">
         <v>76.52</v>
       </c>
-      <c r="G48" s="32">
+      <c r="G48" s="33">
         <v>18.14</v>
       </c>
-      <c r="H48" s="34"/>
-      <c r="I48" s="34"/>
-      <c r="J48" s="31">
+      <c r="H48" s="35"/>
+      <c r="I48" s="35"/>
+      <c r="J48" s="32">
         <v>103.38</v>
       </c>
-      <c r="K48" s="34"/>
-      <c r="L48" s="32">
+      <c r="K48" s="35"/>
+      <c r="L48" s="33">
         <v>10.11</v>
       </c>
-      <c r="M48" s="34"/>
-      <c r="N48" s="34"/>
-      <c r="O48" s="34"/>
-      <c r="P48" s="34"/>
-      <c r="Q48" s="34"/>
-      <c r="R48" s="32">
+      <c r="M48" s="35"/>
+      <c r="N48" s="35"/>
+      <c r="O48" s="35"/>
+      <c r="P48" s="35"/>
+      <c r="Q48" s="35"/>
+      <c r="R48" s="33">
         <v>15.74</v>
       </c>
-      <c r="S48" s="32">
+      <c r="S48" s="33">
         <v>7.64</v>
       </c>
-      <c r="T48" s="32">
+      <c r="T48" s="33">
         <v>5.28</v>
       </c>
-      <c r="U48" s="32">
+      <c r="U48" s="33">
         <v>4.49</v>
       </c>
-      <c r="V48" s="32">
+      <c r="V48" s="33">
         <v>6.98</v>
       </c>
-      <c r="W48" s="32">
+      <c r="W48" s="33">
         <v>10.78</v>
       </c>
-      <c r="X48" s="32">
+      <c r="X48" s="33">
         <v>15.46</v>
       </c>
-      <c r="Y48" s="34"/>
-      <c r="Z48" s="34"/>
-      <c r="AA48" s="34"/>
-      <c r="AB48" s="34"/>
-      <c r="AC48" s="34"/>
-      <c r="AD48" s="34"/>
+      <c r="Y48" s="35"/>
+      <c r="Z48" s="35"/>
+      <c r="AA48" s="35"/>
+      <c r="AB48" s="35"/>
+      <c r="AC48" s="35"/>
+      <c r="AD48" s="35"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
+      <c r="A49" s="29" t="s">
         <v>395</v>
       </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="29"/>
-      <c r="U49" s="29"/>
-      <c r="V49" s="29"/>
-      <c r="W49" s="29"/>
-      <c r="X49" s="29"/>
-      <c r="Y49" s="29"/>
-      <c r="Z49" s="29"/>
-      <c r="AA49" s="29"/>
-      <c r="AB49" s="29"/>
-      <c r="AC49" s="29"/>
-      <c r="AD49" s="29"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="30"/>
+      <c r="X49" s="30"/>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
+      <c r="AA49" s="30"/>
+      <c r="AB49" s="30"/>
+      <c r="AC49" s="30"/>
+      <c r="AD49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="31" t="s">
         <v>396</v>
       </c>
-      <c r="B50" s="32">
+      <c r="B50" s="33">
         <v>12.78</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="33">
         <v>11.42</v>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="33">
         <v>6.22</v>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="33">
         <v>5.23</v>
       </c>
-      <c r="F50" s="32">
+      <c r="F50" s="33">
         <v>5.49</v>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="33">
         <v>4.56</v>
       </c>
-      <c r="H50" s="32">
+      <c r="H50" s="33">
         <v>6.68</v>
       </c>
-      <c r="I50" s="34"/>
-      <c r="J50" s="32">
+      <c r="I50" s="35"/>
+      <c r="J50" s="33">
         <v>8.85</v>
       </c>
-      <c r="K50" s="32">
+      <c r="K50" s="33">
         <v>4.56</v>
       </c>
-      <c r="L50" s="34"/>
-      <c r="M50" s="34"/>
-      <c r="N50" s="32">
+      <c r="L50" s="35"/>
+      <c r="M50" s="35"/>
+      <c r="N50" s="33">
         <v>5.08</v>
       </c>
-      <c r="O50" s="32">
+      <c r="O50" s="33">
         <v>1.38</v>
       </c>
-      <c r="P50" s="34"/>
-      <c r="Q50" s="34"/>
-      <c r="R50" s="34"/>
-      <c r="S50" s="34"/>
-      <c r="T50" s="32">
+      <c r="P50" s="35"/>
+      <c r="Q50" s="35"/>
+      <c r="R50" s="35"/>
+      <c r="S50" s="35"/>
+      <c r="T50" s="33">
         <v>15.73</v>
       </c>
-      <c r="U50" s="32">
+      <c r="U50" s="33">
         <v>60.0</v>
       </c>
-      <c r="V50" s="32">
+      <c r="V50" s="33">
         <v>5.52</v>
       </c>
-      <c r="W50" s="32">
+      <c r="W50" s="33">
         <v>2.88</v>
       </c>
-      <c r="X50" s="34"/>
-      <c r="Y50" s="34"/>
-      <c r="Z50" s="34"/>
-      <c r="AA50" s="34"/>
-      <c r="AB50" s="32">
+      <c r="X50" s="35"/>
+      <c r="Y50" s="35"/>
+      <c r="Z50" s="35"/>
+      <c r="AA50" s="35"/>
+      <c r="AB50" s="33">
         <v>10.28</v>
       </c>
-      <c r="AC50" s="34"/>
-      <c r="AD50" s="34"/>
+      <c r="AC50" s="35"/>
+      <c r="AD50" s="35"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="31" t="s">
         <v>397</v>
       </c>
-      <c r="B51" s="32">
+      <c r="B51" s="33">
         <v>8.18</v>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="33">
         <v>6.49</v>
       </c>
-      <c r="D51" s="32">
+      <c r="D51" s="33">
         <v>5.58</v>
       </c>
-      <c r="E51" s="32">
+      <c r="E51" s="33">
         <v>7.99</v>
       </c>
-      <c r="F51" s="32">
+      <c r="F51" s="33">
         <v>9.04</v>
       </c>
-      <c r="G51" s="32">
+      <c r="G51" s="33">
         <v>8.72</v>
       </c>
-      <c r="H51" s="32">
+      <c r="H51" s="33">
         <v>11.47</v>
       </c>
-      <c r="I51" s="32">
+      <c r="I51" s="33">
         <v>17.25</v>
       </c>
-      <c r="J51" s="32">
+      <c r="J51" s="33">
         <v>9.55</v>
       </c>
-      <c r="K51" s="32">
+      <c r="K51" s="33">
         <v>5.71</v>
       </c>
-      <c r="L51" s="32">
+      <c r="L51" s="33">
         <v>27.61</v>
       </c>
-      <c r="M51" s="34"/>
-      <c r="N51" s="34"/>
-      <c r="O51" s="34"/>
-      <c r="P51" s="34"/>
-      <c r="Q51" s="34"/>
-      <c r="R51" s="32">
+      <c r="M51" s="35"/>
+      <c r="N51" s="35"/>
+      <c r="O51" s="35"/>
+      <c r="P51" s="35"/>
+      <c r="Q51" s="35"/>
+      <c r="R51" s="33">
         <v>14.56</v>
       </c>
-      <c r="S51" s="32">
+      <c r="S51" s="33">
         <v>7.51</v>
       </c>
-      <c r="T51" s="34"/>
-      <c r="U51" s="34"/>
-      <c r="V51" s="34"/>
-      <c r="W51" s="34"/>
-      <c r="X51" s="34"/>
-      <c r="Y51" s="34"/>
-      <c r="Z51" s="34"/>
-      <c r="AA51" s="34"/>
-      <c r="AB51" s="34"/>
-      <c r="AC51" s="34"/>
-      <c r="AD51" s="34"/>
+      <c r="T51" s="35"/>
+      <c r="U51" s="35"/>
+      <c r="V51" s="35"/>
+      <c r="W51" s="35"/>
+      <c r="X51" s="35"/>
+      <c r="Y51" s="35"/>
+      <c r="Z51" s="35"/>
+      <c r="AA51" s="35"/>
+      <c r="AB51" s="35"/>
+      <c r="AC51" s="35"/>
+      <c r="AD51" s="35"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="28" t="s">
+      <c r="A52" s="29" t="s">
         <v>398</v>
       </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="29"/>
-      <c r="S52" s="29"/>
-      <c r="T52" s="29"/>
-      <c r="U52" s="29"/>
-      <c r="V52" s="29"/>
-      <c r="W52" s="29"/>
-      <c r="X52" s="29"/>
-      <c r="Y52" s="29"/>
-      <c r="Z52" s="29"/>
-      <c r="AA52" s="29"/>
-      <c r="AB52" s="29"/>
-      <c r="AC52" s="29"/>
-      <c r="AD52" s="29"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30"/>
+      <c r="T52" s="30"/>
+      <c r="U52" s="30"/>
+      <c r="V52" s="30"/>
+      <c r="W52" s="30"/>
+      <c r="X52" s="30"/>
+      <c r="Y52" s="30"/>
+      <c r="Z52" s="30"/>
+      <c r="AA52" s="30"/>
+      <c r="AB52" s="30"/>
+      <c r="AC52" s="30"/>
+      <c r="AD52" s="30"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="30" t="s">
+      <c r="A53" s="31" t="s">
         <v>399</v>
       </c>
-      <c r="B53" s="32">
+      <c r="B53" s="33">
         <v>18.83</v>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="33">
         <v>15.2</v>
       </c>
-      <c r="D53" s="32">
+      <c r="D53" s="33">
         <v>10.25</v>
       </c>
-      <c r="E53" s="32">
+      <c r="E53" s="33">
         <v>8.17</v>
       </c>
-      <c r="F53" s="32">
+      <c r="F53" s="33">
         <v>8.96</v>
       </c>
-      <c r="G53" s="32">
+      <c r="G53" s="33">
         <v>6.29</v>
       </c>
-      <c r="H53" s="32">
+      <c r="H53" s="33">
         <v>7.56</v>
       </c>
-      <c r="I53" s="34"/>
-      <c r="J53" s="32">
+      <c r="I53" s="35"/>
+      <c r="J53" s="33">
         <v>10.92</v>
       </c>
-      <c r="K53" s="32">
+      <c r="K53" s="33">
         <v>6.6</v>
       </c>
-      <c r="L53" s="34"/>
-      <c r="M53" s="34"/>
-      <c r="N53" s="32">
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="33">
         <v>12.37</v>
       </c>
-      <c r="O53" s="32">
+      <c r="O53" s="33">
         <v>2.13</v>
       </c>
-      <c r="P53" s="34"/>
-      <c r="Q53" s="34"/>
-      <c r="R53" s="34"/>
-      <c r="S53" s="34"/>
-      <c r="T53" s="32">
+      <c r="P53" s="35"/>
+      <c r="Q53" s="35"/>
+      <c r="R53" s="35"/>
+      <c r="S53" s="35"/>
+      <c r="T53" s="33">
         <v>20.3</v>
       </c>
-      <c r="U53" s="34"/>
-      <c r="V53" s="32">
+      <c r="U53" s="35"/>
+      <c r="V53" s="33">
         <v>24.18</v>
       </c>
-      <c r="W53" s="32">
+      <c r="W53" s="33">
         <v>15.11</v>
       </c>
-      <c r="X53" s="32">
+      <c r="X53" s="33">
         <v>1.16</v>
       </c>
-      <c r="Y53" s="34"/>
-      <c r="Z53" s="32">
+      <c r="Y53" s="35"/>
+      <c r="Z53" s="33">
         <v>6.57</v>
       </c>
-      <c r="AA53" s="32">
+      <c r="AA53" s="33">
         <v>7.67</v>
       </c>
-      <c r="AB53" s="32">
+      <c r="AB53" s="33">
         <v>17.9</v>
       </c>
-      <c r="AC53" s="32">
+      <c r="AC53" s="33">
         <v>13.16</v>
       </c>
-      <c r="AD53" s="32">
+      <c r="AD53" s="33">
         <v>23.81</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="30" t="s">
+      <c r="A54" s="31" t="s">
         <v>400</v>
       </c>
-      <c r="B54" s="32">
+      <c r="B54" s="33">
         <v>12.46</v>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="33">
         <v>9.74</v>
       </c>
-      <c r="D54" s="32">
+      <c r="D54" s="33">
         <v>8.15</v>
       </c>
-      <c r="E54" s="32">
+      <c r="E54" s="33">
         <v>12.68</v>
       </c>
-      <c r="F54" s="32">
+      <c r="F54" s="33">
         <v>13.31</v>
       </c>
-      <c r="G54" s="32">
+      <c r="G54" s="33">
         <v>12.48</v>
       </c>
-      <c r="H54" s="32">
+      <c r="H54" s="33">
         <v>19.74</v>
       </c>
-      <c r="I54" s="31">
+      <c r="I54" s="32">
         <v>112.6</v>
       </c>
-      <c r="J54" s="32">
+      <c r="J54" s="33">
         <v>26.85</v>
       </c>
-      <c r="K54" s="32">
+      <c r="K54" s="33">
         <v>18.23</v>
       </c>
-      <c r="L54" s="34"/>
-      <c r="M54" s="34"/>
-      <c r="N54" s="34"/>
-      <c r="O54" s="34"/>
-      <c r="P54" s="34"/>
-      <c r="Q54" s="34"/>
-      <c r="R54" s="34"/>
-      <c r="S54" s="32">
+      <c r="L54" s="35"/>
+      <c r="M54" s="35"/>
+      <c r="N54" s="35"/>
+      <c r="O54" s="35"/>
+      <c r="P54" s="35"/>
+      <c r="Q54" s="35"/>
+      <c r="R54" s="35"/>
+      <c r="S54" s="33">
         <v>51.28</v>
       </c>
-      <c r="T54" s="32">
+      <c r="T54" s="33">
         <v>6.46</v>
       </c>
-      <c r="U54" s="32">
+      <c r="U54" s="33">
         <v>6.58</v>
       </c>
-      <c r="V54" s="32">
+      <c r="V54" s="33">
         <v>5.17</v>
       </c>
-      <c r="W54" s="32">
+      <c r="W54" s="33">
         <v>4.45</v>
       </c>
-      <c r="X54" s="32">
+      <c r="X54" s="33">
         <v>4.34</v>
       </c>
-      <c r="Y54" s="32">
+      <c r="Y54" s="33">
         <v>11.75</v>
       </c>
-      <c r="Z54" s="32">
+      <c r="Z54" s="33">
         <v>10.14</v>
       </c>
-      <c r="AA54" s="34"/>
-      <c r="AB54" s="34"/>
-      <c r="AC54" s="34"/>
-      <c r="AD54" s="34"/>
+      <c r="AA54" s="35"/>
+      <c r="AB54" s="35"/>
+      <c r="AC54" s="35"/>
+      <c r="AD54" s="35"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="28" t="s">
+      <c r="A55" s="29" t="s">
         <v>401</v>
       </c>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
-      <c r="N55" s="29"/>
-      <c r="O55" s="29"/>
-      <c r="P55" s="29"/>
-      <c r="Q55" s="29"/>
-      <c r="R55" s="29"/>
-      <c r="S55" s="29"/>
-      <c r="T55" s="29"/>
-      <c r="U55" s="29"/>
-      <c r="V55" s="29"/>
-      <c r="W55" s="29"/>
-      <c r="X55" s="29"/>
-      <c r="Y55" s="29"/>
-      <c r="Z55" s="29"/>
-      <c r="AA55" s="29"/>
-      <c r="AB55" s="29"/>
-      <c r="AC55" s="29"/>
-      <c r="AD55" s="29"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
+      <c r="S55" s="30"/>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
+      <c r="V55" s="30"/>
+      <c r="W55" s="30"/>
+      <c r="X55" s="30"/>
+      <c r="Y55" s="30"/>
+      <c r="Z55" s="30"/>
+      <c r="AA55" s="30"/>
+      <c r="AB55" s="30"/>
+      <c r="AC55" s="30"/>
+      <c r="AD55" s="30"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="30" t="s">
+      <c r="A56" s="31" t="s">
         <v>402</v>
       </c>
-      <c r="B56" s="32">
+      <c r="B56" s="33">
         <v>18.83</v>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="33">
         <v>13.3</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="33">
         <v>8.85</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="33">
         <v>8.17</v>
       </c>
-      <c r="F56" s="32">
+      <c r="F56" s="33">
         <v>8.96</v>
       </c>
-      <c r="G56" s="32">
+      <c r="G56" s="33">
         <v>6.29</v>
       </c>
-      <c r="H56" s="32">
+      <c r="H56" s="33">
         <v>8.45</v>
       </c>
-      <c r="I56" s="32">
+      <c r="I56" s="33">
         <v>9.88</v>
       </c>
-      <c r="J56" s="32">
+      <c r="J56" s="33">
         <v>10.92</v>
       </c>
-      <c r="K56" s="32">
+      <c r="K56" s="33">
         <v>6.6</v>
       </c>
-      <c r="L56" s="34"/>
-      <c r="M56" s="34"/>
-      <c r="N56" s="32">
+      <c r="L56" s="35"/>
+      <c r="M56" s="35"/>
+      <c r="N56" s="33">
         <v>12.37</v>
       </c>
-      <c r="O56" s="32">
+      <c r="O56" s="33">
         <v>2.13</v>
       </c>
-      <c r="P56" s="34"/>
-      <c r="Q56" s="34"/>
-      <c r="R56" s="34"/>
-      <c r="S56" s="34"/>
-      <c r="T56" s="32">
+      <c r="P56" s="35"/>
+      <c r="Q56" s="35"/>
+      <c r="R56" s="35"/>
+      <c r="S56" s="35"/>
+      <c r="T56" s="33">
         <v>17.28</v>
       </c>
-      <c r="U56" s="34"/>
-      <c r="V56" s="32">
+      <c r="U56" s="35"/>
+      <c r="V56" s="33">
         <v>20.86</v>
       </c>
-      <c r="W56" s="32">
+      <c r="W56" s="33">
         <v>10.74</v>
       </c>
-      <c r="X56" s="34"/>
-      <c r="Y56" s="34"/>
-      <c r="Z56" s="34"/>
-      <c r="AA56" s="34"/>
-      <c r="AB56" s="32">
+      <c r="X56" s="35"/>
+      <c r="Y56" s="35"/>
+      <c r="Z56" s="35"/>
+      <c r="AA56" s="35"/>
+      <c r="AB56" s="33">
         <v>17.83</v>
       </c>
-      <c r="AC56" s="34"/>
-      <c r="AD56" s="34"/>
+      <c r="AC56" s="35"/>
+      <c r="AD56" s="35"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="30" t="s">
+      <c r="A57" s="31" t="s">
         <v>403</v>
       </c>
-      <c r="B57" s="32">
+      <c r="B57" s="33">
         <v>1.1</v>
       </c>
-      <c r="C57" s="32">
+      <c r="C57" s="33">
         <v>0.83</v>
       </c>
-      <c r="D57" s="32">
+      <c r="D57" s="33">
         <v>0.8</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="33">
         <v>0.96</v>
       </c>
-      <c r="F57" s="32">
+      <c r="F57" s="33">
         <v>1.15</v>
       </c>
-      <c r="G57" s="32">
+      <c r="G57" s="33">
         <v>1.22</v>
       </c>
-      <c r="H57" s="32">
+      <c r="H57" s="33">
         <v>1.26</v>
       </c>
-      <c r="I57" s="32">
+      <c r="I57" s="33">
         <v>1.2</v>
       </c>
-      <c r="J57" s="32">
+      <c r="J57" s="33">
         <v>0.94</v>
       </c>
-      <c r="K57" s="32">
+      <c r="K57" s="33">
         <v>0.64</v>
       </c>
-      <c r="L57" s="32">
+      <c r="L57" s="33">
         <v>0.51</v>
       </c>
-      <c r="M57" s="32">
+      <c r="M57" s="33">
         <v>0.46</v>
       </c>
-      <c r="N57" s="32">
+      <c r="N57" s="33">
         <v>0.54</v>
       </c>
-      <c r="O57" s="32">
+      <c r="O57" s="33">
         <v>0.67</v>
       </c>
-      <c r="P57" s="32">
+      <c r="P57" s="33">
         <v>0.95</v>
       </c>
-      <c r="Q57" s="32">
+      <c r="Q57" s="33">
         <v>0.84</v>
       </c>
-      <c r="R57" s="32">
+      <c r="R57" s="33">
         <v>0.79</v>
       </c>
-      <c r="S57" s="32">
+      <c r="S57" s="33">
         <v>0.71</v>
       </c>
-      <c r="T57" s="32">
+      <c r="T57" s="33">
         <v>0.62</v>
       </c>
-      <c r="U57" s="32">
+      <c r="U57" s="33">
         <v>0.57</v>
       </c>
-      <c r="V57" s="32">
+      <c r="V57" s="33">
         <v>0.67</v>
       </c>
-      <c r="W57" s="32">
+      <c r="W57" s="33">
         <v>0.78</v>
       </c>
-      <c r="X57" s="32">
+      <c r="X57" s="33">
         <v>1.04</v>
       </c>
-      <c r="Y57" s="32">
+      <c r="Y57" s="33">
         <v>1.62</v>
       </c>
-      <c r="Z57" s="32">
+      <c r="Z57" s="33">
         <v>1.86</v>
       </c>
-      <c r="AA57" s="34"/>
-      <c r="AB57" s="34"/>
-      <c r="AC57" s="34"/>
-      <c r="AD57" s="34"/>
+      <c r="AA57" s="35"/>
+      <c r="AB57" s="35"/>
+      <c r="AC57" s="35"/>
+      <c r="AD57" s="35"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
+      <c r="A58" s="29" t="s">
         <v>404</v>
       </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="29"/>
-      <c r="M58" s="29"/>
-      <c r="N58" s="29"/>
-      <c r="O58" s="29"/>
-      <c r="P58" s="29"/>
-      <c r="Q58" s="29"/>
-      <c r="R58" s="29"/>
-      <c r="S58" s="29"/>
-      <c r="T58" s="29"/>
-      <c r="U58" s="29"/>
-      <c r="V58" s="29"/>
-      <c r="W58" s="29"/>
-      <c r="X58" s="29"/>
-      <c r="Y58" s="29"/>
-      <c r="Z58" s="29"/>
-      <c r="AA58" s="29"/>
-      <c r="AB58" s="29"/>
-      <c r="AC58" s="29"/>
-      <c r="AD58" s="29"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+      <c r="S58" s="30"/>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
+      <c r="V58" s="30"/>
+      <c r="W58" s="30"/>
+      <c r="X58" s="30"/>
+      <c r="Y58" s="30"/>
+      <c r="Z58" s="30"/>
+      <c r="AA58" s="30"/>
+      <c r="AB58" s="30"/>
+      <c r="AC58" s="30"/>
+      <c r="AD58" s="30"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="30" t="s">
+      <c r="A59" s="31" t="s">
         <v>405</v>
       </c>
-      <c r="B59" s="32">
+      <c r="B59" s="33">
         <v>38.02</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="33">
         <v>1.39</v>
       </c>
-      <c r="D59" s="33">
+      <c r="D59" s="34">
         <v>-1.07</v>
       </c>
-      <c r="E59" s="32">
+      <c r="E59" s="33">
         <v>0.38</v>
       </c>
-      <c r="F59" s="33">
+      <c r="F59" s="34">
         <v>-0.38</v>
       </c>
-      <c r="G59" s="32">
+      <c r="G59" s="33">
         <v>0.52</v>
       </c>
-      <c r="H59" s="32">
+      <c r="H59" s="33">
         <v>0.02</v>
       </c>
-      <c r="I59" s="34"/>
-      <c r="J59" s="32">
+      <c r="I59" s="35"/>
+      <c r="J59" s="33">
         <v>0.44</v>
       </c>
-      <c r="K59" s="32">
+      <c r="K59" s="33">
         <v>0.02</v>
       </c>
-      <c r="L59" s="34"/>
-      <c r="M59" s="34"/>
-      <c r="N59" s="33">
+      <c r="L59" s="35"/>
+      <c r="M59" s="35"/>
+      <c r="N59" s="34">
         <v>-0.18</v>
       </c>
-      <c r="O59" s="32">
+      <c r="O59" s="33">
         <v>0.01</v>
       </c>
-      <c r="P59" s="34"/>
-      <c r="Q59" s="34"/>
-      <c r="R59" s="34"/>
-      <c r="S59" s="34"/>
-      <c r="T59" s="32">
+      <c r="P59" s="35"/>
+      <c r="Q59" s="35"/>
+      <c r="R59" s="35"/>
+      <c r="S59" s="35"/>
+      <c r="T59" s="33">
         <v>0.11</v>
       </c>
-      <c r="U59" s="34"/>
-      <c r="V59" s="33">
+      <c r="U59" s="35"/>
+      <c r="V59" s="34">
         <v>-1.89</v>
       </c>
-      <c r="W59" s="33">
+      <c r="W59" s="34">
         <v>-0.17</v>
       </c>
-      <c r="X59" s="34">
+      <c r="X59" s="35">
         <v>0.0</v>
       </c>
-      <c r="Y59" s="34"/>
-      <c r="Z59" s="32">
+      <c r="Y59" s="35"/>
+      <c r="Z59" s="33">
         <v>0.16</v>
       </c>
-      <c r="AA59" s="32">
+      <c r="AA59" s="33">
         <v>0.04</v>
       </c>
-      <c r="AB59" s="33">
+      <c r="AB59" s="34">
         <v>-0.47</v>
       </c>
-      <c r="AC59" s="32">
+      <c r="AC59" s="33">
         <v>0.13</v>
       </c>
-      <c r="AD59" s="34"/>
+      <c r="AD59" s="35"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="30" t="s">
+      <c r="A60" s="31" t="s">
         <v>406</v>
       </c>
-      <c r="B60" s="33">
+      <c r="B60" s="34">
         <v>-9.09</v>
       </c>
-      <c r="C60" s="32">
+      <c r="C60" s="33">
         <v>11.79</v>
       </c>
-      <c r="D60" s="34"/>
-      <c r="E60" s="33">
+      <c r="D60" s="35"/>
+      <c r="E60" s="34">
         <v>-2.86</v>
       </c>
-      <c r="F60" s="33">
+      <c r="F60" s="34">
         <v>-3.39</v>
       </c>
-      <c r="G60" s="34"/>
-      <c r="H60" s="34"/>
-      <c r="I60" s="34"/>
-      <c r="J60" s="32">
+      <c r="G60" s="35"/>
+      <c r="H60" s="35"/>
+      <c r="I60" s="35"/>
+      <c r="J60" s="33">
         <v>38.16</v>
       </c>
-      <c r="K60" s="34"/>
-      <c r="L60" s="34"/>
-      <c r="M60" s="34"/>
-      <c r="N60" s="34"/>
-      <c r="O60" s="34"/>
-      <c r="P60" s="34"/>
-      <c r="Q60" s="34"/>
-      <c r="R60" s="34"/>
-      <c r="S60" s="34"/>
-      <c r="T60" s="34"/>
-      <c r="U60" s="34"/>
-      <c r="V60" s="33">
+      <c r="K60" s="35"/>
+      <c r="L60" s="35"/>
+      <c r="M60" s="35"/>
+      <c r="N60" s="35"/>
+      <c r="O60" s="35"/>
+      <c r="P60" s="35"/>
+      <c r="Q60" s="35"/>
+      <c r="R60" s="35"/>
+      <c r="S60" s="35"/>
+      <c r="T60" s="35"/>
+      <c r="U60" s="35"/>
+      <c r="V60" s="34">
         <v>-0.33</v>
       </c>
-      <c r="W60" s="32">
+      <c r="W60" s="33">
         <v>0.51</v>
       </c>
-      <c r="X60" s="32">
+      <c r="X60" s="33">
         <v>0.07</v>
       </c>
-      <c r="Y60" s="34"/>
-      <c r="Z60" s="34"/>
-      <c r="AA60" s="34"/>
-      <c r="AB60" s="34"/>
-      <c r="AC60" s="34"/>
-      <c r="AD60" s="34"/>
+      <c r="Y60" s="35"/>
+      <c r="Z60" s="35"/>
+      <c r="AA60" s="35"/>
+      <c r="AB60" s="35"/>
+      <c r="AC60" s="35"/>
+      <c r="AD60" s="35"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="28" t="s">
+      <c r="A61" s="29" t="s">
         <v>407</v>
       </c>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
-      <c r="Q61" s="29"/>
-      <c r="R61" s="29"/>
-      <c r="S61" s="29"/>
-      <c r="T61" s="29"/>
-      <c r="U61" s="29"/>
-      <c r="V61" s="29"/>
-      <c r="W61" s="29"/>
-      <c r="X61" s="29"/>
-      <c r="Y61" s="29"/>
-      <c r="Z61" s="29"/>
-      <c r="AA61" s="29"/>
-      <c r="AB61" s="29"/>
-      <c r="AC61" s="29"/>
-      <c r="AD61" s="29"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+      <c r="S61" s="30"/>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
+      <c r="V61" s="30"/>
+      <c r="W61" s="30"/>
+      <c r="X61" s="30"/>
+      <c r="Y61" s="30"/>
+      <c r="Z61" s="30"/>
+      <c r="AA61" s="30"/>
+      <c r="AB61" s="30"/>
+      <c r="AC61" s="30"/>
+      <c r="AD61" s="30"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="30" t="s">
+      <c r="A62" s="31" t="s">
         <v>408</v>
       </c>
-      <c r="B62" s="32">
+      <c r="B62" s="33">
         <v>1.24</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="33">
         <v>0.26</v>
       </c>
-      <c r="D62" s="32">
+      <c r="D62" s="33">
         <v>0.61</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="33">
         <v>0.37</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="33">
         <v>0.41</v>
       </c>
-      <c r="G62" s="32">
+      <c r="G62" s="33">
         <v>0.35</v>
       </c>
-      <c r="H62" s="32">
+      <c r="H62" s="33">
         <v>0.3</v>
       </c>
-      <c r="I62" s="32">
+      <c r="I62" s="33">
         <v>0.58</v>
       </c>
-      <c r="J62" s="32">
+      <c r="J62" s="33">
         <v>0.64</v>
       </c>
-      <c r="K62" s="32">
+      <c r="K62" s="33">
         <v>0.37</v>
       </c>
-      <c r="L62" s="32">
+      <c r="L62" s="33">
         <v>0.27</v>
       </c>
-      <c r="M62" s="32">
+      <c r="M62" s="33">
         <v>0.23</v>
       </c>
-      <c r="N62" s="32">
+      <c r="N62" s="33">
         <v>0.25</v>
       </c>
-      <c r="O62" s="32">
+      <c r="O62" s="33">
         <v>0.24</v>
       </c>
-      <c r="P62" s="32">
+      <c r="P62" s="33">
         <v>0.3</v>
       </c>
-      <c r="Q62" s="32">
+      <c r="Q62" s="33">
         <v>0.28</v>
       </c>
-      <c r="R62" s="32">
+      <c r="R62" s="33">
         <v>0.18</v>
       </c>
-      <c r="S62" s="32">
+      <c r="S62" s="33">
         <v>0.25</v>
       </c>
-      <c r="T62" s="32">
+      <c r="T62" s="33">
         <v>0.65</v>
       </c>
-      <c r="U62" s="33">
+      <c r="U62" s="34">
         <v>-0.14</v>
       </c>
-      <c r="V62" s="32">
+      <c r="V62" s="33">
         <v>0.64</v>
       </c>
-      <c r="W62" s="32">
+      <c r="W62" s="33">
         <v>0.3</v>
       </c>
-      <c r="X62" s="32">
+      <c r="X62" s="33">
         <v>0.26</v>
       </c>
-      <c r="Y62" s="32">
+      <c r="Y62" s="33">
         <v>0.71</v>
       </c>
-      <c r="Z62" s="32">
+      <c r="Z62" s="33">
         <v>0.57</v>
       </c>
-      <c r="AA62" s="32">
+      <c r="AA62" s="33">
         <v>0.62</v>
       </c>
-      <c r="AB62" s="32">
+      <c r="AB62" s="33">
         <v>1.29</v>
       </c>
-      <c r="AC62" s="32">
+      <c r="AC62" s="33">
         <v>0.96</v>
       </c>
-      <c r="AD62" s="32">
+      <c r="AD62" s="33">
         <v>0.7</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="30" t="s">
+      <c r="A63" s="31" t="s">
         <v>409</v>
       </c>
-      <c r="B63" s="32">
+      <c r="B63" s="33">
         <v>0.55</v>
       </c>
-      <c r="C63" s="32">
+      <c r="C63" s="33">
         <v>0.39</v>
       </c>
-      <c r="D63" s="32">
+      <c r="D63" s="33">
         <v>0.39</v>
       </c>
-      <c r="E63" s="32">
+      <c r="E63" s="33">
         <v>0.4</v>
       </c>
-      <c r="F63" s="32">
+      <c r="F63" s="33">
         <v>0.45</v>
       </c>
-      <c r="G63" s="32">
+      <c r="G63" s="33">
         <v>0.45</v>
       </c>
-      <c r="H63" s="32">
+      <c r="H63" s="33">
         <v>0.43</v>
       </c>
-      <c r="I63" s="32">
+      <c r="I63" s="33">
         <v>0.42</v>
       </c>
-      <c r="J63" s="32">
+      <c r="J63" s="33">
         <v>0.35</v>
       </c>
-      <c r="K63" s="32">
+      <c r="K63" s="33">
         <v>0.27</v>
       </c>
-      <c r="L63" s="32">
+      <c r="L63" s="33">
         <v>0.26</v>
       </c>
-      <c r="M63" s="32">
+      <c r="M63" s="33">
         <v>0.26</v>
       </c>
-      <c r="N63" s="32">
+      <c r="N63" s="33">
         <v>0.24</v>
       </c>
-      <c r="O63" s="32">
+      <c r="O63" s="33">
         <v>0.24</v>
       </c>
-      <c r="P63" s="32">
+      <c r="P63" s="33">
         <v>0.32</v>
       </c>
-      <c r="Q63" s="32">
+      <c r="Q63" s="33">
         <v>0.24</v>
       </c>
-      <c r="R63" s="32">
+      <c r="R63" s="33">
         <v>0.3</v>
       </c>
-      <c r="S63" s="32">
+      <c r="S63" s="33">
         <v>0.32</v>
       </c>
-      <c r="T63" s="32">
+      <c r="T63" s="33">
         <v>0.3</v>
       </c>
-      <c r="U63" s="32">
+      <c r="U63" s="33">
         <v>0.3</v>
       </c>
-      <c r="V63" s="32">
+      <c r="V63" s="33">
         <v>0.44</v>
       </c>
-      <c r="W63" s="32">
+      <c r="W63" s="33">
         <v>0.48</v>
       </c>
-      <c r="X63" s="32">
+      <c r="X63" s="33">
         <v>0.55</v>
       </c>
-      <c r="Y63" s="32">
+      <c r="Y63" s="33">
         <v>0.67</v>
       </c>
-      <c r="Z63" s="32">
+      <c r="Z63" s="33">
         <v>0.67</v>
       </c>
-      <c r="AA63" s="34"/>
-      <c r="AB63" s="34"/>
-      <c r="AC63" s="34"/>
-      <c r="AD63" s="34"/>
+      <c r="AA63" s="35"/>
+      <c r="AB63" s="35"/>
+      <c r="AC63" s="35"/>
+      <c r="AD63" s="35"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="28" t="s">
+      <c r="A64" s="29" t="s">
         <v>410</v>
       </c>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="29"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="29"/>
-      <c r="O64" s="29"/>
-      <c r="P64" s="29"/>
-      <c r="Q64" s="29"/>
-      <c r="R64" s="29"/>
-      <c r="S64" s="29"/>
-      <c r="T64" s="29"/>
-      <c r="U64" s="29"/>
-      <c r="V64" s="29"/>
-      <c r="W64" s="29"/>
-      <c r="X64" s="29"/>
-      <c r="Y64" s="29"/>
-      <c r="Z64" s="29"/>
-      <c r="AA64" s="29"/>
-      <c r="AB64" s="29"/>
-      <c r="AC64" s="29"/>
-      <c r="AD64" s="29"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
+      <c r="R64" s="30"/>
+      <c r="S64" s="30"/>
+      <c r="T64" s="30"/>
+      <c r="U64" s="30"/>
+      <c r="V64" s="30"/>
+      <c r="W64" s="30"/>
+      <c r="X64" s="30"/>
+      <c r="Y64" s="30"/>
+      <c r="Z64" s="30"/>
+      <c r="AA64" s="30"/>
+      <c r="AB64" s="30"/>
+      <c r="AC64" s="30"/>
+      <c r="AD64" s="30"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="30" t="s">
+      <c r="A65" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="B65" s="32">
+      <c r="B65" s="33">
         <v>10.62</v>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="33">
         <v>2.23</v>
       </c>
-      <c r="D65" s="32">
+      <c r="D65" s="33">
         <v>5.21</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="33">
         <v>4.88</v>
       </c>
-      <c r="F65" s="32">
+      <c r="F65" s="33">
         <v>6.27</v>
       </c>
-      <c r="G65" s="32">
+      <c r="G65" s="33">
         <v>5.24</v>
       </c>
-      <c r="H65" s="32">
+      <c r="H65" s="33">
         <v>6.1</v>
       </c>
-      <c r="I65" s="32">
+      <c r="I65" s="33">
         <v>8.13</v>
       </c>
-      <c r="J65" s="32">
+      <c r="J65" s="33">
         <v>9.8</v>
       </c>
-      <c r="K65" s="32">
+      <c r="K65" s="33">
         <v>5.35</v>
       </c>
-      <c r="L65" s="32">
+      <c r="L65" s="33">
         <v>7.57</v>
       </c>
-      <c r="M65" s="32">
+      <c r="M65" s="33">
         <v>15.49</v>
       </c>
-      <c r="N65" s="32">
+      <c r="N65" s="33">
         <v>4.68</v>
       </c>
-      <c r="O65" s="32">
+      <c r="O65" s="33">
         <v>3.44</v>
       </c>
-      <c r="P65" s="34"/>
-      <c r="Q65" s="34"/>
-      <c r="R65" s="32">
+      <c r="P65" s="35"/>
+      <c r="Q65" s="35"/>
+      <c r="R65" s="33">
         <v>15.19</v>
       </c>
-      <c r="S65" s="32">
+      <c r="S65" s="33">
         <v>4.04</v>
       </c>
-      <c r="T65" s="32">
+      <c r="T65" s="33">
         <v>10.01</v>
       </c>
-      <c r="U65" s="34"/>
-      <c r="V65" s="32">
+      <c r="U65" s="35"/>
+      <c r="V65" s="33">
         <v>3.17</v>
       </c>
-      <c r="W65" s="32">
+      <c r="W65" s="33">
         <v>2.9</v>
       </c>
-      <c r="X65" s="34"/>
-      <c r="Y65" s="34"/>
-      <c r="Z65" s="34"/>
-      <c r="AA65" s="34"/>
-      <c r="AB65" s="32">
+      <c r="X65" s="35"/>
+      <c r="Y65" s="35"/>
+      <c r="Z65" s="35"/>
+      <c r="AA65" s="35"/>
+      <c r="AB65" s="33">
         <v>16.6</v>
       </c>
-      <c r="AC65" s="34"/>
-      <c r="AD65" s="34"/>
+      <c r="AC65" s="35"/>
+      <c r="AD65" s="35"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="B66" s="32">
+      <c r="B66" s="33">
         <v>5.78</v>
       </c>
-      <c r="C66" s="32">
+      <c r="C66" s="33">
         <v>4.66</v>
       </c>
-      <c r="D66" s="32">
+      <c r="D66" s="33">
         <v>5.46</v>
       </c>
-      <c r="E66" s="32">
+      <c r="E66" s="33">
         <v>6.11</v>
       </c>
-      <c r="F66" s="32">
+      <c r="F66" s="33">
         <v>7.12</v>
       </c>
-      <c r="G66" s="32">
+      <c r="G66" s="33">
         <v>6.93</v>
       </c>
-      <c r="H66" s="32">
+      <c r="H66" s="33">
         <v>7.42</v>
       </c>
-      <c r="I66" s="32">
+      <c r="I66" s="33">
         <v>8.16</v>
       </c>
-      <c r="J66" s="32">
+      <c r="J66" s="33">
         <v>7.35</v>
       </c>
-      <c r="K66" s="32">
+      <c r="K66" s="33">
         <v>5.63</v>
       </c>
-      <c r="L66" s="32">
+      <c r="L66" s="33">
         <v>8.41</v>
       </c>
-      <c r="M66" s="34"/>
-      <c r="N66" s="34"/>
-      <c r="O66" s="32">
+      <c r="M66" s="35"/>
+      <c r="N66" s="35"/>
+      <c r="O66" s="33">
         <v>71.73</v>
       </c>
-      <c r="P66" s="32">
+      <c r="P66" s="33">
         <v>42.19</v>
       </c>
-      <c r="Q66" s="32">
+      <c r="Q66" s="33">
         <v>38.68</v>
       </c>
-      <c r="R66" s="32">
+      <c r="R66" s="33">
         <v>5.29</v>
       </c>
-      <c r="S66" s="32">
+      <c r="S66" s="33">
         <v>3.74</v>
       </c>
-      <c r="T66" s="34"/>
-      <c r="U66" s="34"/>
-      <c r="V66" s="34"/>
-      <c r="W66" s="34"/>
-      <c r="X66" s="34"/>
-      <c r="Y66" s="34"/>
-      <c r="Z66" s="34"/>
-      <c r="AA66" s="34"/>
-      <c r="AB66" s="34"/>
-      <c r="AC66" s="34"/>
-      <c r="AD66" s="34"/>
+      <c r="T66" s="35"/>
+      <c r="U66" s="35"/>
+      <c r="V66" s="35"/>
+      <c r="W66" s="35"/>
+      <c r="X66" s="35"/>
+      <c r="Y66" s="35"/>
+      <c r="Z66" s="35"/>
+      <c r="AA66" s="35"/>
+      <c r="AB66" s="35"/>
+      <c r="AC66" s="35"/>
+      <c r="AD66" s="35"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="28" t="s">
+      <c r="A67" s="29" t="s">
         <v>413</v>
       </c>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-      <c r="L67" s="29"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-      <c r="P67" s="29"/>
-      <c r="Q67" s="29"/>
-      <c r="R67" s="29"/>
-      <c r="S67" s="29"/>
-      <c r="T67" s="29"/>
-      <c r="U67" s="29"/>
-      <c r="V67" s="29"/>
-      <c r="W67" s="29"/>
-      <c r="X67" s="29"/>
-      <c r="Y67" s="29"/>
-      <c r="Z67" s="29"/>
-      <c r="AA67" s="29"/>
-      <c r="AB67" s="29"/>
-      <c r="AC67" s="29"/>
-      <c r="AD67" s="29"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="30"/>
+      <c r="T67" s="30"/>
+      <c r="U67" s="30"/>
+      <c r="V67" s="30"/>
+      <c r="W67" s="30"/>
+      <c r="X67" s="30"/>
+      <c r="Y67" s="30"/>
+      <c r="Z67" s="30"/>
+      <c r="AA67" s="30"/>
+      <c r="AB67" s="30"/>
+      <c r="AC67" s="30"/>
+      <c r="AD67" s="30"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="30" t="s">
+      <c r="A68" s="31" t="s">
         <v>414</v>
       </c>
-      <c r="B68" s="34"/>
-      <c r="C68" s="32">
+      <c r="B68" s="35"/>
+      <c r="C68" s="33">
         <v>5.35</v>
       </c>
-      <c r="D68" s="32">
+      <c r="D68" s="33">
         <v>4.99</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68" s="33">
         <v>4.48</v>
       </c>
-      <c r="F68" s="32">
+      <c r="F68" s="33">
         <v>28.76</v>
       </c>
-      <c r="G68" s="32">
+      <c r="G68" s="33">
         <v>5.01</v>
       </c>
-      <c r="H68" s="32">
+      <c r="H68" s="33">
         <v>11.47</v>
       </c>
-      <c r="I68" s="34"/>
-      <c r="J68" s="32">
+      <c r="I68" s="35"/>
+      <c r="J68" s="33">
         <v>11.79</v>
       </c>
-      <c r="K68" s="32">
+      <c r="K68" s="33">
         <v>4.97</v>
       </c>
-      <c r="L68" s="34"/>
-      <c r="M68" s="34"/>
-      <c r="N68" s="32">
+      <c r="L68" s="35"/>
+      <c r="M68" s="35"/>
+      <c r="N68" s="33">
         <v>4.37</v>
       </c>
-      <c r="O68" s="32">
+      <c r="O68" s="33">
         <v>13.77</v>
       </c>
-      <c r="P68" s="32">
+      <c r="P68" s="33">
         <v>2.61</v>
       </c>
-      <c r="Q68" s="34"/>
-      <c r="R68" s="34"/>
-      <c r="S68" s="32">
+      <c r="Q68" s="35"/>
+      <c r="R68" s="35"/>
+      <c r="S68" s="33">
         <v>7.3</v>
       </c>
-      <c r="T68" s="32">
+      <c r="T68" s="33">
         <v>62.43</v>
       </c>
-      <c r="U68" s="33">
+      <c r="U68" s="34">
         <v>-1.02</v>
       </c>
-      <c r="V68" s="32">
+      <c r="V68" s="33">
         <v>1.93</v>
       </c>
-      <c r="W68" s="32">
+      <c r="W68" s="33">
         <v>2.93</v>
       </c>
-      <c r="X68" s="32">
+      <c r="X68" s="33">
         <v>2.87</v>
       </c>
-      <c r="Y68" s="32">
+      <c r="Y68" s="33">
         <v>22.03</v>
       </c>
-      <c r="Z68" s="32">
+      <c r="Z68" s="33">
         <v>14.1</v>
       </c>
-      <c r="AA68" s="32">
+      <c r="AA68" s="33">
         <v>13.19</v>
       </c>
-      <c r="AB68" s="32">
+      <c r="AB68" s="33">
         <v>18.08</v>
       </c>
-      <c r="AC68" s="32">
+      <c r="AC68" s="33">
         <v>9.23</v>
       </c>
-      <c r="AD68" s="32">
+      <c r="AD68" s="33">
         <v>8.32</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="30" t="s">
+      <c r="A69" s="31" t="s">
         <v>415</v>
       </c>
-      <c r="B69" s="32">
+      <c r="B69" s="33">
         <v>17.69</v>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="33">
         <v>6.02</v>
       </c>
-      <c r="D69" s="32">
+      <c r="D69" s="33">
         <v>6.6</v>
       </c>
-      <c r="E69" s="32">
+      <c r="E69" s="33">
         <v>11.84</v>
       </c>
-      <c r="F69" s="32">
+      <c r="F69" s="33">
         <v>16.68</v>
       </c>
-      <c r="G69" s="32">
+      <c r="G69" s="33">
         <v>11.49</v>
       </c>
-      <c r="H69" s="32">
+      <c r="H69" s="33">
         <v>44.81</v>
       </c>
-      <c r="I69" s="34"/>
-      <c r="J69" s="32">
+      <c r="I69" s="35"/>
+      <c r="J69" s="33">
         <v>24.12</v>
       </c>
-      <c r="K69" s="32">
+      <c r="K69" s="33">
         <v>35.36</v>
       </c>
-      <c r="L69" s="32">
+      <c r="L69" s="33">
         <v>17.23</v>
       </c>
-      <c r="M69" s="34"/>
-      <c r="N69" s="34"/>
-      <c r="O69" s="34"/>
-      <c r="P69" s="34"/>
-      <c r="Q69" s="32">
+      <c r="M69" s="35"/>
+      <c r="N69" s="35"/>
+      <c r="O69" s="35"/>
+      <c r="P69" s="35"/>
+      <c r="Q69" s="33">
         <v>22.37</v>
       </c>
-      <c r="R69" s="32">
+      <c r="R69" s="33">
         <v>3.67</v>
       </c>
-      <c r="S69" s="32">
+      <c r="S69" s="33">
         <v>2.94</v>
       </c>
-      <c r="T69" s="32">
+      <c r="T69" s="33">
         <v>2.76</v>
       </c>
-      <c r="U69" s="32">
+      <c r="U69" s="33">
         <v>2.67</v>
       </c>
-      <c r="V69" s="32">
+      <c r="V69" s="33">
         <v>5.38</v>
       </c>
-      <c r="W69" s="32">
+      <c r="W69" s="33">
         <v>7.66</v>
       </c>
-      <c r="X69" s="32">
+      <c r="X69" s="33">
         <v>9.95</v>
       </c>
-      <c r="Y69" s="32">
+      <c r="Y69" s="33">
         <v>13.7</v>
       </c>
-      <c r="Z69" s="32">
+      <c r="Z69" s="33">
         <v>13.08</v>
       </c>
-      <c r="AA69" s="34"/>
-      <c r="AB69" s="34"/>
-      <c r="AC69" s="34"/>
-      <c r="AD69" s="34"/>
+      <c r="AA69" s="35"/>
+      <c r="AB69" s="35"/>
+      <c r="AC69" s="35"/>
+      <c r="AD69" s="35"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="28" t="s">
+      <c r="A70" s="29" t="s">
         <v>416</v>
       </c>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="29"/>
-      <c r="M70" s="29"/>
-      <c r="N70" s="29"/>
-      <c r="O70" s="29"/>
-      <c r="P70" s="29"/>
-      <c r="Q70" s="29"/>
-      <c r="R70" s="29"/>
-      <c r="S70" s="29"/>
-      <c r="T70" s="29"/>
-      <c r="U70" s="29"/>
-      <c r="V70" s="29"/>
-      <c r="W70" s="29"/>
-      <c r="X70" s="29"/>
-      <c r="Y70" s="29"/>
-      <c r="Z70" s="29"/>
-      <c r="AA70" s="29"/>
-      <c r="AB70" s="29"/>
-      <c r="AC70" s="29"/>
-      <c r="AD70" s="29"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+      <c r="N70" s="30"/>
+      <c r="O70" s="30"/>
+      <c r="P70" s="30"/>
+      <c r="Q70" s="30"/>
+      <c r="R70" s="30"/>
+      <c r="S70" s="30"/>
+      <c r="T70" s="30"/>
+      <c r="U70" s="30"/>
+      <c r="V70" s="30"/>
+      <c r="W70" s="30"/>
+      <c r="X70" s="30"/>
+      <c r="Y70" s="30"/>
+      <c r="Z70" s="30"/>
+      <c r="AA70" s="30"/>
+      <c r="AB70" s="30"/>
+      <c r="AC70" s="30"/>
+      <c r="AD70" s="30"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="30" t="s">
+      <c r="A71" s="31" t="s">
         <v>417</v>
       </c>
-      <c r="B71" s="34"/>
-      <c r="C71" s="32">
+      <c r="B71" s="35"/>
+      <c r="C71" s="33">
         <v>65.18</v>
       </c>
-      <c r="D71" s="32">
+      <c r="D71" s="33">
         <v>7.78</v>
       </c>
-      <c r="E71" s="32">
+      <c r="E71" s="33">
         <v>5.94</v>
       </c>
-      <c r="F71" s="34"/>
-      <c r="G71" s="32">
+      <c r="F71" s="35"/>
+      <c r="G71" s="33">
         <v>9.94</v>
       </c>
-      <c r="H71" s="32">
+      <c r="H71" s="33">
         <v>19.02</v>
       </c>
-      <c r="I71" s="34"/>
-      <c r="J71" s="32">
+      <c r="I71" s="35"/>
+      <c r="J71" s="33">
         <v>18.06</v>
       </c>
-      <c r="K71" s="32">
+      <c r="K71" s="33">
         <v>5.24</v>
       </c>
-      <c r="L71" s="34"/>
-      <c r="M71" s="34"/>
-      <c r="N71" s="32">
+      <c r="L71" s="35"/>
+      <c r="M71" s="35"/>
+      <c r="N71" s="33">
         <v>5.44</v>
       </c>
-      <c r="O71" s="32">
+      <c r="O71" s="33">
         <v>20.78</v>
       </c>
-      <c r="P71" s="32">
+      <c r="P71" s="33">
         <v>2.72</v>
       </c>
-      <c r="Q71" s="34"/>
-      <c r="R71" s="34"/>
-      <c r="S71" s="32">
+      <c r="Q71" s="35"/>
+      <c r="R71" s="35"/>
+      <c r="S71" s="33">
         <v>9.92</v>
       </c>
-      <c r="T71" s="31">
+      <c r="T71" s="32">
         <v>138.07</v>
       </c>
-      <c r="U71" s="33">
+      <c r="U71" s="34">
         <v>-1.12</v>
       </c>
-      <c r="V71" s="32">
+      <c r="V71" s="33">
         <v>3.46</v>
       </c>
-      <c r="W71" s="32">
+      <c r="W71" s="33">
         <v>5.24</v>
       </c>
-      <c r="X71" s="32">
+      <c r="X71" s="33">
         <v>3.92</v>
       </c>
-      <c r="Y71" s="32">
+      <c r="Y71" s="33">
         <v>23.42</v>
       </c>
-      <c r="Z71" s="34"/>
-      <c r="AA71" s="34"/>
-      <c r="AB71" s="32">
+      <c r="Z71" s="35"/>
+      <c r="AA71" s="35"/>
+      <c r="AB71" s="33">
         <v>18.19</v>
       </c>
-      <c r="AC71" s="32">
+      <c r="AC71" s="33">
         <v>13.2</v>
       </c>
-      <c r="AD71" s="32">
+      <c r="AD71" s="33">
         <v>14.38</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="30" t="s">
+      <c r="A72" s="31" t="s">
         <v>418</v>
       </c>
-      <c r="B72" s="31">
+      <c r="B72" s="32">
         <v>785.49</v>
       </c>
-      <c r="C72" s="32">
+      <c r="C72" s="33">
         <v>11.9</v>
       </c>
-      <c r="D72" s="32">
+      <c r="D72" s="33">
         <v>11.63</v>
       </c>
-      <c r="E72" s="32">
+      <c r="E72" s="33">
         <v>34.85</v>
       </c>
-      <c r="F72" s="32">
+      <c r="F72" s="33">
         <v>91.5</v>
       </c>
-      <c r="G72" s="32">
+      <c r="G72" s="33">
         <v>21.48</v>
       </c>
-      <c r="H72" s="34"/>
-      <c r="I72" s="34"/>
-      <c r="J72" s="32">
+      <c r="H72" s="35"/>
+      <c r="I72" s="35"/>
+      <c r="J72" s="33">
         <v>80.68</v>
       </c>
-      <c r="K72" s="31">
+      <c r="K72" s="32">
         <v>5779.75</v>
       </c>
-      <c r="L72" s="32">
+      <c r="L72" s="33">
         <v>35.66</v>
       </c>
-      <c r="M72" s="34"/>
-      <c r="N72" s="34"/>
-      <c r="O72" s="34"/>
-      <c r="P72" s="34"/>
-      <c r="Q72" s="34"/>
-      <c r="R72" s="32">
+      <c r="M72" s="35"/>
+      <c r="N72" s="35"/>
+      <c r="O72" s="35"/>
+      <c r="P72" s="35"/>
+      <c r="Q72" s="35"/>
+      <c r="R72" s="33">
         <v>7.58</v>
       </c>
-      <c r="S72" s="32">
+      <c r="S72" s="33">
         <v>4.69</v>
       </c>
-      <c r="T72" s="32">
+      <c r="T72" s="33">
         <v>4.19</v>
       </c>
-      <c r="U72" s="32">
+      <c r="U72" s="33">
         <v>4.0</v>
       </c>
-      <c r="V72" s="32">
+      <c r="V72" s="33">
         <v>17.21</v>
       </c>
-      <c r="W72" s="32">
+      <c r="W72" s="33">
         <v>86.77</v>
       </c>
-      <c r="X72" s="34"/>
-      <c r="Y72" s="34"/>
-      <c r="Z72" s="34"/>
-      <c r="AA72" s="34"/>
-      <c r="AB72" s="34"/>
-      <c r="AC72" s="34"/>
-      <c r="AD72" s="34"/>
+      <c r="X72" s="35"/>
+      <c r="Y72" s="35"/>
+      <c r="Z72" s="35"/>
+      <c r="AA72" s="35"/>
+      <c r="AB72" s="35"/>
+      <c r="AC72" s="35"/>
+      <c r="AD72" s="35"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>

--- a/data/cox_xlsx/SKAKO.CO.xlsx
+++ b/data/cox_xlsx/SKAKO.CO.xlsx
@@ -1407,7 +1407,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1490,6 +1490,9 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -10442,13 +10445,34 @@
       <c r="N46" s="18">
         <v>62.86</v>
       </c>
-      <c r="O46" s="19"/>
-      <c r="P46" s="19"/>
-      <c r="Q46" s="19"/>
-      <c r="R46" s="19"/>
-      <c r="S46" s="19"/>
-      <c r="T46" s="19"/>
-      <c r="U46" s="19"/>
+      <c r="O46" s="28">
+        <f t="shared" ref="O46:U46" si="1">O44+O53+O56+O58+O43</f>
+        <v>53.29</v>
+      </c>
+      <c r="P46" s="28">
+        <f t="shared" si="1"/>
+        <v>35.95</v>
+      </c>
+      <c r="Q46" s="28">
+        <f t="shared" si="1"/>
+        <v>68.32</v>
+      </c>
+      <c r="R46" s="28">
+        <f t="shared" si="1"/>
+        <v>68.63</v>
+      </c>
+      <c r="S46" s="28">
+        <f t="shared" si="1"/>
+        <v>19.24</v>
+      </c>
+      <c r="T46" s="28">
+        <f t="shared" si="1"/>
+        <v>21.1</v>
+      </c>
+      <c r="U46" s="28">
+        <f t="shared" si="1"/>
+        <v>24.4</v>
+      </c>
       <c r="V46" s="18">
         <v>34.02</v>
       </c>
@@ -18182,7 +18206,7 @@
       <c r="A75" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="B75" s="28">
+      <c r="B75" s="29">
         <v>-144.81</v>
       </c>
       <c r="C75" s="25">
@@ -18236,10 +18260,10 @@
       <c r="S75" s="25">
         <v>-49.27</v>
       </c>
-      <c r="T75" s="28">
+      <c r="T75" s="29">
         <v>-368.65</v>
       </c>
-      <c r="U75" s="28">
+      <c r="U75" s="29">
         <v>-351.62</v>
       </c>
       <c r="V75" s="25">
@@ -18600,7 +18624,7 @@
       <c r="A83" s="16" t="s">
         <v>343</v>
       </c>
-      <c r="B83" s="28">
+      <c r="B83" s="29">
         <v>-204.42</v>
       </c>
       <c r="C83" s="17">
@@ -18654,7 +18678,7 @@
       <c r="S83" s="25">
         <v>-1.61</v>
       </c>
-      <c r="T83" s="28">
+      <c r="T83" s="29">
         <v>-457.29</v>
       </c>
       <c r="U83" s="17">
@@ -20567,3430 +20591,3430 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="30" t="s">
         <v>368</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="30"/>
-      <c r="AC20" s="30"/>
-      <c r="AD20" s="30"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="31"/>
+      <c r="Z20" s="31"/>
+      <c r="AA20" s="31"/>
+      <c r="AB20" s="31"/>
+      <c r="AC20" s="31"/>
+      <c r="AD20" s="31"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="32" t="s">
         <v>368</v>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="33">
         <v>462.82</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="34">
         <v>97.62</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="33">
         <v>203.2</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="33">
         <v>182.49</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="33">
         <v>194.46</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="33">
         <v>161.58</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="33">
         <v>135.59</v>
       </c>
-      <c r="I21" s="32">
+      <c r="I21" s="33">
         <v>270.94</v>
       </c>
-      <c r="J21" s="32">
+      <c r="J21" s="33">
         <v>242.93</v>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="33">
         <v>152.38</v>
       </c>
-      <c r="L21" s="32">
+      <c r="L21" s="33">
         <v>116.88</v>
       </c>
-      <c r="M21" s="33">
+      <c r="M21" s="34">
         <v>88.4</v>
       </c>
-      <c r="N21" s="33">
+      <c r="N21" s="34">
         <v>86.3</v>
       </c>
-      <c r="O21" s="33">
+      <c r="O21" s="34">
         <v>84.2</v>
       </c>
-      <c r="P21" s="33">
+      <c r="P21" s="34">
         <v>99.0</v>
       </c>
-      <c r="Q21" s="32">
+      <c r="Q21" s="33">
         <v>127.41</v>
       </c>
-      <c r="R21" s="32">
+      <c r="R21" s="33">
         <v>176.1</v>
       </c>
-      <c r="S21" s="32">
+      <c r="S21" s="33">
         <v>170.1</v>
       </c>
-      <c r="T21" s="32">
+      <c r="T21" s="33">
         <v>395.27</v>
       </c>
-      <c r="U21" s="34">
+      <c r="U21" s="35">
         <v>-79.18</v>
       </c>
-      <c r="V21" s="32">
+      <c r="V21" s="33">
         <v>312.57</v>
       </c>
-      <c r="W21" s="32">
+      <c r="W21" s="33">
         <v>581.68</v>
       </c>
-      <c r="X21" s="32">
+      <c r="X21" s="33">
         <v>570.48</v>
       </c>
-      <c r="Y21" s="32">
+      <c r="Y21" s="33">
         <v>350.37</v>
       </c>
-      <c r="Z21" s="32">
+      <c r="Z21" s="33">
         <v>2145.28</v>
       </c>
-      <c r="AA21" s="32">
+      <c r="AA21" s="33">
         <v>1829.76</v>
       </c>
-      <c r="AB21" s="32">
+      <c r="AB21" s="33">
         <v>720.33</v>
       </c>
-      <c r="AC21" s="32">
+      <c r="AC21" s="33">
         <v>572.79</v>
       </c>
-      <c r="AD21" s="32">
+      <c r="AD21" s="33">
         <v>190.83</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="32" t="s">
         <v>369</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="33">
         <v>244.94</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="33">
         <v>181.69</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="33">
         <v>181.23</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="33">
         <v>189.39</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="33">
         <v>215.82</v>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="33">
         <v>196.8</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="33">
         <v>191.18</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="33">
         <v>184.48</v>
       </c>
-      <c r="J22" s="32">
+      <c r="J22" s="33">
         <v>141.87</v>
       </c>
-      <c r="K22" s="32">
+      <c r="K22" s="33">
         <v>118.96</v>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="33">
         <v>106.51</v>
       </c>
-      <c r="M22" s="32">
+      <c r="M22" s="33">
         <v>102.11</v>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="33">
         <v>100.91</v>
       </c>
-      <c r="O22" s="32">
+      <c r="O22" s="33">
         <v>121.71</v>
       </c>
-      <c r="P22" s="32">
+      <c r="P22" s="33">
         <v>180.19</v>
       </c>
-      <c r="Q22" s="32">
+      <c r="Q22" s="33">
         <v>154.59</v>
       </c>
-      <c r="R22" s="32">
+      <c r="R22" s="33">
         <v>224.69</v>
       </c>
-      <c r="S22" s="32">
+      <c r="S22" s="33">
         <v>264.37</v>
       </c>
-      <c r="T22" s="32">
+      <c r="T22" s="33">
         <v>367.43</v>
       </c>
-      <c r="U22" s="32">
+      <c r="U22" s="33">
         <v>349.82</v>
       </c>
-      <c r="V22" s="32">
+      <c r="V22" s="33">
         <v>807.59</v>
       </c>
-      <c r="W22" s="32">
+      <c r="W22" s="33">
         <v>1137.62</v>
       </c>
-      <c r="X22" s="32">
+      <c r="X22" s="33">
         <v>1006.51</v>
       </c>
-      <c r="Y22" s="32">
+      <c r="Y22" s="33">
         <v>1090.32</v>
       </c>
-      <c r="Z22" s="32">
+      <c r="Z22" s="33">
         <v>1093.22</v>
       </c>
-      <c r="AA22" s="35"/>
-      <c r="AB22" s="35"/>
-      <c r="AC22" s="35"/>
-      <c r="AD22" s="35"/>
+      <c r="AA22" s="36"/>
+      <c r="AB22" s="36"/>
+      <c r="AC22" s="36"/>
+      <c r="AD22" s="36"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="30" t="s">
         <v>370</v>
       </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="30"/>
-      <c r="AC23" s="30"/>
-      <c r="AD23" s="30"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="31"/>
+      <c r="Z23" s="31"/>
+      <c r="AA23" s="31"/>
+      <c r="AB23" s="31"/>
+      <c r="AC23" s="31"/>
+      <c r="AD23" s="31"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="32" t="s">
         <v>370</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="33">
         <v>403.96</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="33">
         <v>303.91</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="33">
         <v>173.59</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="33">
         <v>146.15</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="33">
         <v>137.87</v>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="33">
         <v>118.93</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="33">
         <v>128.36</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="33">
         <v>236.7</v>
       </c>
-      <c r="J24" s="32">
+      <c r="J24" s="33">
         <v>222.39</v>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="33">
         <v>113.32</v>
       </c>
-      <c r="L24" s="33">
+      <c r="L24" s="34">
         <v>52.04</v>
       </c>
-      <c r="M24" s="33">
+      <c r="M24" s="34">
         <v>60.89</v>
       </c>
-      <c r="N24" s="33">
+      <c r="N24" s="34">
         <v>46.45</v>
       </c>
-      <c r="O24" s="33">
+      <c r="O24" s="34">
         <v>27.92</v>
       </c>
-      <c r="P24" s="33">
+      <c r="P24" s="34">
         <v>40.47</v>
       </c>
-      <c r="Q24" s="33">
+      <c r="Q24" s="34">
         <v>69.96</v>
       </c>
-      <c r="R24" s="32">
+      <c r="R24" s="33">
         <v>199.07</v>
       </c>
-      <c r="S24" s="32">
+      <c r="S24" s="33">
         <v>267.24</v>
       </c>
-      <c r="T24" s="32">
+      <c r="T24" s="33">
         <v>524.23</v>
       </c>
-      <c r="U24" s="32">
+      <c r="U24" s="33">
         <v>391.52</v>
       </c>
-      <c r="V24" s="32">
+      <c r="V24" s="33">
         <v>601.43</v>
       </c>
-      <c r="W24" s="32">
+      <c r="W24" s="33">
         <v>437.87</v>
       </c>
-      <c r="X24" s="32">
+      <c r="X24" s="33">
         <v>317.38</v>
       </c>
-      <c r="Y24" s="32">
+      <c r="Y24" s="33">
         <v>357.37</v>
       </c>
-      <c r="Z24" s="32">
+      <c r="Z24" s="33">
         <v>942.78</v>
       </c>
-      <c r="AA24" s="32">
+      <c r="AA24" s="33">
         <v>848.99</v>
       </c>
-      <c r="AB24" s="32">
+      <c r="AB24" s="33">
         <v>701.3</v>
       </c>
-      <c r="AC24" s="32">
+      <c r="AC24" s="33">
         <v>414.76</v>
       </c>
-      <c r="AD24" s="32">
+      <c r="AD24" s="33">
         <v>156.5</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="32" t="s">
         <v>371</v>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="33">
         <v>248.73</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="33">
         <v>186.77</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="33">
         <v>145.69</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="33">
         <v>154.15</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="33">
         <v>181.84</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="33">
         <v>167.59</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="33">
         <v>156.18</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="33">
         <v>144.52</v>
       </c>
-      <c r="J25" s="32">
+      <c r="J25" s="33">
         <v>101.36</v>
       </c>
-      <c r="K25" s="33">
+      <c r="K25" s="34">
         <v>66.75</v>
       </c>
-      <c r="L25" s="33">
+      <c r="L25" s="34">
         <v>51.01</v>
       </c>
-      <c r="M25" s="33">
+      <c r="M25" s="34">
         <v>51.42</v>
       </c>
-      <c r="N25" s="33">
+      <c r="N25" s="34">
         <v>64.59</v>
       </c>
-      <c r="O25" s="32">
+      <c r="O25" s="33">
         <v>110.74</v>
       </c>
-      <c r="P25" s="32">
+      <c r="P25" s="33">
         <v>204.9</v>
       </c>
-      <c r="Q25" s="32">
+      <c r="Q25" s="33">
         <v>291.44</v>
       </c>
-      <c r="R25" s="32">
+      <c r="R25" s="33">
         <v>466.31</v>
       </c>
-      <c r="S25" s="32">
+      <c r="S25" s="33">
         <v>430.5</v>
       </c>
-      <c r="T25" s="32">
+      <c r="T25" s="33">
         <v>462.59</v>
       </c>
-      <c r="U25" s="32">
+      <c r="U25" s="33">
         <v>418.52</v>
       </c>
-      <c r="V25" s="32">
+      <c r="V25" s="33">
         <v>540.71</v>
       </c>
-      <c r="W25" s="32">
+      <c r="W25" s="33">
         <v>603.8</v>
       </c>
-      <c r="X25" s="32">
+      <c r="X25" s="33">
         <v>564.09</v>
       </c>
-      <c r="Y25" s="32">
+      <c r="Y25" s="33">
         <v>630.25</v>
       </c>
-      <c r="Z25" s="32">
+      <c r="Z25" s="33">
         <v>609.28</v>
       </c>
-      <c r="AA25" s="35"/>
-      <c r="AB25" s="35"/>
-      <c r="AC25" s="35"/>
-      <c r="AD25" s="35"/>
+      <c r="AA25" s="36"/>
+      <c r="AB25" s="36"/>
+      <c r="AC25" s="36"/>
+      <c r="AD25" s="36"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="30" t="s">
         <v>372</v>
       </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="30"/>
-      <c r="AC26" s="30"/>
-      <c r="AD26" s="30"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="31"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="31"/>
+      <c r="AB26" s="31"/>
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="31"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="32" t="s">
         <v>373</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="33">
         <v>128.14</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="34">
         <v>97.83</v>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="34">
         <v>55.88</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="34">
         <v>47.05</v>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="34">
         <v>44.38</v>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="34">
         <v>38.28</v>
       </c>
-      <c r="H27" s="33">
+      <c r="H27" s="34">
         <v>41.32</v>
       </c>
-      <c r="I27" s="33">
+      <c r="I27" s="34">
         <v>76.2</v>
       </c>
-      <c r="J27" s="33">
+      <c r="J27" s="34">
         <v>71.59</v>
       </c>
-      <c r="K27" s="33">
+      <c r="K27" s="34">
         <v>36.48</v>
       </c>
-      <c r="L27" s="33">
+      <c r="L27" s="34">
         <v>16.75</v>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="34">
         <v>19.6</v>
       </c>
-      <c r="N27" s="33">
+      <c r="N27" s="34">
         <v>19.07</v>
       </c>
-      <c r="O27" s="33">
+      <c r="O27" s="34">
         <v>11.46</v>
       </c>
-      <c r="P27" s="33">
+      <c r="P27" s="34">
         <v>17.8</v>
       </c>
-      <c r="Q27" s="33">
+      <c r="Q27" s="34">
         <v>30.77</v>
       </c>
-      <c r="R27" s="33">
+      <c r="R27" s="34">
         <v>87.54</v>
       </c>
-      <c r="S27" s="32">
+      <c r="S27" s="33">
         <v>117.52</v>
       </c>
-      <c r="T27" s="32">
+      <c r="T27" s="33">
         <v>230.53</v>
       </c>
-      <c r="U27" s="32">
+      <c r="U27" s="33">
         <v>172.17</v>
       </c>
-      <c r="V27" s="32">
+      <c r="V27" s="33">
         <v>264.48</v>
       </c>
-      <c r="W27" s="32">
+      <c r="W27" s="33">
         <v>192.56</v>
       </c>
-      <c r="X27" s="32">
+      <c r="X27" s="33">
         <v>139.57</v>
       </c>
-      <c r="Y27" s="32">
+      <c r="Y27" s="33">
         <v>108.57</v>
       </c>
-      <c r="Z27" s="32">
+      <c r="Z27" s="33">
         <v>238.47</v>
       </c>
-      <c r="AA27" s="32">
+      <c r="AA27" s="33">
         <v>192.21</v>
       </c>
-      <c r="AB27" s="32">
+      <c r="AB27" s="33">
         <v>158.77</v>
       </c>
-      <c r="AC27" s="32">
+      <c r="AC27" s="33">
         <v>170.33</v>
       </c>
-      <c r="AD27" s="32">
+      <c r="AD27" s="33">
         <v>152.68</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="32" t="s">
         <v>374</v>
       </c>
-      <c r="B28" s="33">
+      <c r="B28" s="34">
         <v>79.69</v>
       </c>
-      <c r="C28" s="33">
+      <c r="C28" s="34">
         <v>60.13</v>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="34">
         <v>46.9</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="34">
         <v>49.62</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="34">
         <v>58.54</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="34">
         <v>53.95</v>
       </c>
-      <c r="H28" s="33">
+      <c r="H28" s="34">
         <v>50.28</v>
       </c>
-      <c r="I28" s="33">
+      <c r="I28" s="34">
         <v>46.52</v>
       </c>
-      <c r="J28" s="33">
+      <c r="J28" s="34">
         <v>33.65</v>
       </c>
-      <c r="K28" s="33">
+      <c r="K28" s="34">
         <v>23.17</v>
       </c>
-      <c r="L28" s="33">
+      <c r="L28" s="34">
         <v>19.12</v>
       </c>
-      <c r="M28" s="33">
+      <c r="M28" s="34">
         <v>20.69</v>
       </c>
-      <c r="N28" s="33">
+      <c r="N28" s="34">
         <v>27.98</v>
       </c>
-      <c r="O28" s="33">
+      <c r="O28" s="34">
         <v>48.54</v>
       </c>
-      <c r="P28" s="33">
+      <c r="P28" s="34">
         <v>90.11</v>
       </c>
-      <c r="Q28" s="32">
+      <c r="Q28" s="33">
         <v>128.16</v>
       </c>
-      <c r="R28" s="32">
+      <c r="R28" s="33">
         <v>205.06</v>
       </c>
-      <c r="S28" s="32">
+      <c r="S28" s="33">
         <v>189.31</v>
       </c>
-      <c r="T28" s="32">
+      <c r="T28" s="33">
         <v>203.43</v>
       </c>
-      <c r="U28" s="32">
+      <c r="U28" s="33">
         <v>174.34</v>
       </c>
-      <c r="V28" s="32">
+      <c r="V28" s="33">
         <v>192.5</v>
       </c>
-      <c r="W28" s="32">
+      <c r="W28" s="33">
         <v>181.86</v>
       </c>
-      <c r="X28" s="32">
+      <c r="X28" s="33">
         <v>150.74</v>
       </c>
-      <c r="Y28" s="32">
+      <c r="Y28" s="33">
         <v>168.29</v>
       </c>
-      <c r="Z28" s="32">
+      <c r="Z28" s="33">
         <v>182.45</v>
       </c>
-      <c r="AA28" s="35"/>
-      <c r="AB28" s="35"/>
-      <c r="AC28" s="35"/>
-      <c r="AD28" s="35"/>
+      <c r="AA28" s="36"/>
+      <c r="AB28" s="36"/>
+      <c r="AC28" s="36"/>
+      <c r="AD28" s="36"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="30" t="s">
         <v>375</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
-      <c r="AC29" s="30"/>
-      <c r="AD29" s="30"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="31"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
+      <c r="Y29" s="31"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="31"/>
+      <c r="AB29" s="31"/>
+      <c r="AC29" s="31"/>
+      <c r="AD29" s="31"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="32" t="s">
         <v>376</v>
       </c>
-      <c r="B30" s="36">
+      <c r="B30" s="37">
         <v>-14.66</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="38">
         <v>0.48</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="38">
         <v>14.6</v>
       </c>
-      <c r="E30" s="37">
+      <c r="E30" s="38">
         <v>21.17</v>
       </c>
-      <c r="F30" s="36">
+      <c r="F30" s="37">
         <v>-3.89</v>
       </c>
-      <c r="G30" s="37">
+      <c r="G30" s="38">
         <v>13.76</v>
       </c>
-      <c r="H30" s="37">
+      <c r="H30" s="38">
         <v>5.59</v>
       </c>
-      <c r="I30" s="36">
+      <c r="I30" s="37">
         <v>-9.32</v>
       </c>
-      <c r="J30" s="37">
+      <c r="J30" s="38">
         <v>6.09</v>
       </c>
-      <c r="K30" s="37">
+      <c r="K30" s="38">
         <v>25.89</v>
       </c>
-      <c r="L30" s="36">
+      <c r="L30" s="37">
         <v>-63.25</v>
       </c>
-      <c r="M30" s="36">
+      <c r="M30" s="37">
         <v>-34.61</v>
       </c>
-      <c r="N30" s="37">
+      <c r="N30" s="38">
         <v>26.94</v>
       </c>
-      <c r="O30" s="37">
+      <c r="O30" s="38">
         <v>15.78</v>
       </c>
-      <c r="P30" s="37">
+      <c r="P30" s="38">
         <v>91.78</v>
       </c>
-      <c r="Q30" s="36">
+      <c r="Q30" s="37">
         <v>-133.78</v>
       </c>
-      <c r="R30" s="36">
+      <c r="R30" s="37">
         <v>-34.54</v>
       </c>
-      <c r="S30" s="37">
+      <c r="S30" s="38">
         <v>6.41</v>
       </c>
-      <c r="T30" s="37">
+      <c r="T30" s="38">
         <v>0.55</v>
       </c>
-      <c r="U30" s="37">
+      <c r="U30" s="38">
         <v>18.02</v>
       </c>
-      <c r="V30" s="37">
+      <c r="V30" s="38">
         <v>15.04</v>
       </c>
-      <c r="W30" s="37">
+      <c r="W30" s="38">
         <v>25.35</v>
       </c>
-      <c r="X30" s="37">
+      <c r="X30" s="38">
         <v>45.83</v>
       </c>
-      <c r="Y30" s="37">
+      <c r="Y30" s="38">
         <v>7.58</v>
       </c>
-      <c r="Z30" s="36">
+      <c r="Z30" s="37">
         <v>-12.91</v>
       </c>
-      <c r="AA30" s="36">
+      <c r="AA30" s="37">
         <v>-7.69</v>
       </c>
-      <c r="AB30" s="37">
+      <c r="AB30" s="38">
         <v>13.72</v>
       </c>
-      <c r="AC30" s="37">
+      <c r="AC30" s="38">
         <v>9.56</v>
       </c>
-      <c r="AD30" s="37">
+      <c r="AD30" s="38">
         <v>3.26</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="32" t="s">
         <v>377</v>
       </c>
-      <c r="B31" s="37">
+      <c r="B31" s="38">
         <v>0.14</v>
       </c>
-      <c r="C31" s="37">
+      <c r="C31" s="38">
         <v>8.12</v>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="38">
         <v>10.64</v>
       </c>
-      <c r="E31" s="37">
+      <c r="E31" s="38">
         <v>3.55</v>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="38">
         <v>1.31</v>
       </c>
-      <c r="G31" s="37">
+      <c r="G31" s="38">
         <v>5.51</v>
       </c>
-      <c r="H31" s="36">
+      <c r="H31" s="37">
         <v>-0.76</v>
       </c>
-      <c r="I31" s="36">
+      <c r="I31" s="37">
         <v>-5.26</v>
       </c>
-      <c r="J31" s="37">
+      <c r="J31" s="38">
         <v>0.97</v>
       </c>
-      <c r="K31" s="36">
+      <c r="K31" s="37">
         <v>-0.55</v>
       </c>
-      <c r="L31" s="37">
+      <c r="L31" s="38">
         <v>9.89</v>
       </c>
-      <c r="M31" s="36">
+      <c r="M31" s="37">
         <v>-22.05</v>
       </c>
-      <c r="N31" s="36">
+      <c r="N31" s="37">
         <v>-26.4</v>
       </c>
-      <c r="O31" s="36">
+      <c r="O31" s="37">
         <v>-15.28</v>
       </c>
-      <c r="P31" s="36">
+      <c r="P31" s="37">
         <v>-8.41</v>
       </c>
-      <c r="Q31" s="36">
+      <c r="Q31" s="37">
         <v>-3.98</v>
       </c>
-      <c r="R31" s="37">
+      <c r="R31" s="38">
         <v>6.35</v>
       </c>
-      <c r="S31" s="37">
+      <c r="S31" s="38">
         <v>13.09</v>
       </c>
-      <c r="T31" s="37">
+      <c r="T31" s="38">
         <v>18.95</v>
       </c>
-      <c r="U31" s="37">
+      <c r="U31" s="38">
         <v>22.25</v>
       </c>
-      <c r="V31" s="37">
+      <c r="V31" s="38">
         <v>14.32</v>
       </c>
-      <c r="W31" s="37">
+      <c r="W31" s="38">
         <v>9.28</v>
       </c>
-      <c r="X31" s="37">
+      <c r="X31" s="38">
         <v>6.47</v>
       </c>
-      <c r="Y31" s="36">
+      <c r="Y31" s="37">
         <v>-0.05</v>
       </c>
-      <c r="Z31" s="36">
+      <c r="Z31" s="37">
         <v>-0.42</v>
       </c>
-      <c r="AA31" s="37"/>
-      <c r="AB31" s="37"/>
-      <c r="AC31" s="37"/>
-      <c r="AD31" s="37"/>
+      <c r="AA31" s="38"/>
+      <c r="AB31" s="38"/>
+      <c r="AC31" s="38"/>
+      <c r="AD31" s="38"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="30" t="s">
         <v>378</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
-      <c r="W32" s="30"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="30"/>
-      <c r="AC32" s="30"/>
-      <c r="AD32" s="30"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
+      <c r="V32" s="31"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="31"/>
+      <c r="Y32" s="31"/>
+      <c r="Z32" s="31"/>
+      <c r="AA32" s="31"/>
+      <c r="AB32" s="31"/>
+      <c r="AC32" s="31"/>
+      <c r="AD32" s="31"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="B33" s="37">
+      <c r="B33" s="38">
         <v>6.16</v>
       </c>
-      <c r="C33" s="37">
+      <c r="C33" s="38">
         <v>7.67</v>
       </c>
-      <c r="D33" s="37">
+      <c r="D33" s="38">
         <v>10.09</v>
       </c>
-      <c r="E33" s="37">
+      <c r="E33" s="38">
         <v>8.59</v>
       </c>
-      <c r="F33" s="37">
+      <c r="F33" s="38">
         <v>6.34</v>
       </c>
-      <c r="G33" s="37">
+      <c r="G33" s="38">
         <v>0.0</v>
       </c>
-      <c r="H33" s="37">
+      <c r="H33" s="38">
         <v>0.0</v>
       </c>
-      <c r="I33" s="37">
+      <c r="I33" s="38">
         <v>0.0</v>
       </c>
-      <c r="J33" s="37">
+      <c r="J33" s="38">
         <v>0.0</v>
       </c>
-      <c r="K33" s="37">
+      <c r="K33" s="38">
         <v>0.0</v>
       </c>
-      <c r="L33" s="37">
+      <c r="L33" s="38">
         <v>0.0</v>
       </c>
-      <c r="M33" s="37">
+      <c r="M33" s="38">
         <v>0.0</v>
       </c>
-      <c r="N33" s="37">
+      <c r="N33" s="38">
         <v>0.0</v>
       </c>
-      <c r="O33" s="37">
+      <c r="O33" s="38">
         <v>0.0</v>
       </c>
-      <c r="P33" s="37">
+      <c r="P33" s="38">
         <v>0.0</v>
       </c>
-      <c r="Q33" s="37">
+      <c r="Q33" s="38">
         <v>0.0</v>
       </c>
-      <c r="R33" s="37">
+      <c r="R33" s="38">
         <v>8.05</v>
       </c>
-      <c r="S33" s="37">
+      <c r="S33" s="38">
         <v>13.04</v>
       </c>
-      <c r="T33" s="37">
+      <c r="T33" s="38">
         <v>86.17</v>
       </c>
-      <c r="U33" s="37">
+      <c r="U33" s="38">
         <v>64.93</v>
       </c>
-      <c r="V33" s="37">
+      <c r="V33" s="38">
         <v>12.07</v>
       </c>
-      <c r="W33" s="37">
+      <c r="W33" s="38">
         <v>2.7</v>
       </c>
-      <c r="X33" s="37">
+      <c r="X33" s="38">
         <v>3.24</v>
       </c>
-      <c r="Y33" s="37">
+      <c r="Y33" s="38">
         <v>4.55</v>
       </c>
-      <c r="Z33" s="37">
+      <c r="Z33" s="38">
         <v>2.23</v>
       </c>
-      <c r="AA33" s="37">
+      <c r="AA33" s="38">
         <v>1.35</v>
       </c>
-      <c r="AB33" s="37">
+      <c r="AB33" s="38">
         <v>1.58</v>
       </c>
-      <c r="AC33" s="37">
+      <c r="AC33" s="38">
         <v>1.14</v>
       </c>
-      <c r="AD33" s="37">
+      <c r="AD33" s="38">
         <v>1.07</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="32" t="s">
         <v>380</v>
       </c>
-      <c r="B34" s="37">
+      <c r="B34" s="38">
         <v>7.53</v>
       </c>
-      <c r="C34" s="37">
+      <c r="C34" s="38">
         <v>6.99</v>
       </c>
-      <c r="D34" s="37">
+      <c r="D34" s="38">
         <v>5.41</v>
       </c>
-      <c r="E34" s="37">
+      <c r="E34" s="38">
         <v>2.71</v>
       </c>
-      <c r="F34" s="37">
+      <c r="F34" s="38">
         <v>0.96</v>
       </c>
-      <c r="G34" s="37">
+      <c r="G34" s="38">
         <v>0.0</v>
       </c>
-      <c r="H34" s="37">
+      <c r="H34" s="38">
         <v>0.0</v>
       </c>
-      <c r="I34" s="37">
+      <c r="I34" s="38">
         <v>0.0</v>
       </c>
-      <c r="J34" s="37">
+      <c r="J34" s="38">
         <v>0.0</v>
       </c>
-      <c r="K34" s="37">
+      <c r="K34" s="38">
         <v>0.0</v>
       </c>
-      <c r="L34" s="37">
+      <c r="L34" s="38">
         <v>0.0</v>
       </c>
-      <c r="M34" s="37">
+      <c r="M34" s="38">
         <v>0.0</v>
       </c>
-      <c r="N34" s="37">
+      <c r="N34" s="38">
         <v>3.8</v>
       </c>
-      <c r="O34" s="37">
+      <c r="O34" s="38">
         <v>8.49</v>
       </c>
-      <c r="P34" s="37">
+      <c r="P34" s="38">
         <v>46.35</v>
       </c>
-      <c r="Q34" s="37">
+      <c r="Q34" s="38">
         <v>52.92</v>
       </c>
-      <c r="R34" s="37">
+      <c r="R34" s="38">
         <v>42.37</v>
       </c>
-      <c r="S34" s="37">
+      <c r="S34" s="38">
         <v>37.34</v>
       </c>
-      <c r="T34" s="37">
+      <c r="T34" s="38">
         <v>34.98</v>
       </c>
-      <c r="U34" s="37">
+      <c r="U34" s="38">
         <v>18.06</v>
       </c>
-      <c r="V34" s="37">
+      <c r="V34" s="38">
         <v>5.46</v>
       </c>
-      <c r="W34" s="37">
+      <c r="W34" s="38">
         <v>2.6</v>
       </c>
-      <c r="X34" s="37">
+      <c r="X34" s="38">
         <v>2.41</v>
       </c>
-      <c r="Y34" s="37">
+      <c r="Y34" s="38">
         <v>2.0</v>
       </c>
-      <c r="Z34" s="37">
+      <c r="Z34" s="38">
         <v>1.53</v>
       </c>
-      <c r="AA34" s="37"/>
-      <c r="AB34" s="37"/>
-      <c r="AC34" s="37"/>
-      <c r="AD34" s="37"/>
+      <c r="AA34" s="38"/>
+      <c r="AB34" s="38"/>
+      <c r="AC34" s="38"/>
+      <c r="AD34" s="38"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="32" t="s">
         <v>381</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="38">
         <v>6.16</v>
       </c>
-      <c r="C35" s="37">
+      <c r="C35" s="38">
         <v>7.67</v>
       </c>
-      <c r="D35" s="37">
+      <c r="D35" s="38">
         <v>10.09</v>
       </c>
-      <c r="E35" s="37">
+      <c r="E35" s="38">
         <v>8.59</v>
       </c>
-      <c r="F35" s="37">
+      <c r="F35" s="38">
         <v>6.34</v>
       </c>
-      <c r="G35" s="37">
+      <c r="G35" s="38">
         <v>0.0</v>
       </c>
-      <c r="H35" s="37">
+      <c r="H35" s="38">
         <v>0.0</v>
       </c>
-      <c r="I35" s="37">
+      <c r="I35" s="38">
         <v>0.0</v>
       </c>
-      <c r="J35" s="37">
+      <c r="J35" s="38">
         <v>0.0</v>
       </c>
-      <c r="K35" s="37">
+      <c r="K35" s="38">
         <v>0.0</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="38">
         <v>0.0</v>
       </c>
-      <c r="M35" s="37">
+      <c r="M35" s="38">
         <v>0.0</v>
       </c>
-      <c r="N35" s="37">
+      <c r="N35" s="38">
         <v>0.0</v>
       </c>
-      <c r="O35" s="37">
+      <c r="O35" s="38">
         <v>0.0</v>
       </c>
-      <c r="P35" s="37">
+      <c r="P35" s="38">
         <v>0.0</v>
       </c>
-      <c r="Q35" s="37">
+      <c r="Q35" s="38">
         <v>0.0</v>
       </c>
-      <c r="R35" s="37">
+      <c r="R35" s="38">
         <v>11.18</v>
       </c>
-      <c r="S35" s="37">
+      <c r="S35" s="38">
         <v>18.11</v>
       </c>
-      <c r="T35" s="37">
+      <c r="T35" s="38">
         <v>119.68</v>
       </c>
-      <c r="U35" s="37">
+      <c r="U35" s="38">
         <v>90.19</v>
       </c>
-      <c r="V35" s="37">
+      <c r="V35" s="38">
         <v>16.76</v>
       </c>
-      <c r="W35" s="37">
+      <c r="W35" s="38">
         <v>3.74</v>
       </c>
-      <c r="X35" s="37">
+      <c r="X35" s="38">
         <v>4.49</v>
       </c>
-      <c r="Y35" s="37">
+      <c r="Y35" s="38">
         <v>6.32</v>
       </c>
-      <c r="Z35" s="37">
+      <c r="Z35" s="38">
         <v>2.97</v>
       </c>
-      <c r="AA35" s="37">
+      <c r="AA35" s="38">
         <v>1.81</v>
       </c>
-      <c r="AB35" s="37">
+      <c r="AB35" s="38">
         <v>2.11</v>
       </c>
-      <c r="AC35" s="37">
+      <c r="AC35" s="38">
         <v>1.52</v>
       </c>
-      <c r="AD35" s="37">
+      <c r="AD35" s="38">
         <v>1.43</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="B36" s="37">
+      <c r="B36" s="38">
         <v>7.53</v>
       </c>
-      <c r="C36" s="37">
+      <c r="C36" s="38">
         <v>6.99</v>
       </c>
-      <c r="D36" s="37">
+      <c r="D36" s="38">
         <v>5.41</v>
       </c>
-      <c r="E36" s="37">
+      <c r="E36" s="38">
         <v>2.71</v>
       </c>
-      <c r="F36" s="37">
+      <c r="F36" s="38">
         <v>0.96</v>
       </c>
-      <c r="G36" s="37">
+      <c r="G36" s="38">
         <v>0.0</v>
       </c>
-      <c r="H36" s="37">
+      <c r="H36" s="38">
         <v>0.0</v>
       </c>
-      <c r="I36" s="37">
+      <c r="I36" s="38">
         <v>0.0</v>
       </c>
-      <c r="J36" s="37">
+      <c r="J36" s="38">
         <v>0.0</v>
       </c>
-      <c r="K36" s="37">
+      <c r="K36" s="38">
         <v>0.0</v>
       </c>
-      <c r="L36" s="37">
+      <c r="L36" s="38">
         <v>0.0</v>
       </c>
-      <c r="M36" s="37">
+      <c r="M36" s="38">
         <v>0.0</v>
       </c>
-      <c r="N36" s="37">
+      <c r="N36" s="38">
         <v>5.28</v>
       </c>
-      <c r="O36" s="37">
+      <c r="O36" s="38">
         <v>11.79</v>
       </c>
-      <c r="P36" s="37">
+      <c r="P36" s="38">
         <v>64.38</v>
       </c>
-      <c r="Q36" s="37">
+      <c r="Q36" s="38">
         <v>73.5</v>
       </c>
-      <c r="R36" s="37">
+      <c r="R36" s="38">
         <v>58.85</v>
       </c>
-      <c r="S36" s="37">
+      <c r="S36" s="38">
         <v>51.86</v>
       </c>
-      <c r="T36" s="37">
+      <c r="T36" s="38">
         <v>48.59</v>
       </c>
-      <c r="U36" s="37">
+      <c r="U36" s="38">
         <v>25.09</v>
       </c>
-      <c r="V36" s="37">
+      <c r="V36" s="38">
         <v>7.55</v>
       </c>
-      <c r="W36" s="37">
+      <c r="W36" s="38">
         <v>3.57</v>
       </c>
-      <c r="X36" s="37">
+      <c r="X36" s="38">
         <v>3.28</v>
       </c>
-      <c r="Y36" s="37">
+      <c r="Y36" s="38">
         <v>2.7</v>
       </c>
-      <c r="Z36" s="37">
+      <c r="Z36" s="38">
         <v>2.04</v>
       </c>
-      <c r="AA36" s="37"/>
-      <c r="AB36" s="37"/>
-      <c r="AC36" s="37"/>
-      <c r="AD36" s="37"/>
+      <c r="AA36" s="38"/>
+      <c r="AB36" s="38"/>
+      <c r="AC36" s="38"/>
+      <c r="AD36" s="38"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="30" t="s">
         <v>383</v>
       </c>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
-      <c r="S37" s="30"/>
-      <c r="T37" s="30"/>
-      <c r="U37" s="30"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="30"/>
-      <c r="X37" s="30"/>
-      <c r="Y37" s="30"/>
-      <c r="Z37" s="30"/>
-      <c r="AA37" s="30"/>
-      <c r="AB37" s="30"/>
-      <c r="AC37" s="30"/>
-      <c r="AD37" s="30"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="31"/>
+      <c r="T37" s="31"/>
+      <c r="U37" s="31"/>
+      <c r="V37" s="31"/>
+      <c r="W37" s="31"/>
+      <c r="X37" s="31"/>
+      <c r="Y37" s="31"/>
+      <c r="Z37" s="31"/>
+      <c r="AA37" s="31"/>
+      <c r="AB37" s="31"/>
+      <c r="AC37" s="31"/>
+      <c r="AD37" s="31"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="32" t="s">
         <v>384</v>
       </c>
-      <c r="B38" s="33">
+      <c r="B38" s="34">
         <v>2.91</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="34">
         <v>0.93</v>
       </c>
-      <c r="D38" s="33">
+      <c r="D38" s="34">
         <v>0.84</v>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="34">
         <v>0.81</v>
       </c>
-      <c r="F38" s="33">
+      <c r="F38" s="34">
         <v>0.76</v>
       </c>
-      <c r="G38" s="33">
+      <c r="G38" s="34">
         <v>0.72</v>
       </c>
-      <c r="H38" s="33">
+      <c r="H38" s="34">
         <v>0.88</v>
       </c>
-      <c r="I38" s="33">
+      <c r="I38" s="34">
         <v>1.85</v>
       </c>
-      <c r="J38" s="33">
+      <c r="J38" s="34">
         <v>1.76</v>
       </c>
-      <c r="K38" s="33">
+      <c r="K38" s="34">
         <v>1.03</v>
       </c>
-      <c r="L38" s="33">
+      <c r="L38" s="34">
         <v>0.6</v>
       </c>
-      <c r="M38" s="33">
+      <c r="M38" s="34">
         <v>0.54</v>
       </c>
-      <c r="N38" s="33">
+      <c r="N38" s="34">
         <v>0.63</v>
       </c>
-      <c r="O38" s="33">
+      <c r="O38" s="34">
         <v>0.41</v>
       </c>
-      <c r="P38" s="33">
+      <c r="P38" s="34">
         <v>0.4</v>
       </c>
-      <c r="Q38" s="33">
+      <c r="Q38" s="34">
         <v>0.4</v>
       </c>
-      <c r="R38" s="33">
+      <c r="R38" s="34">
         <v>0.69</v>
       </c>
-      <c r="S38" s="33">
+      <c r="S38" s="34">
         <v>0.99</v>
       </c>
-      <c r="T38" s="33">
+      <c r="T38" s="34">
         <v>1.55</v>
       </c>
-      <c r="U38" s="33">
+      <c r="U38" s="34">
         <v>0.6</v>
       </c>
-      <c r="V38" s="33">
+      <c r="V38" s="34">
         <v>0.63</v>
       </c>
-      <c r="W38" s="33">
+      <c r="W38" s="34">
         <v>0.49</v>
       </c>
-      <c r="X38" s="33">
+      <c r="X38" s="34">
         <v>0.41</v>
       </c>
-      <c r="Y38" s="35"/>
-      <c r="Z38" s="35"/>
-      <c r="AA38" s="35"/>
-      <c r="AB38" s="35"/>
-      <c r="AC38" s="35"/>
-      <c r="AD38" s="35"/>
+      <c r="Y38" s="36"/>
+      <c r="Z38" s="36"/>
+      <c r="AA38" s="36"/>
+      <c r="AB38" s="36"/>
+      <c r="AC38" s="36"/>
+      <c r="AD38" s="36"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="B39" s="33">
+      <c r="B39" s="34">
         <v>1.1</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="34">
         <v>0.83</v>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="34">
         <v>0.8</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="34">
         <v>0.96</v>
       </c>
-      <c r="F39" s="33">
+      <c r="F39" s="34">
         <v>1.15</v>
       </c>
-      <c r="G39" s="33">
+      <c r="G39" s="34">
         <v>1.22</v>
       </c>
-      <c r="H39" s="33">
+      <c r="H39" s="34">
         <v>1.26</v>
       </c>
-      <c r="I39" s="33">
+      <c r="I39" s="34">
         <v>1.2</v>
       </c>
-      <c r="J39" s="33">
+      <c r="J39" s="34">
         <v>0.94</v>
       </c>
-      <c r="K39" s="33">
+      <c r="K39" s="34">
         <v>0.64</v>
       </c>
-      <c r="L39" s="33">
+      <c r="L39" s="34">
         <v>0.51</v>
       </c>
-      <c r="M39" s="33">
+      <c r="M39" s="34">
         <v>0.46</v>
       </c>
-      <c r="N39" s="33">
+      <c r="N39" s="34">
         <v>0.54</v>
       </c>
-      <c r="O39" s="33">
+      <c r="O39" s="34">
         <v>0.67</v>
       </c>
-      <c r="P39" s="33">
+      <c r="P39" s="34">
         <v>0.95</v>
       </c>
-      <c r="Q39" s="33">
+      <c r="Q39" s="34">
         <v>0.84</v>
       </c>
-      <c r="R39" s="33">
+      <c r="R39" s="34">
         <v>0.79</v>
       </c>
-      <c r="S39" s="33">
+      <c r="S39" s="34">
         <v>0.71</v>
       </c>
-      <c r="T39" s="33">
+      <c r="T39" s="34">
         <v>0.62</v>
       </c>
-      <c r="U39" s="35"/>
-      <c r="V39" s="35"/>
-      <c r="W39" s="35"/>
-      <c r="X39" s="35"/>
-      <c r="Y39" s="35"/>
-      <c r="Z39" s="35"/>
-      <c r="AA39" s="35"/>
-      <c r="AB39" s="35"/>
-      <c r="AC39" s="35"/>
-      <c r="AD39" s="35"/>
+      <c r="U39" s="36"/>
+      <c r="V39" s="36"/>
+      <c r="W39" s="36"/>
+      <c r="X39" s="36"/>
+      <c r="Y39" s="36"/>
+      <c r="Z39" s="36"/>
+      <c r="AA39" s="36"/>
+      <c r="AB39" s="36"/>
+      <c r="AC39" s="36"/>
+      <c r="AD39" s="36"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="29" t="s">
+      <c r="A40" s="30" t="s">
         <v>386</v>
       </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
-      <c r="S40" s="30"/>
-      <c r="T40" s="30"/>
-      <c r="U40" s="30"/>
-      <c r="V40" s="30"/>
-      <c r="W40" s="30"/>
-      <c r="X40" s="30"/>
-      <c r="Y40" s="30"/>
-      <c r="Z40" s="30"/>
-      <c r="AA40" s="30"/>
-      <c r="AB40" s="30"/>
-      <c r="AC40" s="30"/>
-      <c r="AD40" s="30"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="31"/>
+      <c r="S40" s="31"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="31"/>
+      <c r="V40" s="31"/>
+      <c r="W40" s="31"/>
+      <c r="X40" s="31"/>
+      <c r="Y40" s="31"/>
+      <c r="Z40" s="31"/>
+      <c r="AA40" s="31"/>
+      <c r="AB40" s="31"/>
+      <c r="AC40" s="31"/>
+      <c r="AD40" s="31"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="32" t="s">
         <v>387</v>
       </c>
-      <c r="B41" s="33">
+      <c r="B41" s="34">
         <v>4.13</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="34">
         <v>1.07</v>
       </c>
-      <c r="D41" s="33">
+      <c r="D41" s="34">
         <v>1.16</v>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="34">
         <v>1.2</v>
       </c>
-      <c r="F41" s="33">
+      <c r="F41" s="34">
         <v>1.13</v>
       </c>
-      <c r="G41" s="33">
+      <c r="G41" s="34">
         <v>1.09</v>
       </c>
-      <c r="H41" s="33">
+      <c r="H41" s="34">
         <v>0.95</v>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="34">
         <v>2.02</v>
       </c>
-      <c r="J41" s="33">
+      <c r="J41" s="34">
         <v>1.87</v>
       </c>
-      <c r="K41" s="33">
+      <c r="K41" s="34">
         <v>1.05</v>
       </c>
-      <c r="L41" s="33">
+      <c r="L41" s="34">
         <v>0.61</v>
       </c>
-      <c r="M41" s="33">
+      <c r="M41" s="34">
         <v>0.56</v>
       </c>
-      <c r="N41" s="33">
+      <c r="N41" s="34">
         <v>0.65</v>
       </c>
-      <c r="O41" s="33">
+      <c r="O41" s="34">
         <v>0.41</v>
       </c>
-      <c r="P41" s="33">
+      <c r="P41" s="34">
         <v>0.41</v>
       </c>
-      <c r="Q41" s="33">
+      <c r="Q41" s="34">
         <v>0.41</v>
       </c>
-      <c r="R41" s="33">
+      <c r="R41" s="34">
         <v>0.7</v>
       </c>
-      <c r="S41" s="33">
+      <c r="S41" s="34">
         <v>0.99</v>
       </c>
-      <c r="T41" s="33">
+      <c r="T41" s="34">
         <v>1.56</v>
       </c>
-      <c r="U41" s="33">
+      <c r="U41" s="34">
         <v>0.6</v>
       </c>
-      <c r="V41" s="33">
+      <c r="V41" s="34">
         <v>0.63</v>
       </c>
-      <c r="W41" s="33">
+      <c r="W41" s="34">
         <v>0.49</v>
       </c>
-      <c r="X41" s="33">
+      <c r="X41" s="34">
         <v>0.42</v>
       </c>
-      <c r="Y41" s="33">
+      <c r="Y41" s="34">
         <v>1.34</v>
       </c>
-      <c r="Z41" s="33">
+      <c r="Z41" s="34">
         <v>1.64</v>
       </c>
-      <c r="AA41" s="33">
+      <c r="AA41" s="34">
         <v>1.59</v>
       </c>
-      <c r="AB41" s="33">
+      <c r="AB41" s="34">
         <v>2.68</v>
       </c>
-      <c r="AC41" s="33">
+      <c r="AC41" s="34">
         <v>1.66</v>
       </c>
-      <c r="AD41" s="33">
+      <c r="AD41" s="34">
         <v>4.05</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="32" t="s">
         <v>388</v>
       </c>
-      <c r="B42" s="33">
+      <c r="B42" s="34">
         <v>1.47</v>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="34">
         <v>1.12</v>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="34">
         <v>1.1</v>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="34">
         <v>1.27</v>
       </c>
-      <c r="F42" s="33">
+      <c r="F42" s="34">
         <v>1.41</v>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="34">
         <v>1.4</v>
       </c>
-      <c r="H42" s="33">
+      <c r="H42" s="34">
         <v>1.33</v>
       </c>
-      <c r="I42" s="33">
+      <c r="I42" s="34">
         <v>1.25</v>
       </c>
-      <c r="J42" s="33">
+      <c r="J42" s="34">
         <v>0.97</v>
       </c>
-      <c r="K42" s="33">
+      <c r="K42" s="34">
         <v>0.66</v>
       </c>
-      <c r="L42" s="33">
+      <c r="L42" s="34">
         <v>0.52</v>
       </c>
-      <c r="M42" s="33">
+      <c r="M42" s="34">
         <v>0.47</v>
       </c>
-      <c r="N42" s="33">
+      <c r="N42" s="34">
         <v>0.54</v>
       </c>
-      <c r="O42" s="33">
+      <c r="O42" s="34">
         <v>0.68</v>
       </c>
-      <c r="P42" s="33">
+      <c r="P42" s="34">
         <v>0.96</v>
       </c>
-      <c r="Q42" s="33">
+      <c r="Q42" s="34">
         <v>0.85</v>
       </c>
-      <c r="R42" s="33">
+      <c r="R42" s="34">
         <v>0.8</v>
       </c>
-      <c r="S42" s="33">
+      <c r="S42" s="34">
         <v>0.72</v>
       </c>
-      <c r="T42" s="33">
+      <c r="T42" s="34">
         <v>0.63</v>
       </c>
-      <c r="U42" s="33">
+      <c r="U42" s="34">
         <v>0.58</v>
       </c>
-      <c r="V42" s="33">
+      <c r="V42" s="34">
         <v>0.68</v>
       </c>
-      <c r="W42" s="33">
+      <c r="W42" s="34">
         <v>0.8</v>
       </c>
-      <c r="X42" s="33">
+      <c r="X42" s="34">
         <v>1.09</v>
       </c>
-      <c r="Y42" s="33">
+      <c r="Y42" s="34">
         <v>1.69</v>
       </c>
-      <c r="Z42" s="33">
+      <c r="Z42" s="34">
         <v>1.95</v>
       </c>
-      <c r="AA42" s="35"/>
-      <c r="AB42" s="35"/>
-      <c r="AC42" s="35"/>
-      <c r="AD42" s="35"/>
+      <c r="AA42" s="36"/>
+      <c r="AB42" s="36"/>
+      <c r="AC42" s="36"/>
+      <c r="AD42" s="36"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="30" t="s">
         <v>389</v>
       </c>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="30"/>
-      <c r="S43" s="30"/>
-      <c r="T43" s="30"/>
-      <c r="U43" s="30"/>
-      <c r="V43" s="30"/>
-      <c r="W43" s="30"/>
-      <c r="X43" s="30"/>
-      <c r="Y43" s="30"/>
-      <c r="Z43" s="30"/>
-      <c r="AA43" s="30"/>
-      <c r="AB43" s="30"/>
-      <c r="AC43" s="30"/>
-      <c r="AD43" s="30"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="31"/>
+      <c r="T43" s="31"/>
+      <c r="U43" s="31"/>
+      <c r="V43" s="31"/>
+      <c r="W43" s="31"/>
+      <c r="X43" s="31"/>
+      <c r="Y43" s="31"/>
+      <c r="Z43" s="31"/>
+      <c r="AA43" s="31"/>
+      <c r="AB43" s="31"/>
+      <c r="AC43" s="31"/>
+      <c r="AD43" s="31"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="31" t="s">
+      <c r="A44" s="32" t="s">
         <v>390</v>
       </c>
-      <c r="B44" s="33">
+      <c r="B44" s="34">
         <v>1.08</v>
       </c>
-      <c r="C44" s="33">
+      <c r="C44" s="34">
         <v>0.84</v>
       </c>
-      <c r="D44" s="33">
+      <c r="D44" s="34">
         <v>0.53</v>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="34">
         <v>0.3</v>
       </c>
-      <c r="F44" s="33">
+      <c r="F44" s="34">
         <v>0.29</v>
       </c>
-      <c r="G44" s="33">
+      <c r="G44" s="34">
         <v>0.25</v>
       </c>
-      <c r="H44" s="33">
+      <c r="H44" s="34">
         <v>0.28</v>
       </c>
-      <c r="I44" s="33">
+      <c r="I44" s="34">
         <v>0.51</v>
       </c>
-      <c r="J44" s="33">
+      <c r="J44" s="34">
         <v>0.59</v>
       </c>
-      <c r="K44" s="33">
+      <c r="K44" s="34">
         <v>0.27</v>
       </c>
-      <c r="L44" s="33">
+      <c r="L44" s="34">
         <v>0.12</v>
       </c>
-      <c r="M44" s="33">
+      <c r="M44" s="34">
         <v>0.13</v>
       </c>
-      <c r="N44" s="33">
+      <c r="N44" s="34">
         <v>0.17</v>
       </c>
-      <c r="O44" s="33">
+      <c r="O44" s="34">
         <v>0.07</v>
       </c>
-      <c r="P44" s="33">
+      <c r="P44" s="34">
         <v>0.12</v>
       </c>
-      <c r="Q44" s="33">
+      <c r="Q44" s="34">
         <v>0.15</v>
       </c>
-      <c r="R44" s="33">
+      <c r="R44" s="34">
         <v>0.21</v>
       </c>
-      <c r="S44" s="33">
+      <c r="S44" s="34">
         <v>0.4</v>
       </c>
-      <c r="T44" s="33">
+      <c r="T44" s="34">
         <v>0.86</v>
       </c>
-      <c r="U44" s="33">
+      <c r="U44" s="34">
         <v>0.71</v>
       </c>
-      <c r="V44" s="33">
+      <c r="V44" s="34">
         <v>1.24</v>
       </c>
-      <c r="W44" s="33">
+      <c r="W44" s="34">
         <v>0.22</v>
       </c>
-      <c r="X44" s="33">
+      <c r="X44" s="34">
         <v>0.14</v>
       </c>
-      <c r="Y44" s="33">
+      <c r="Y44" s="34">
         <v>0.4</v>
       </c>
-      <c r="Z44" s="33">
+      <c r="Z44" s="34">
         <v>0.3</v>
       </c>
-      <c r="AA44" s="33">
+      <c r="AA44" s="34">
         <v>0.34</v>
       </c>
-      <c r="AB44" s="33">
+      <c r="AB44" s="34">
         <v>0.52</v>
       </c>
-      <c r="AC44" s="33">
+      <c r="AC44" s="34">
         <v>0.76</v>
       </c>
-      <c r="AD44" s="33">
+      <c r="AD44" s="34">
         <v>1.5</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="31" t="s">
+      <c r="A45" s="32" t="s">
         <v>391</v>
       </c>
-      <c r="B45" s="33">
+      <c r="B45" s="34">
         <v>0.56</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="34">
         <v>0.41</v>
       </c>
-      <c r="D45" s="33">
+      <c r="D45" s="34">
         <v>0.32</v>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="34">
         <v>0.33</v>
       </c>
-      <c r="F45" s="33">
+      <c r="F45" s="34">
         <v>0.38</v>
       </c>
-      <c r="G45" s="33">
+      <c r="G45" s="34">
         <v>0.38</v>
       </c>
-      <c r="H45" s="33">
+      <c r="H45" s="34">
         <v>0.35</v>
       </c>
-      <c r="I45" s="33">
+      <c r="I45" s="34">
         <v>0.31</v>
       </c>
-      <c r="J45" s="33">
+      <c r="J45" s="34">
         <v>0.24</v>
       </c>
-      <c r="K45" s="33">
+      <c r="K45" s="34">
         <v>0.15</v>
       </c>
-      <c r="L45" s="33">
+      <c r="L45" s="34">
         <v>0.12</v>
       </c>
-      <c r="M45" s="33">
+      <c r="M45" s="34">
         <v>0.13</v>
       </c>
-      <c r="N45" s="33">
+      <c r="N45" s="34">
         <v>0.16</v>
       </c>
-      <c r="O45" s="33">
+      <c r="O45" s="34">
         <v>0.22</v>
       </c>
-      <c r="P45" s="33">
+      <c r="P45" s="34">
         <v>0.37</v>
       </c>
-      <c r="Q45" s="33">
+      <c r="Q45" s="34">
         <v>0.46</v>
       </c>
-      <c r="R45" s="33">
+      <c r="R45" s="34">
         <v>0.62</v>
       </c>
-      <c r="S45" s="33">
+      <c r="S45" s="34">
         <v>0.52</v>
       </c>
-      <c r="T45" s="33">
+      <c r="T45" s="34">
         <v>0.38</v>
       </c>
-      <c r="U45" s="33">
+      <c r="U45" s="34">
         <v>0.33</v>
       </c>
-      <c r="V45" s="33">
+      <c r="V45" s="34">
         <v>0.3</v>
       </c>
-      <c r="W45" s="33">
+      <c r="W45" s="34">
         <v>0.25</v>
       </c>
-      <c r="X45" s="33">
+      <c r="X45" s="34">
         <v>0.28</v>
       </c>
-      <c r="Y45" s="33">
+      <c r="Y45" s="34">
         <v>0.4</v>
       </c>
-      <c r="Z45" s="33">
+      <c r="Z45" s="34">
         <v>0.46</v>
       </c>
-      <c r="AA45" s="35"/>
-      <c r="AB45" s="35"/>
-      <c r="AC45" s="35"/>
-      <c r="AD45" s="35"/>
+      <c r="AA45" s="36"/>
+      <c r="AB45" s="36"/>
+      <c r="AC45" s="36"/>
+      <c r="AD45" s="36"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="29" t="s">
+      <c r="A46" s="30" t="s">
         <v>392</v>
       </c>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
-      <c r="S46" s="30"/>
-      <c r="T46" s="30"/>
-      <c r="U46" s="30"/>
-      <c r="V46" s="30"/>
-      <c r="W46" s="30"/>
-      <c r="X46" s="30"/>
-      <c r="Y46" s="30"/>
-      <c r="Z46" s="30"/>
-      <c r="AA46" s="30"/>
-      <c r="AB46" s="30"/>
-      <c r="AC46" s="30"/>
-      <c r="AD46" s="30"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="31"/>
+      <c r="L46" s="31"/>
+      <c r="M46" s="31"/>
+      <c r="N46" s="31"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="31"/>
+      <c r="Q46" s="31"/>
+      <c r="R46" s="31"/>
+      <c r="S46" s="31"/>
+      <c r="T46" s="31"/>
+      <c r="U46" s="31"/>
+      <c r="V46" s="31"/>
+      <c r="W46" s="31"/>
+      <c r="X46" s="31"/>
+      <c r="Y46" s="31"/>
+      <c r="Z46" s="31"/>
+      <c r="AA46" s="31"/>
+      <c r="AB46" s="31"/>
+      <c r="AC46" s="31"/>
+      <c r="AD46" s="31"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="31" t="s">
+      <c r="A47" s="32" t="s">
         <v>393</v>
       </c>
-      <c r="B47" s="35"/>
-      <c r="C47" s="32">
+      <c r="B47" s="36"/>
+      <c r="C47" s="33">
         <v>209.27</v>
       </c>
-      <c r="D47" s="33">
+      <c r="D47" s="34">
         <v>6.85</v>
       </c>
-      <c r="E47" s="33">
+      <c r="E47" s="34">
         <v>4.72</v>
       </c>
-      <c r="F47" s="35"/>
-      <c r="G47" s="33">
+      <c r="F47" s="36"/>
+      <c r="G47" s="34">
         <v>7.26</v>
       </c>
-      <c r="H47" s="33">
+      <c r="H47" s="34">
         <v>17.88</v>
       </c>
-      <c r="I47" s="35"/>
-      <c r="J47" s="33">
+      <c r="I47" s="36"/>
+      <c r="J47" s="34">
         <v>16.41</v>
       </c>
-      <c r="K47" s="33">
+      <c r="K47" s="34">
         <v>3.86</v>
       </c>
-      <c r="L47" s="35"/>
-      <c r="M47" s="35"/>
-      <c r="N47" s="33">
+      <c r="L47" s="36"/>
+      <c r="M47" s="36"/>
+      <c r="N47" s="34">
         <v>3.71</v>
       </c>
-      <c r="O47" s="33">
+      <c r="O47" s="34">
         <v>6.34</v>
       </c>
-      <c r="P47" s="33">
+      <c r="P47" s="34">
         <v>1.09</v>
       </c>
-      <c r="Q47" s="35"/>
-      <c r="R47" s="35"/>
-      <c r="S47" s="33">
+      <c r="Q47" s="36"/>
+      <c r="R47" s="36"/>
+      <c r="S47" s="34">
         <v>15.59</v>
       </c>
-      <c r="T47" s="32">
+      <c r="T47" s="33">
         <v>183.12</v>
       </c>
-      <c r="U47" s="33">
+      <c r="U47" s="34">
         <v>5.55</v>
       </c>
-      <c r="V47" s="33">
+      <c r="V47" s="34">
         <v>6.65</v>
       </c>
-      <c r="W47" s="33">
+      <c r="W47" s="34">
         <v>3.94</v>
       </c>
-      <c r="X47" s="33">
+      <c r="X47" s="34">
         <v>2.18</v>
       </c>
-      <c r="Y47" s="33">
+      <c r="Y47" s="34">
         <v>13.2</v>
       </c>
-      <c r="Z47" s="35"/>
-      <c r="AA47" s="35"/>
-      <c r="AB47" s="33">
+      <c r="Z47" s="36"/>
+      <c r="AA47" s="36"/>
+      <c r="AB47" s="34">
         <v>7.29</v>
       </c>
-      <c r="AC47" s="33">
+      <c r="AC47" s="34">
         <v>10.46</v>
       </c>
-      <c r="AD47" s="33">
+      <c r="AD47" s="34">
         <v>30.64</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="31" t="s">
+      <c r="A48" s="32" t="s">
         <v>394</v>
       </c>
-      <c r="B48" s="32">
+      <c r="B48" s="33">
         <v>703.11</v>
       </c>
-      <c r="C48" s="33">
+      <c r="C48" s="34">
         <v>12.32</v>
       </c>
-      <c r="D48" s="33">
+      <c r="D48" s="34">
         <v>9.4</v>
       </c>
-      <c r="E48" s="33">
+      <c r="E48" s="34">
         <v>28.15</v>
       </c>
-      <c r="F48" s="33">
+      <c r="F48" s="34">
         <v>76.52</v>
       </c>
-      <c r="G48" s="33">
+      <c r="G48" s="34">
         <v>18.14</v>
       </c>
-      <c r="H48" s="35"/>
-      <c r="I48" s="35"/>
-      <c r="J48" s="32">
+      <c r="H48" s="36"/>
+      <c r="I48" s="36"/>
+      <c r="J48" s="33">
         <v>103.38</v>
       </c>
-      <c r="K48" s="35"/>
-      <c r="L48" s="33">
+      <c r="K48" s="36"/>
+      <c r="L48" s="34">
         <v>10.11</v>
       </c>
-      <c r="M48" s="35"/>
-      <c r="N48" s="35"/>
-      <c r="O48" s="35"/>
-      <c r="P48" s="35"/>
-      <c r="Q48" s="35"/>
-      <c r="R48" s="33">
+      <c r="M48" s="36"/>
+      <c r="N48" s="36"/>
+      <c r="O48" s="36"/>
+      <c r="P48" s="36"/>
+      <c r="Q48" s="36"/>
+      <c r="R48" s="34">
         <v>15.74</v>
       </c>
-      <c r="S48" s="33">
+      <c r="S48" s="34">
         <v>7.64</v>
       </c>
-      <c r="T48" s="33">
+      <c r="T48" s="34">
         <v>5.28</v>
       </c>
-      <c r="U48" s="33">
+      <c r="U48" s="34">
         <v>4.49</v>
       </c>
-      <c r="V48" s="33">
+      <c r="V48" s="34">
         <v>6.98</v>
       </c>
-      <c r="W48" s="33">
+      <c r="W48" s="34">
         <v>10.78</v>
       </c>
-      <c r="X48" s="33">
+      <c r="X48" s="34">
         <v>15.46</v>
       </c>
-      <c r="Y48" s="35"/>
-      <c r="Z48" s="35"/>
-      <c r="AA48" s="35"/>
-      <c r="AB48" s="35"/>
-      <c r="AC48" s="35"/>
-      <c r="AD48" s="35"/>
+      <c r="Y48" s="36"/>
+      <c r="Z48" s="36"/>
+      <c r="AA48" s="36"/>
+      <c r="AB48" s="36"/>
+      <c r="AC48" s="36"/>
+      <c r="AD48" s="36"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="29" t="s">
+      <c r="A49" s="30" t="s">
         <v>395</v>
       </c>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="30"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="30"/>
-      <c r="Q49" s="30"/>
-      <c r="R49" s="30"/>
-      <c r="S49" s="30"/>
-      <c r="T49" s="30"/>
-      <c r="U49" s="30"/>
-      <c r="V49" s="30"/>
-      <c r="W49" s="30"/>
-      <c r="X49" s="30"/>
-      <c r="Y49" s="30"/>
-      <c r="Z49" s="30"/>
-      <c r="AA49" s="30"/>
-      <c r="AB49" s="30"/>
-      <c r="AC49" s="30"/>
-      <c r="AD49" s="30"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="31"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="31"/>
+      <c r="M49" s="31"/>
+      <c r="N49" s="31"/>
+      <c r="O49" s="31"/>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="31"/>
+      <c r="R49" s="31"/>
+      <c r="S49" s="31"/>
+      <c r="T49" s="31"/>
+      <c r="U49" s="31"/>
+      <c r="V49" s="31"/>
+      <c r="W49" s="31"/>
+      <c r="X49" s="31"/>
+      <c r="Y49" s="31"/>
+      <c r="Z49" s="31"/>
+      <c r="AA49" s="31"/>
+      <c r="AB49" s="31"/>
+      <c r="AC49" s="31"/>
+      <c r="AD49" s="31"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="31" t="s">
+      <c r="A50" s="32" t="s">
         <v>396</v>
       </c>
-      <c r="B50" s="33">
+      <c r="B50" s="34">
         <v>12.78</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="34">
         <v>11.42</v>
       </c>
-      <c r="D50" s="33">
+      <c r="D50" s="34">
         <v>6.22</v>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="34">
         <v>5.23</v>
       </c>
-      <c r="F50" s="33">
+      <c r="F50" s="34">
         <v>5.49</v>
       </c>
-      <c r="G50" s="33">
+      <c r="G50" s="34">
         <v>4.56</v>
       </c>
-      <c r="H50" s="33">
+      <c r="H50" s="34">
         <v>6.68</v>
       </c>
-      <c r="I50" s="35"/>
-      <c r="J50" s="33">
+      <c r="I50" s="36"/>
+      <c r="J50" s="34">
         <v>8.85</v>
       </c>
-      <c r="K50" s="33">
+      <c r="K50" s="34">
         <v>4.56</v>
       </c>
-      <c r="L50" s="35"/>
-      <c r="M50" s="35"/>
-      <c r="N50" s="33">
+      <c r="L50" s="36"/>
+      <c r="M50" s="36"/>
+      <c r="N50" s="34">
         <v>5.08</v>
       </c>
-      <c r="O50" s="33">
+      <c r="O50" s="34">
         <v>1.38</v>
       </c>
-      <c r="P50" s="35"/>
-      <c r="Q50" s="35"/>
-      <c r="R50" s="35"/>
-      <c r="S50" s="35"/>
-      <c r="T50" s="33">
+      <c r="P50" s="36"/>
+      <c r="Q50" s="36"/>
+      <c r="R50" s="36"/>
+      <c r="S50" s="36"/>
+      <c r="T50" s="34">
         <v>15.73</v>
       </c>
-      <c r="U50" s="33">
+      <c r="U50" s="34">
         <v>60.0</v>
       </c>
-      <c r="V50" s="33">
+      <c r="V50" s="34">
         <v>5.52</v>
       </c>
-      <c r="W50" s="33">
+      <c r="W50" s="34">
         <v>2.88</v>
       </c>
-      <c r="X50" s="35"/>
-      <c r="Y50" s="35"/>
-      <c r="Z50" s="35"/>
-      <c r="AA50" s="35"/>
-      <c r="AB50" s="33">
+      <c r="X50" s="36"/>
+      <c r="Y50" s="36"/>
+      <c r="Z50" s="36"/>
+      <c r="AA50" s="36"/>
+      <c r="AB50" s="34">
         <v>10.28</v>
       </c>
-      <c r="AC50" s="35"/>
-      <c r="AD50" s="35"/>
+      <c r="AC50" s="36"/>
+      <c r="AD50" s="36"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="31" t="s">
+      <c r="A51" s="32" t="s">
         <v>397</v>
       </c>
-      <c r="B51" s="33">
+      <c r="B51" s="34">
         <v>8.18</v>
       </c>
-      <c r="C51" s="33">
+      <c r="C51" s="34">
         <v>6.49</v>
       </c>
-      <c r="D51" s="33">
+      <c r="D51" s="34">
         <v>5.58</v>
       </c>
-      <c r="E51" s="33">
+      <c r="E51" s="34">
         <v>7.99</v>
       </c>
-      <c r="F51" s="33">
+      <c r="F51" s="34">
         <v>9.04</v>
       </c>
-      <c r="G51" s="33">
+      <c r="G51" s="34">
         <v>8.72</v>
       </c>
-      <c r="H51" s="33">
+      <c r="H51" s="34">
         <v>11.47</v>
       </c>
-      <c r="I51" s="33">
+      <c r="I51" s="34">
         <v>17.25</v>
       </c>
-      <c r="J51" s="33">
+      <c r="J51" s="34">
         <v>9.55</v>
       </c>
-      <c r="K51" s="33">
+      <c r="K51" s="34">
         <v>5.71</v>
       </c>
-      <c r="L51" s="33">
+      <c r="L51" s="34">
         <v>27.61</v>
       </c>
-      <c r="M51" s="35"/>
-      <c r="N51" s="35"/>
-      <c r="O51" s="35"/>
-      <c r="P51" s="35"/>
-      <c r="Q51" s="35"/>
-      <c r="R51" s="33">
+      <c r="M51" s="36"/>
+      <c r="N51" s="36"/>
+      <c r="O51" s="36"/>
+      <c r="P51" s="36"/>
+      <c r="Q51" s="36"/>
+      <c r="R51" s="34">
         <v>14.56</v>
       </c>
-      <c r="S51" s="33">
+      <c r="S51" s="34">
         <v>7.51</v>
       </c>
-      <c r="T51" s="35"/>
-      <c r="U51" s="35"/>
-      <c r="V51" s="35"/>
-      <c r="W51" s="35"/>
-      <c r="X51" s="35"/>
-      <c r="Y51" s="35"/>
-      <c r="Z51" s="35"/>
-      <c r="AA51" s="35"/>
-      <c r="AB51" s="35"/>
-      <c r="AC51" s="35"/>
-      <c r="AD51" s="35"/>
+      <c r="T51" s="36"/>
+      <c r="U51" s="36"/>
+      <c r="V51" s="36"/>
+      <c r="W51" s="36"/>
+      <c r="X51" s="36"/>
+      <c r="Y51" s="36"/>
+      <c r="Z51" s="36"/>
+      <c r="AA51" s="36"/>
+      <c r="AB51" s="36"/>
+      <c r="AC51" s="36"/>
+      <c r="AD51" s="36"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="29" t="s">
+      <c r="A52" s="30" t="s">
         <v>398</v>
       </c>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="30"/>
-      <c r="J52" s="30"/>
-      <c r="K52" s="30"/>
-      <c r="L52" s="30"/>
-      <c r="M52" s="30"/>
-      <c r="N52" s="30"/>
-      <c r="O52" s="30"/>
-      <c r="P52" s="30"/>
-      <c r="Q52" s="30"/>
-      <c r="R52" s="30"/>
-      <c r="S52" s="30"/>
-      <c r="T52" s="30"/>
-      <c r="U52" s="30"/>
-      <c r="V52" s="30"/>
-      <c r="W52" s="30"/>
-      <c r="X52" s="30"/>
-      <c r="Y52" s="30"/>
-      <c r="Z52" s="30"/>
-      <c r="AA52" s="30"/>
-      <c r="AB52" s="30"/>
-      <c r="AC52" s="30"/>
-      <c r="AD52" s="30"/>
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="31"/>
+      <c r="I52" s="31"/>
+      <c r="J52" s="31"/>
+      <c r="K52" s="31"/>
+      <c r="L52" s="31"/>
+      <c r="M52" s="31"/>
+      <c r="N52" s="31"/>
+      <c r="O52" s="31"/>
+      <c r="P52" s="31"/>
+      <c r="Q52" s="31"/>
+      <c r="R52" s="31"/>
+      <c r="S52" s="31"/>
+      <c r="T52" s="31"/>
+      <c r="U52" s="31"/>
+      <c r="V52" s="31"/>
+      <c r="W52" s="31"/>
+      <c r="X52" s="31"/>
+      <c r="Y52" s="31"/>
+      <c r="Z52" s="31"/>
+      <c r="AA52" s="31"/>
+      <c r="AB52" s="31"/>
+      <c r="AC52" s="31"/>
+      <c r="AD52" s="31"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="31" t="s">
+      <c r="A53" s="32" t="s">
         <v>399</v>
       </c>
-      <c r="B53" s="33">
+      <c r="B53" s="34">
         <v>18.83</v>
       </c>
-      <c r="C53" s="33">
+      <c r="C53" s="34">
         <v>15.2</v>
       </c>
-      <c r="D53" s="33">
+      <c r="D53" s="34">
         <v>10.25</v>
       </c>
-      <c r="E53" s="33">
+      <c r="E53" s="34">
         <v>8.17</v>
       </c>
-      <c r="F53" s="33">
+      <c r="F53" s="34">
         <v>8.96</v>
       </c>
-      <c r="G53" s="33">
+      <c r="G53" s="34">
         <v>6.29</v>
       </c>
-      <c r="H53" s="33">
+      <c r="H53" s="34">
         <v>7.56</v>
       </c>
-      <c r="I53" s="35"/>
-      <c r="J53" s="33">
+      <c r="I53" s="36"/>
+      <c r="J53" s="34">
         <v>10.92</v>
       </c>
-      <c r="K53" s="33">
+      <c r="K53" s="34">
         <v>6.6</v>
       </c>
-      <c r="L53" s="35"/>
-      <c r="M53" s="35"/>
-      <c r="N53" s="33">
+      <c r="L53" s="36"/>
+      <c r="M53" s="36"/>
+      <c r="N53" s="34">
         <v>12.37</v>
       </c>
-      <c r="O53" s="33">
+      <c r="O53" s="34">
         <v>2.13</v>
       </c>
-      <c r="P53" s="35"/>
-      <c r="Q53" s="35"/>
-      <c r="R53" s="35"/>
-      <c r="S53" s="35"/>
-      <c r="T53" s="33">
+      <c r="P53" s="36"/>
+      <c r="Q53" s="36"/>
+      <c r="R53" s="36"/>
+      <c r="S53" s="36"/>
+      <c r="T53" s="34">
         <v>20.3</v>
       </c>
-      <c r="U53" s="35"/>
-      <c r="V53" s="33">
+      <c r="U53" s="36"/>
+      <c r="V53" s="34">
         <v>24.18</v>
       </c>
-      <c r="W53" s="33">
+      <c r="W53" s="34">
         <v>15.11</v>
       </c>
-      <c r="X53" s="33">
+      <c r="X53" s="34">
         <v>1.16</v>
       </c>
-      <c r="Y53" s="35"/>
-      <c r="Z53" s="33">
+      <c r="Y53" s="36"/>
+      <c r="Z53" s="34">
         <v>6.57</v>
       </c>
-      <c r="AA53" s="33">
+      <c r="AA53" s="34">
         <v>7.67</v>
       </c>
-      <c r="AB53" s="33">
+      <c r="AB53" s="34">
         <v>17.9</v>
       </c>
-      <c r="AC53" s="33">
+      <c r="AC53" s="34">
         <v>13.16</v>
       </c>
-      <c r="AD53" s="33">
+      <c r="AD53" s="34">
         <v>23.81</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="31" t="s">
+      <c r="A54" s="32" t="s">
         <v>400</v>
       </c>
-      <c r="B54" s="33">
+      <c r="B54" s="34">
         <v>12.46</v>
       </c>
-      <c r="C54" s="33">
+      <c r="C54" s="34">
         <v>9.74</v>
       </c>
-      <c r="D54" s="33">
+      <c r="D54" s="34">
         <v>8.15</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="34">
         <v>12.68</v>
       </c>
-      <c r="F54" s="33">
+      <c r="F54" s="34">
         <v>13.31</v>
       </c>
-      <c r="G54" s="33">
+      <c r="G54" s="34">
         <v>12.48</v>
       </c>
-      <c r="H54" s="33">
+      <c r="H54" s="34">
         <v>19.74</v>
       </c>
-      <c r="I54" s="32">
+      <c r="I54" s="33">
         <v>112.6</v>
       </c>
-      <c r="J54" s="33">
+      <c r="J54" s="34">
         <v>26.85</v>
       </c>
-      <c r="K54" s="33">
+      <c r="K54" s="34">
         <v>18.23</v>
       </c>
-      <c r="L54" s="35"/>
-      <c r="M54" s="35"/>
-      <c r="N54" s="35"/>
-      <c r="O54" s="35"/>
-      <c r="P54" s="35"/>
-      <c r="Q54" s="35"/>
-      <c r="R54" s="35"/>
-      <c r="S54" s="33">
+      <c r="L54" s="36"/>
+      <c r="M54" s="36"/>
+      <c r="N54" s="36"/>
+      <c r="O54" s="36"/>
+      <c r="P54" s="36"/>
+      <c r="Q54" s="36"/>
+      <c r="R54" s="36"/>
+      <c r="S54" s="34">
         <v>51.28</v>
       </c>
-      <c r="T54" s="33">
+      <c r="T54" s="34">
         <v>6.46</v>
       </c>
-      <c r="U54" s="33">
+      <c r="U54" s="34">
         <v>6.58</v>
       </c>
-      <c r="V54" s="33">
+      <c r="V54" s="34">
         <v>5.17</v>
       </c>
-      <c r="W54" s="33">
+      <c r="W54" s="34">
         <v>4.45</v>
       </c>
-      <c r="X54" s="33">
+      <c r="X54" s="34">
         <v>4.34</v>
       </c>
-      <c r="Y54" s="33">
+      <c r="Y54" s="34">
         <v>11.75</v>
       </c>
-      <c r="Z54" s="33">
+      <c r="Z54" s="34">
         <v>10.14</v>
       </c>
-      <c r="AA54" s="35"/>
-      <c r="AB54" s="35"/>
-      <c r="AC54" s="35"/>
-      <c r="AD54" s="35"/>
+      <c r="AA54" s="36"/>
+      <c r="AB54" s="36"/>
+      <c r="AC54" s="36"/>
+      <c r="AD54" s="36"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="29" t="s">
+      <c r="A55" s="30" t="s">
         <v>401</v>
       </c>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="30"/>
-      <c r="K55" s="30"/>
-      <c r="L55" s="30"/>
-      <c r="M55" s="30"/>
-      <c r="N55" s="30"/>
-      <c r="O55" s="30"/>
-      <c r="P55" s="30"/>
-      <c r="Q55" s="30"/>
-      <c r="R55" s="30"/>
-      <c r="S55" s="30"/>
-      <c r="T55" s="30"/>
-      <c r="U55" s="30"/>
-      <c r="V55" s="30"/>
-      <c r="W55" s="30"/>
-      <c r="X55" s="30"/>
-      <c r="Y55" s="30"/>
-      <c r="Z55" s="30"/>
-      <c r="AA55" s="30"/>
-      <c r="AB55" s="30"/>
-      <c r="AC55" s="30"/>
-      <c r="AD55" s="30"/>
+      <c r="B55" s="31"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="31"/>
+      <c r="J55" s="31"/>
+      <c r="K55" s="31"/>
+      <c r="L55" s="31"/>
+      <c r="M55" s="31"/>
+      <c r="N55" s="31"/>
+      <c r="O55" s="31"/>
+      <c r="P55" s="31"/>
+      <c r="Q55" s="31"/>
+      <c r="R55" s="31"/>
+      <c r="S55" s="31"/>
+      <c r="T55" s="31"/>
+      <c r="U55" s="31"/>
+      <c r="V55" s="31"/>
+      <c r="W55" s="31"/>
+      <c r="X55" s="31"/>
+      <c r="Y55" s="31"/>
+      <c r="Z55" s="31"/>
+      <c r="AA55" s="31"/>
+      <c r="AB55" s="31"/>
+      <c r="AC55" s="31"/>
+      <c r="AD55" s="31"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="31" t="s">
+      <c r="A56" s="32" t="s">
         <v>402</v>
       </c>
-      <c r="B56" s="33">
+      <c r="B56" s="34">
         <v>18.83</v>
       </c>
-      <c r="C56" s="33">
+      <c r="C56" s="34">
         <v>13.3</v>
       </c>
-      <c r="D56" s="33">
+      <c r="D56" s="34">
         <v>8.85</v>
       </c>
-      <c r="E56" s="33">
+      <c r="E56" s="34">
         <v>8.17</v>
       </c>
-      <c r="F56" s="33">
+      <c r="F56" s="34">
         <v>8.96</v>
       </c>
-      <c r="G56" s="33">
+      <c r="G56" s="34">
         <v>6.29</v>
       </c>
-      <c r="H56" s="33">
+      <c r="H56" s="34">
         <v>8.45</v>
       </c>
-      <c r="I56" s="33">
+      <c r="I56" s="34">
         <v>9.88</v>
       </c>
-      <c r="J56" s="33">
+      <c r="J56" s="34">
         <v>10.92</v>
       </c>
-      <c r="K56" s="33">
+      <c r="K56" s="34">
         <v>6.6</v>
       </c>
-      <c r="L56" s="35"/>
-      <c r="M56" s="35"/>
-      <c r="N56" s="33">
+      <c r="L56" s="36"/>
+      <c r="M56" s="36"/>
+      <c r="N56" s="34">
         <v>12.37</v>
       </c>
-      <c r="O56" s="33">
+      <c r="O56" s="34">
         <v>2.13</v>
       </c>
-      <c r="P56" s="35"/>
-      <c r="Q56" s="35"/>
-      <c r="R56" s="35"/>
-      <c r="S56" s="35"/>
-      <c r="T56" s="33">
+      <c r="P56" s="36"/>
+      <c r="Q56" s="36"/>
+      <c r="R56" s="36"/>
+      <c r="S56" s="36"/>
+      <c r="T56" s="34">
         <v>17.28</v>
       </c>
-      <c r="U56" s="35"/>
-      <c r="V56" s="33">
+      <c r="U56" s="36"/>
+      <c r="V56" s="34">
         <v>20.86</v>
       </c>
-      <c r="W56" s="33">
+      <c r="W56" s="34">
         <v>10.74</v>
       </c>
-      <c r="X56" s="35"/>
-      <c r="Y56" s="35"/>
-      <c r="Z56" s="35"/>
-      <c r="AA56" s="35"/>
-      <c r="AB56" s="33">
+      <c r="X56" s="36"/>
+      <c r="Y56" s="36"/>
+      <c r="Z56" s="36"/>
+      <c r="AA56" s="36"/>
+      <c r="AB56" s="34">
         <v>17.83</v>
       </c>
-      <c r="AC56" s="35"/>
-      <c r="AD56" s="35"/>
+      <c r="AC56" s="36"/>
+      <c r="AD56" s="36"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="31" t="s">
+      <c r="A57" s="32" t="s">
         <v>403</v>
       </c>
-      <c r="B57" s="33">
+      <c r="B57" s="34">
         <v>1.1</v>
       </c>
-      <c r="C57" s="33">
+      <c r="C57" s="34">
         <v>0.83</v>
       </c>
-      <c r="D57" s="33">
+      <c r="D57" s="34">
         <v>0.8</v>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="34">
         <v>0.96</v>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="34">
         <v>1.15</v>
       </c>
-      <c r="G57" s="33">
+      <c r="G57" s="34">
         <v>1.22</v>
       </c>
-      <c r="H57" s="33">
+      <c r="H57" s="34">
         <v>1.26</v>
       </c>
-      <c r="I57" s="33">
+      <c r="I57" s="34">
         <v>1.2</v>
       </c>
-      <c r="J57" s="33">
+      <c r="J57" s="34">
         <v>0.94</v>
       </c>
-      <c r="K57" s="33">
+      <c r="K57" s="34">
         <v>0.64</v>
       </c>
-      <c r="L57" s="33">
+      <c r="L57" s="34">
         <v>0.51</v>
       </c>
-      <c r="M57" s="33">
+      <c r="M57" s="34">
         <v>0.46</v>
       </c>
-      <c r="N57" s="33">
+      <c r="N57" s="34">
         <v>0.54</v>
       </c>
-      <c r="O57" s="33">
+      <c r="O57" s="34">
         <v>0.67</v>
       </c>
-      <c r="P57" s="33">
+      <c r="P57" s="34">
         <v>0.95</v>
       </c>
-      <c r="Q57" s="33">
+      <c r="Q57" s="34">
         <v>0.84</v>
       </c>
-      <c r="R57" s="33">
+      <c r="R57" s="34">
         <v>0.79</v>
       </c>
-      <c r="S57" s="33">
+      <c r="S57" s="34">
         <v>0.71</v>
       </c>
-      <c r="T57" s="33">
+      <c r="T57" s="34">
         <v>0.62</v>
       </c>
-      <c r="U57" s="33">
+      <c r="U57" s="34">
         <v>0.57</v>
       </c>
-      <c r="V57" s="33">
+      <c r="V57" s="34">
         <v>0.67</v>
       </c>
-      <c r="W57" s="33">
+      <c r="W57" s="34">
         <v>0.78</v>
       </c>
-      <c r="X57" s="33">
+      <c r="X57" s="34">
         <v>1.04</v>
       </c>
-      <c r="Y57" s="33">
+      <c r="Y57" s="34">
         <v>1.62</v>
       </c>
-      <c r="Z57" s="33">
+      <c r="Z57" s="34">
         <v>1.86</v>
       </c>
-      <c r="AA57" s="35"/>
-      <c r="AB57" s="35"/>
-      <c r="AC57" s="35"/>
-      <c r="AD57" s="35"/>
+      <c r="AA57" s="36"/>
+      <c r="AB57" s="36"/>
+      <c r="AC57" s="36"/>
+      <c r="AD57" s="36"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="30" t="s">
         <v>404</v>
       </c>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="30"/>
-      <c r="K58" s="30"/>
-      <c r="L58" s="30"/>
-      <c r="M58" s="30"/>
-      <c r="N58" s="30"/>
-      <c r="O58" s="30"/>
-      <c r="P58" s="30"/>
-      <c r="Q58" s="30"/>
-      <c r="R58" s="30"/>
-      <c r="S58" s="30"/>
-      <c r="T58" s="30"/>
-      <c r="U58" s="30"/>
-      <c r="V58" s="30"/>
-      <c r="W58" s="30"/>
-      <c r="X58" s="30"/>
-      <c r="Y58" s="30"/>
-      <c r="Z58" s="30"/>
-      <c r="AA58" s="30"/>
-      <c r="AB58" s="30"/>
-      <c r="AC58" s="30"/>
-      <c r="AD58" s="30"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
+      <c r="J58" s="31"/>
+      <c r="K58" s="31"/>
+      <c r="L58" s="31"/>
+      <c r="M58" s="31"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
+      <c r="R58" s="31"/>
+      <c r="S58" s="31"/>
+      <c r="T58" s="31"/>
+      <c r="U58" s="31"/>
+      <c r="V58" s="31"/>
+      <c r="W58" s="31"/>
+      <c r="X58" s="31"/>
+      <c r="Y58" s="31"/>
+      <c r="Z58" s="31"/>
+      <c r="AA58" s="31"/>
+      <c r="AB58" s="31"/>
+      <c r="AC58" s="31"/>
+      <c r="AD58" s="31"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="31" t="s">
+      <c r="A59" s="32" t="s">
         <v>405</v>
       </c>
-      <c r="B59" s="33">
+      <c r="B59" s="34">
         <v>38.02</v>
       </c>
-      <c r="C59" s="33">
+      <c r="C59" s="34">
         <v>1.39</v>
       </c>
-      <c r="D59" s="34">
+      <c r="D59" s="35">
         <v>-1.07</v>
       </c>
-      <c r="E59" s="33">
+      <c r="E59" s="34">
         <v>0.38</v>
       </c>
-      <c r="F59" s="34">
+      <c r="F59" s="35">
         <v>-0.38</v>
       </c>
-      <c r="G59" s="33">
+      <c r="G59" s="34">
         <v>0.52</v>
       </c>
-      <c r="H59" s="33">
+      <c r="H59" s="34">
         <v>0.02</v>
       </c>
-      <c r="I59" s="35"/>
-      <c r="J59" s="33">
+      <c r="I59" s="36"/>
+      <c r="J59" s="34">
         <v>0.44</v>
       </c>
-      <c r="K59" s="33">
+      <c r="K59" s="34">
         <v>0.02</v>
       </c>
-      <c r="L59" s="35"/>
-      <c r="M59" s="35"/>
-      <c r="N59" s="34">
+      <c r="L59" s="36"/>
+      <c r="M59" s="36"/>
+      <c r="N59" s="35">
         <v>-0.18</v>
       </c>
-      <c r="O59" s="33">
+      <c r="O59" s="34">
         <v>0.01</v>
       </c>
-      <c r="P59" s="35"/>
-      <c r="Q59" s="35"/>
-      <c r="R59" s="35"/>
-      <c r="S59" s="35"/>
-      <c r="T59" s="33">
+      <c r="P59" s="36"/>
+      <c r="Q59" s="36"/>
+      <c r="R59" s="36"/>
+      <c r="S59" s="36"/>
+      <c r="T59" s="34">
         <v>0.11</v>
       </c>
-      <c r="U59" s="35"/>
-      <c r="V59" s="34">
+      <c r="U59" s="36"/>
+      <c r="V59" s="35">
         <v>-1.89</v>
       </c>
-      <c r="W59" s="34">
+      <c r="W59" s="35">
         <v>-0.17</v>
       </c>
-      <c r="X59" s="35">
+      <c r="X59" s="36">
         <v>0.0</v>
       </c>
-      <c r="Y59" s="35"/>
-      <c r="Z59" s="33">
+      <c r="Y59" s="36"/>
+      <c r="Z59" s="34">
         <v>0.16</v>
       </c>
-      <c r="AA59" s="33">
+      <c r="AA59" s="34">
         <v>0.04</v>
       </c>
-      <c r="AB59" s="34">
+      <c r="AB59" s="35">
         <v>-0.47</v>
       </c>
-      <c r="AC59" s="33">
+      <c r="AC59" s="34">
         <v>0.13</v>
       </c>
-      <c r="AD59" s="35"/>
+      <c r="AD59" s="36"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="31" t="s">
+      <c r="A60" s="32" t="s">
         <v>406</v>
       </c>
-      <c r="B60" s="34">
+      <c r="B60" s="35">
         <v>-9.09</v>
       </c>
-      <c r="C60" s="33">
+      <c r="C60" s="34">
         <v>11.79</v>
       </c>
-      <c r="D60" s="35"/>
-      <c r="E60" s="34">
+      <c r="D60" s="36"/>
+      <c r="E60" s="35">
         <v>-2.86</v>
       </c>
-      <c r="F60" s="34">
+      <c r="F60" s="35">
         <v>-3.39</v>
       </c>
-      <c r="G60" s="35"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="35"/>
-      <c r="J60" s="33">
+      <c r="G60" s="36"/>
+      <c r="H60" s="36"/>
+      <c r="I60" s="36"/>
+      <c r="J60" s="34">
         <v>38.16</v>
       </c>
-      <c r="K60" s="35"/>
-      <c r="L60" s="35"/>
-      <c r="M60" s="35"/>
-      <c r="N60" s="35"/>
-      <c r="O60" s="35"/>
-      <c r="P60" s="35"/>
-      <c r="Q60" s="35"/>
-      <c r="R60" s="35"/>
-      <c r="S60" s="35"/>
-      <c r="T60" s="35"/>
-      <c r="U60" s="35"/>
-      <c r="V60" s="34">
+      <c r="K60" s="36"/>
+      <c r="L60" s="36"/>
+      <c r="M60" s="36"/>
+      <c r="N60" s="36"/>
+      <c r="O60" s="36"/>
+      <c r="P60" s="36"/>
+      <c r="Q60" s="36"/>
+      <c r="R60" s="36"/>
+      <c r="S60" s="36"/>
+      <c r="T60" s="36"/>
+      <c r="U60" s="36"/>
+      <c r="V60" s="35">
         <v>-0.33</v>
       </c>
-      <c r="W60" s="33">
+      <c r="W60" s="34">
         <v>0.51</v>
       </c>
-      <c r="X60" s="33">
+      <c r="X60" s="34">
         <v>0.07</v>
       </c>
-      <c r="Y60" s="35"/>
-      <c r="Z60" s="35"/>
-      <c r="AA60" s="35"/>
-      <c r="AB60" s="35"/>
-      <c r="AC60" s="35"/>
-      <c r="AD60" s="35"/>
+      <c r="Y60" s="36"/>
+      <c r="Z60" s="36"/>
+      <c r="AA60" s="36"/>
+      <c r="AB60" s="36"/>
+      <c r="AC60" s="36"/>
+      <c r="AD60" s="36"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="29" t="s">
+      <c r="A61" s="30" t="s">
         <v>407</v>
       </c>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="30"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="30"/>
-      <c r="O61" s="30"/>
-      <c r="P61" s="30"/>
-      <c r="Q61" s="30"/>
-      <c r="R61" s="30"/>
-      <c r="S61" s="30"/>
-      <c r="T61" s="30"/>
-      <c r="U61" s="30"/>
-      <c r="V61" s="30"/>
-      <c r="W61" s="30"/>
-      <c r="X61" s="30"/>
-      <c r="Y61" s="30"/>
-      <c r="Z61" s="30"/>
-      <c r="AA61" s="30"/>
-      <c r="AB61" s="30"/>
-      <c r="AC61" s="30"/>
-      <c r="AD61" s="30"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="31"/>
+      <c r="K61" s="31"/>
+      <c r="L61" s="31"/>
+      <c r="M61" s="31"/>
+      <c r="N61" s="31"/>
+      <c r="O61" s="31"/>
+      <c r="P61" s="31"/>
+      <c r="Q61" s="31"/>
+      <c r="R61" s="31"/>
+      <c r="S61" s="31"/>
+      <c r="T61" s="31"/>
+      <c r="U61" s="31"/>
+      <c r="V61" s="31"/>
+      <c r="W61" s="31"/>
+      <c r="X61" s="31"/>
+      <c r="Y61" s="31"/>
+      <c r="Z61" s="31"/>
+      <c r="AA61" s="31"/>
+      <c r="AB61" s="31"/>
+      <c r="AC61" s="31"/>
+      <c r="AD61" s="31"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="31" t="s">
+      <c r="A62" s="32" t="s">
         <v>408</v>
       </c>
-      <c r="B62" s="33">
+      <c r="B62" s="34">
         <v>1.24</v>
       </c>
-      <c r="C62" s="33">
+      <c r="C62" s="34">
         <v>0.26</v>
       </c>
-      <c r="D62" s="33">
+      <c r="D62" s="34">
         <v>0.61</v>
       </c>
-      <c r="E62" s="33">
+      <c r="E62" s="34">
         <v>0.37</v>
       </c>
-      <c r="F62" s="33">
+      <c r="F62" s="34">
         <v>0.41</v>
       </c>
-      <c r="G62" s="33">
+      <c r="G62" s="34">
         <v>0.35</v>
       </c>
-      <c r="H62" s="33">
+      <c r="H62" s="34">
         <v>0.3</v>
       </c>
-      <c r="I62" s="33">
+      <c r="I62" s="34">
         <v>0.58</v>
       </c>
-      <c r="J62" s="33">
+      <c r="J62" s="34">
         <v>0.64</v>
       </c>
-      <c r="K62" s="33">
+      <c r="K62" s="34">
         <v>0.37</v>
       </c>
-      <c r="L62" s="33">
+      <c r="L62" s="34">
         <v>0.27</v>
       </c>
-      <c r="M62" s="33">
+      <c r="M62" s="34">
         <v>0.23</v>
       </c>
-      <c r="N62" s="33">
+      <c r="N62" s="34">
         <v>0.25</v>
       </c>
-      <c r="O62" s="33">
+      <c r="O62" s="34">
         <v>0.24</v>
       </c>
-      <c r="P62" s="33">
+      <c r="P62" s="34">
         <v>0.3</v>
       </c>
-      <c r="Q62" s="33">
+      <c r="Q62" s="34">
         <v>0.28</v>
       </c>
-      <c r="R62" s="33">
+      <c r="R62" s="34">
         <v>0.18</v>
       </c>
-      <c r="S62" s="33">
+      <c r="S62" s="34">
         <v>0.25</v>
       </c>
-      <c r="T62" s="33">
+      <c r="T62" s="34">
         <v>0.65</v>
       </c>
-      <c r="U62" s="34">
+      <c r="U62" s="35">
         <v>-0.14</v>
       </c>
-      <c r="V62" s="33">
+      <c r="V62" s="34">
         <v>0.64</v>
       </c>
-      <c r="W62" s="33">
+      <c r="W62" s="34">
         <v>0.3</v>
       </c>
-      <c r="X62" s="33">
+      <c r="X62" s="34">
         <v>0.26</v>
       </c>
-      <c r="Y62" s="33">
+      <c r="Y62" s="34">
         <v>0.71</v>
       </c>
-      <c r="Z62" s="33">
+      <c r="Z62" s="34">
         <v>0.57</v>
       </c>
-      <c r="AA62" s="33">
+      <c r="AA62" s="34">
         <v>0.62</v>
       </c>
-      <c r="AB62" s="33">
+      <c r="AB62" s="34">
         <v>1.29</v>
       </c>
-      <c r="AC62" s="33">
+      <c r="AC62" s="34">
         <v>0.96</v>
       </c>
-      <c r="AD62" s="33">
+      <c r="AD62" s="34">
         <v>0.7</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="31" t="s">
+      <c r="A63" s="32" t="s">
         <v>409</v>
       </c>
-      <c r="B63" s="33">
+      <c r="B63" s="34">
         <v>0.55</v>
       </c>
-      <c r="C63" s="33">
+      <c r="C63" s="34">
         <v>0.39</v>
       </c>
-      <c r="D63" s="33">
+      <c r="D63" s="34">
         <v>0.39</v>
       </c>
-      <c r="E63" s="33">
+      <c r="E63" s="34">
         <v>0.4</v>
       </c>
-      <c r="F63" s="33">
+      <c r="F63" s="34">
         <v>0.45</v>
       </c>
-      <c r="G63" s="33">
+      <c r="G63" s="34">
         <v>0.45</v>
       </c>
-      <c r="H63" s="33">
+      <c r="H63" s="34">
         <v>0.43</v>
       </c>
-      <c r="I63" s="33">
+      <c r="I63" s="34">
         <v>0.42</v>
       </c>
-      <c r="J63" s="33">
+      <c r="J63" s="34">
         <v>0.35</v>
       </c>
-      <c r="K63" s="33">
+      <c r="K63" s="34">
         <v>0.27</v>
       </c>
-      <c r="L63" s="33">
+      <c r="L63" s="34">
         <v>0.26</v>
       </c>
-      <c r="M63" s="33">
+      <c r="M63" s="34">
         <v>0.26</v>
       </c>
-      <c r="N63" s="33">
+      <c r="N63" s="34">
         <v>0.24</v>
       </c>
-      <c r="O63" s="33">
+      <c r="O63" s="34">
         <v>0.24</v>
       </c>
-      <c r="P63" s="33">
+      <c r="P63" s="34">
         <v>0.32</v>
       </c>
-      <c r="Q63" s="33">
+      <c r="Q63" s="34">
         <v>0.24</v>
       </c>
-      <c r="R63" s="33">
+      <c r="R63" s="34">
         <v>0.3</v>
       </c>
-      <c r="S63" s="33">
+      <c r="S63" s="34">
         <v>0.32</v>
       </c>
-      <c r="T63" s="33">
+      <c r="T63" s="34">
         <v>0.3</v>
       </c>
-      <c r="U63" s="33">
+      <c r="U63" s="34">
         <v>0.3</v>
       </c>
-      <c r="V63" s="33">
+      <c r="V63" s="34">
         <v>0.44</v>
       </c>
-      <c r="W63" s="33">
+      <c r="W63" s="34">
         <v>0.48</v>
       </c>
-      <c r="X63" s="33">
+      <c r="X63" s="34">
         <v>0.55</v>
       </c>
-      <c r="Y63" s="33">
+      <c r="Y63" s="34">
         <v>0.67</v>
       </c>
-      <c r="Z63" s="33">
+      <c r="Z63" s="34">
         <v>0.67</v>
       </c>
-      <c r="AA63" s="35"/>
-      <c r="AB63" s="35"/>
-      <c r="AC63" s="35"/>
-      <c r="AD63" s="35"/>
+      <c r="AA63" s="36"/>
+      <c r="AB63" s="36"/>
+      <c r="AC63" s="36"/>
+      <c r="AD63" s="36"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="30" t="s">
         <v>410</v>
       </c>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
-      <c r="H64" s="30"/>
-      <c r="I64" s="30"/>
-      <c r="J64" s="30"/>
-      <c r="K64" s="30"/>
-      <c r="L64" s="30"/>
-      <c r="M64" s="30"/>
-      <c r="N64" s="30"/>
-      <c r="O64" s="30"/>
-      <c r="P64" s="30"/>
-      <c r="Q64" s="30"/>
-      <c r="R64" s="30"/>
-      <c r="S64" s="30"/>
-      <c r="T64" s="30"/>
-      <c r="U64" s="30"/>
-      <c r="V64" s="30"/>
-      <c r="W64" s="30"/>
-      <c r="X64" s="30"/>
-      <c r="Y64" s="30"/>
-      <c r="Z64" s="30"/>
-      <c r="AA64" s="30"/>
-      <c r="AB64" s="30"/>
-      <c r="AC64" s="30"/>
-      <c r="AD64" s="30"/>
+      <c r="B64" s="31"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="31"/>
+      <c r="I64" s="31"/>
+      <c r="J64" s="31"/>
+      <c r="K64" s="31"/>
+      <c r="L64" s="31"/>
+      <c r="M64" s="31"/>
+      <c r="N64" s="31"/>
+      <c r="O64" s="31"/>
+      <c r="P64" s="31"/>
+      <c r="Q64" s="31"/>
+      <c r="R64" s="31"/>
+      <c r="S64" s="31"/>
+      <c r="T64" s="31"/>
+      <c r="U64" s="31"/>
+      <c r="V64" s="31"/>
+      <c r="W64" s="31"/>
+      <c r="X64" s="31"/>
+      <c r="Y64" s="31"/>
+      <c r="Z64" s="31"/>
+      <c r="AA64" s="31"/>
+      <c r="AB64" s="31"/>
+      <c r="AC64" s="31"/>
+      <c r="AD64" s="31"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="31" t="s">
+      <c r="A65" s="32" t="s">
         <v>411</v>
       </c>
-      <c r="B65" s="33">
+      <c r="B65" s="34">
         <v>10.62</v>
       </c>
-      <c r="C65" s="33">
+      <c r="C65" s="34">
         <v>2.23</v>
       </c>
-      <c r="D65" s="33">
+      <c r="D65" s="34">
         <v>5.21</v>
       </c>
-      <c r="E65" s="33">
+      <c r="E65" s="34">
         <v>4.88</v>
       </c>
-      <c r="F65" s="33">
+      <c r="F65" s="34">
         <v>6.27</v>
       </c>
-      <c r="G65" s="33">
+      <c r="G65" s="34">
         <v>5.24</v>
       </c>
-      <c r="H65" s="33">
+      <c r="H65" s="34">
         <v>6.1</v>
       </c>
-      <c r="I65" s="33">
+      <c r="I65" s="34">
         <v>8.13</v>
       </c>
-      <c r="J65" s="33">
+      <c r="J65" s="34">
         <v>9.8</v>
       </c>
-      <c r="K65" s="33">
+      <c r="K65" s="34">
         <v>5.35</v>
       </c>
-      <c r="L65" s="33">
+      <c r="L65" s="34">
         <v>7.57</v>
       </c>
-      <c r="M65" s="33">
+      <c r="M65" s="34">
         <v>15.49</v>
       </c>
-      <c r="N65" s="33">
+      <c r="N65" s="34">
         <v>4.68</v>
       </c>
-      <c r="O65" s="33">
+      <c r="O65" s="34">
         <v>3.44</v>
       </c>
-      <c r="P65" s="35"/>
-      <c r="Q65" s="35"/>
-      <c r="R65" s="33">
+      <c r="P65" s="36"/>
+      <c r="Q65" s="36"/>
+      <c r="R65" s="34">
         <v>15.19</v>
       </c>
-      <c r="S65" s="33">
+      <c r="S65" s="34">
         <v>4.04</v>
       </c>
-      <c r="T65" s="33">
+      <c r="T65" s="34">
         <v>10.01</v>
       </c>
-      <c r="U65" s="35"/>
-      <c r="V65" s="33">
+      <c r="U65" s="36"/>
+      <c r="V65" s="34">
         <v>3.17</v>
       </c>
-      <c r="W65" s="33">
+      <c r="W65" s="34">
         <v>2.9</v>
       </c>
-      <c r="X65" s="35"/>
-      <c r="Y65" s="35"/>
-      <c r="Z65" s="35"/>
-      <c r="AA65" s="35"/>
-      <c r="AB65" s="33">
+      <c r="X65" s="36"/>
+      <c r="Y65" s="36"/>
+      <c r="Z65" s="36"/>
+      <c r="AA65" s="36"/>
+      <c r="AB65" s="34">
         <v>16.6</v>
       </c>
-      <c r="AC65" s="35"/>
-      <c r="AD65" s="35"/>
+      <c r="AC65" s="36"/>
+      <c r="AD65" s="36"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="31" t="s">
+      <c r="A66" s="32" t="s">
         <v>412</v>
       </c>
-      <c r="B66" s="33">
+      <c r="B66" s="34">
         <v>5.78</v>
       </c>
-      <c r="C66" s="33">
+      <c r="C66" s="34">
         <v>4.66</v>
       </c>
-      <c r="D66" s="33">
+      <c r="D66" s="34">
         <v>5.46</v>
       </c>
-      <c r="E66" s="33">
+      <c r="E66" s="34">
         <v>6.11</v>
       </c>
-      <c r="F66" s="33">
+      <c r="F66" s="34">
         <v>7.12</v>
       </c>
-      <c r="G66" s="33">
+      <c r="G66" s="34">
         <v>6.93</v>
       </c>
-      <c r="H66" s="33">
+      <c r="H66" s="34">
         <v>7.42</v>
       </c>
-      <c r="I66" s="33">
+      <c r="I66" s="34">
         <v>8.16</v>
       </c>
-      <c r="J66" s="33">
+      <c r="J66" s="34">
         <v>7.35</v>
       </c>
-      <c r="K66" s="33">
+      <c r="K66" s="34">
         <v>5.63</v>
       </c>
-      <c r="L66" s="33">
+      <c r="L66" s="34">
         <v>8.41</v>
       </c>
-      <c r="M66" s="35"/>
-      <c r="N66" s="35"/>
-      <c r="O66" s="33">
+      <c r="M66" s="36"/>
+      <c r="N66" s="36"/>
+      <c r="O66" s="34">
         <v>71.73</v>
       </c>
-      <c r="P66" s="33">
+      <c r="P66" s="34">
         <v>42.19</v>
       </c>
-      <c r="Q66" s="33">
+      <c r="Q66" s="34">
         <v>38.68</v>
       </c>
-      <c r="R66" s="33">
+      <c r="R66" s="34">
         <v>5.29</v>
       </c>
-      <c r="S66" s="33">
+      <c r="S66" s="34">
         <v>3.74</v>
       </c>
-      <c r="T66" s="35"/>
-      <c r="U66" s="35"/>
-      <c r="V66" s="35"/>
-      <c r="W66" s="35"/>
-      <c r="X66" s="35"/>
-      <c r="Y66" s="35"/>
-      <c r="Z66" s="35"/>
-      <c r="AA66" s="35"/>
-      <c r="AB66" s="35"/>
-      <c r="AC66" s="35"/>
-      <c r="AD66" s="35"/>
+      <c r="T66" s="36"/>
+      <c r="U66" s="36"/>
+      <c r="V66" s="36"/>
+      <c r="W66" s="36"/>
+      <c r="X66" s="36"/>
+      <c r="Y66" s="36"/>
+      <c r="Z66" s="36"/>
+      <c r="AA66" s="36"/>
+      <c r="AB66" s="36"/>
+      <c r="AC66" s="36"/>
+      <c r="AD66" s="36"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="29" t="s">
+      <c r="A67" s="30" t="s">
         <v>413</v>
       </c>
-      <c r="B67" s="30"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="30"/>
-      <c r="J67" s="30"/>
-      <c r="K67" s="30"/>
-      <c r="L67" s="30"/>
-      <c r="M67" s="30"/>
-      <c r="N67" s="30"/>
-      <c r="O67" s="30"/>
-      <c r="P67" s="30"/>
-      <c r="Q67" s="30"/>
-      <c r="R67" s="30"/>
-      <c r="S67" s="30"/>
-      <c r="T67" s="30"/>
-      <c r="U67" s="30"/>
-      <c r="V67" s="30"/>
-      <c r="W67" s="30"/>
-      <c r="X67" s="30"/>
-      <c r="Y67" s="30"/>
-      <c r="Z67" s="30"/>
-      <c r="AA67" s="30"/>
-      <c r="AB67" s="30"/>
-      <c r="AC67" s="30"/>
-      <c r="AD67" s="30"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="31"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="31"/>
+      <c r="M67" s="31"/>
+      <c r="N67" s="31"/>
+      <c r="O67" s="31"/>
+      <c r="P67" s="31"/>
+      <c r="Q67" s="31"/>
+      <c r="R67" s="31"/>
+      <c r="S67" s="31"/>
+      <c r="T67" s="31"/>
+      <c r="U67" s="31"/>
+      <c r="V67" s="31"/>
+      <c r="W67" s="31"/>
+      <c r="X67" s="31"/>
+      <c r="Y67" s="31"/>
+      <c r="Z67" s="31"/>
+      <c r="AA67" s="31"/>
+      <c r="AB67" s="31"/>
+      <c r="AC67" s="31"/>
+      <c r="AD67" s="31"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="31" t="s">
+      <c r="A68" s="32" t="s">
         <v>414</v>
       </c>
-      <c r="B68" s="35"/>
-      <c r="C68" s="33">
+      <c r="B68" s="36"/>
+      <c r="C68" s="34">
         <v>5.35</v>
       </c>
-      <c r="D68" s="33">
+      <c r="D68" s="34">
         <v>4.99</v>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="34">
         <v>4.48</v>
       </c>
-      <c r="F68" s="33">
+      <c r="F68" s="34">
         <v>28.76</v>
       </c>
-      <c r="G68" s="33">
+      <c r="G68" s="34">
         <v>5.01</v>
       </c>
-      <c r="H68" s="33">
+      <c r="H68" s="34">
         <v>11.47</v>
       </c>
-      <c r="I68" s="35"/>
-      <c r="J68" s="33">
+      <c r="I68" s="36"/>
+      <c r="J68" s="34">
         <v>11.79</v>
       </c>
-      <c r="K68" s="33">
+      <c r="K68" s="34">
         <v>4.97</v>
       </c>
-      <c r="L68" s="35"/>
-      <c r="M68" s="35"/>
-      <c r="N68" s="33">
+      <c r="L68" s="36"/>
+      <c r="M68" s="36"/>
+      <c r="N68" s="34">
         <v>4.37</v>
       </c>
-      <c r="O68" s="33">
+      <c r="O68" s="34">
         <v>13.77</v>
       </c>
-      <c r="P68" s="33">
+      <c r="P68" s="34">
         <v>2.61</v>
       </c>
-      <c r="Q68" s="35"/>
-      <c r="R68" s="35"/>
-      <c r="S68" s="33">
+      <c r="Q68" s="36"/>
+      <c r="R68" s="36"/>
+      <c r="S68" s="34">
         <v>7.3</v>
       </c>
-      <c r="T68" s="33">
+      <c r="T68" s="34">
         <v>62.43</v>
       </c>
-      <c r="U68" s="34">
+      <c r="U68" s="35">
         <v>-1.02</v>
       </c>
-      <c r="V68" s="33">
+      <c r="V68" s="34">
         <v>1.93</v>
       </c>
-      <c r="W68" s="33">
+      <c r="W68" s="34">
         <v>2.93</v>
       </c>
-      <c r="X68" s="33">
+      <c r="X68" s="34">
         <v>2.87</v>
       </c>
-      <c r="Y68" s="33">
+      <c r="Y68" s="34">
         <v>22.03</v>
       </c>
-      <c r="Z68" s="33">
+      <c r="Z68" s="34">
         <v>14.1</v>
       </c>
-      <c r="AA68" s="33">
+      <c r="AA68" s="34">
         <v>13.19</v>
       </c>
-      <c r="AB68" s="33">
+      <c r="AB68" s="34">
         <v>18.08</v>
       </c>
-      <c r="AC68" s="33">
+      <c r="AC68" s="34">
         <v>9.23</v>
       </c>
-      <c r="AD68" s="33">
+      <c r="AD68" s="34">
         <v>8.32</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="31" t="s">
+      <c r="A69" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="B69" s="33">
+      <c r="B69" s="34">
         <v>17.69</v>
       </c>
-      <c r="C69" s="33">
+      <c r="C69" s="34">
         <v>6.02</v>
       </c>
-      <c r="D69" s="33">
+      <c r="D69" s="34">
         <v>6.6</v>
       </c>
-      <c r="E69" s="33">
+      <c r="E69" s="34">
         <v>11.84</v>
       </c>
-      <c r="F69" s="33">
+      <c r="F69" s="34">
         <v>16.68</v>
       </c>
-      <c r="G69" s="33">
+      <c r="G69" s="34">
         <v>11.49</v>
       </c>
-      <c r="H69" s="33">
+      <c r="H69" s="34">
         <v>44.81</v>
       </c>
-      <c r="I69" s="35"/>
-      <c r="J69" s="33">
+      <c r="I69" s="36"/>
+      <c r="J69" s="34">
         <v>24.12</v>
       </c>
-      <c r="K69" s="33">
+      <c r="K69" s="34">
         <v>35.36</v>
       </c>
-      <c r="L69" s="33">
+      <c r="L69" s="34">
         <v>17.23</v>
       </c>
-      <c r="M69" s="35"/>
-      <c r="N69" s="35"/>
-      <c r="O69" s="35"/>
-      <c r="P69" s="35"/>
-      <c r="Q69" s="33">
+      <c r="M69" s="36"/>
+      <c r="N69" s="36"/>
+      <c r="O69" s="36"/>
+      <c r="P69" s="36"/>
+      <c r="Q69" s="34">
         <v>22.37</v>
       </c>
-      <c r="R69" s="33">
+      <c r="R69" s="34">
         <v>3.67</v>
       </c>
-      <c r="S69" s="33">
+      <c r="S69" s="34">
         <v>2.94</v>
       </c>
-      <c r="T69" s="33">
+      <c r="T69" s="34">
         <v>2.76</v>
       </c>
-      <c r="U69" s="33">
+      <c r="U69" s="34">
         <v>2.67</v>
       </c>
-      <c r="V69" s="33">
+      <c r="V69" s="34">
         <v>5.38</v>
       </c>
-      <c r="W69" s="33">
+      <c r="W69" s="34">
         <v>7.66</v>
       </c>
-      <c r="X69" s="33">
+      <c r="X69" s="34">
         <v>9.95</v>
       </c>
-      <c r="Y69" s="33">
+      <c r="Y69" s="34">
         <v>13.7</v>
       </c>
-      <c r="Z69" s="33">
+      <c r="Z69" s="34">
         <v>13.08</v>
       </c>
-      <c r="AA69" s="35"/>
-      <c r="AB69" s="35"/>
-      <c r="AC69" s="35"/>
-      <c r="AD69" s="35"/>
+      <c r="AA69" s="36"/>
+      <c r="AB69" s="36"/>
+      <c r="AC69" s="36"/>
+      <c r="AD69" s="36"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="29" t="s">
+      <c r="A70" s="30" t="s">
         <v>416</v>
       </c>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="30"/>
-      <c r="K70" s="30"/>
-      <c r="L70" s="30"/>
-      <c r="M70" s="30"/>
-      <c r="N70" s="30"/>
-      <c r="O70" s="30"/>
-      <c r="P70" s="30"/>
-      <c r="Q70" s="30"/>
-      <c r="R70" s="30"/>
-      <c r="S70" s="30"/>
-      <c r="T70" s="30"/>
-      <c r="U70" s="30"/>
-      <c r="V70" s="30"/>
-      <c r="W70" s="30"/>
-      <c r="X70" s="30"/>
-      <c r="Y70" s="30"/>
-      <c r="Z70" s="30"/>
-      <c r="AA70" s="30"/>
-      <c r="AB70" s="30"/>
-      <c r="AC70" s="30"/>
-      <c r="AD70" s="30"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
+      <c r="J70" s="31"/>
+      <c r="K70" s="31"/>
+      <c r="L70" s="31"/>
+      <c r="M70" s="31"/>
+      <c r="N70" s="31"/>
+      <c r="O70" s="31"/>
+      <c r="P70" s="31"/>
+      <c r="Q70" s="31"/>
+      <c r="R70" s="31"/>
+      <c r="S70" s="31"/>
+      <c r="T70" s="31"/>
+      <c r="U70" s="31"/>
+      <c r="V70" s="31"/>
+      <c r="W70" s="31"/>
+      <c r="X70" s="31"/>
+      <c r="Y70" s="31"/>
+      <c r="Z70" s="31"/>
+      <c r="AA70" s="31"/>
+      <c r="AB70" s="31"/>
+      <c r="AC70" s="31"/>
+      <c r="AD70" s="31"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="31" t="s">
+      <c r="A71" s="32" t="s">
         <v>417</v>
       </c>
-      <c r="B71" s="35"/>
-      <c r="C71" s="33">
+      <c r="B71" s="36"/>
+      <c r="C71" s="34">
         <v>65.18</v>
       </c>
-      <c r="D71" s="33">
+      <c r="D71" s="34">
         <v>7.78</v>
       </c>
-      <c r="E71" s="33">
+      <c r="E71" s="34">
         <v>5.94</v>
       </c>
-      <c r="F71" s="35"/>
-      <c r="G71" s="33">
+      <c r="F71" s="36"/>
+      <c r="G71" s="34">
         <v>9.94</v>
       </c>
-      <c r="H71" s="33">
+      <c r="H71" s="34">
         <v>19.02</v>
       </c>
-      <c r="I71" s="35"/>
-      <c r="J71" s="33">
+      <c r="I71" s="36"/>
+      <c r="J71" s="34">
         <v>18.06</v>
       </c>
-      <c r="K71" s="33">
+      <c r="K71" s="34">
         <v>5.24</v>
       </c>
-      <c r="L71" s="35"/>
-      <c r="M71" s="35"/>
-      <c r="N71" s="33">
+      <c r="L71" s="36"/>
+      <c r="M71" s="36"/>
+      <c r="N71" s="34">
         <v>5.44</v>
       </c>
-      <c r="O71" s="33">
+      <c r="O71" s="34">
         <v>20.78</v>
       </c>
-      <c r="P71" s="33">
+      <c r="P71" s="34">
         <v>2.72</v>
       </c>
-      <c r="Q71" s="35"/>
-      <c r="R71" s="35"/>
-      <c r="S71" s="33">
+      <c r="Q71" s="36"/>
+      <c r="R71" s="36"/>
+      <c r="S71" s="34">
         <v>9.92</v>
       </c>
-      <c r="T71" s="32">
+      <c r="T71" s="33">
         <v>138.07</v>
       </c>
-      <c r="U71" s="34">
+      <c r="U71" s="35">
         <v>-1.12</v>
       </c>
-      <c r="V71" s="33">
+      <c r="V71" s="34">
         <v>3.46</v>
       </c>
-      <c r="W71" s="33">
+      <c r="W71" s="34">
         <v>5.24</v>
       </c>
-      <c r="X71" s="33">
+      <c r="X71" s="34">
         <v>3.92</v>
       </c>
-      <c r="Y71" s="33">
+      <c r="Y71" s="34">
         <v>23.42</v>
       </c>
-      <c r="Z71" s="35"/>
-      <c r="AA71" s="35"/>
-      <c r="AB71" s="33">
+      <c r="Z71" s="36"/>
+      <c r="AA71" s="36"/>
+      <c r="AB71" s="34">
         <v>18.19</v>
       </c>
-      <c r="AC71" s="33">
+      <c r="AC71" s="34">
         <v>13.2</v>
       </c>
-      <c r="AD71" s="33">
+      <c r="AD71" s="34">
         <v>14.38</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="31" t="s">
+      <c r="A72" s="32" t="s">
         <v>418</v>
       </c>
-      <c r="B72" s="32">
+      <c r="B72" s="33">
         <v>785.49</v>
       </c>
-      <c r="C72" s="33">
+      <c r="C72" s="34">
         <v>11.9</v>
       </c>
-      <c r="D72" s="33">
+      <c r="D72" s="34">
         <v>11.63</v>
       </c>
-      <c r="E72" s="33">
+      <c r="E72" s="34">
         <v>34.85</v>
       </c>
-      <c r="F72" s="33">
+      <c r="F72" s="34">
         <v>91.5</v>
       </c>
-      <c r="G72" s="33">
+      <c r="G72" s="34">
         <v>21.48</v>
       </c>
-      <c r="H72" s="35"/>
-      <c r="I72" s="35"/>
-      <c r="J72" s="33">
+      <c r="H72" s="36"/>
+      <c r="I72" s="36"/>
+      <c r="J72" s="34">
         <v>80.68</v>
       </c>
-      <c r="K72" s="32">
+      <c r="K72" s="33">
         <v>5779.75</v>
       </c>
-      <c r="L72" s="33">
+      <c r="L72" s="34">
         <v>35.66</v>
       </c>
-      <c r="M72" s="35"/>
-      <c r="N72" s="35"/>
-      <c r="O72" s="35"/>
-      <c r="P72" s="35"/>
-      <c r="Q72" s="35"/>
-      <c r="R72" s="33">
+      <c r="M72" s="36"/>
+      <c r="N72" s="36"/>
+      <c r="O72" s="36"/>
+      <c r="P72" s="36"/>
+      <c r="Q72" s="36"/>
+      <c r="R72" s="34">
         <v>7.58</v>
       </c>
-      <c r="S72" s="33">
+      <c r="S72" s="34">
         <v>4.69</v>
       </c>
-      <c r="T72" s="33">
+      <c r="T72" s="34">
         <v>4.19</v>
       </c>
-      <c r="U72" s="33">
+      <c r="U72" s="34">
         <v>4.0</v>
       </c>
-      <c r="V72" s="33">
+      <c r="V72" s="34">
         <v>17.21</v>
       </c>
-      <c r="W72" s="33">
+      <c r="W72" s="34">
         <v>86.77</v>
       </c>
-      <c r="X72" s="35"/>
-      <c r="Y72" s="35"/>
-      <c r="Z72" s="35"/>
-      <c r="AA72" s="35"/>
-      <c r="AB72" s="35"/>
-      <c r="AC72" s="35"/>
-      <c r="AD72" s="35"/>
+      <c r="X72" s="36"/>
+      <c r="Y72" s="36"/>
+      <c r="Z72" s="36"/>
+      <c r="AA72" s="36"/>
+      <c r="AB72" s="36"/>
+      <c r="AC72" s="36"/>
+      <c r="AD72" s="36"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>

--- a/data/cox_xlsx/SKAKO.CO.xlsx
+++ b/data/cox_xlsx/SKAKO.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="420">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -766,6 +766,9 @@
   </si>
   <si>
     <t>Provisions</t>
+  </si>
+  <si>
+    <t>Loans and borrowings LT</t>
   </si>
   <si>
     <t>Other non-current liabilities</t>
@@ -12582,8 +12585,8 @@
       </c>
     </row>
     <row r="95" ht="15.0" customHeight="1">
-      <c r="A95" s="14" t="s">
-        <v>232</v>
+      <c r="A95" s="26" t="s">
+        <v>249</v>
       </c>
       <c r="B95" s="18">
         <v>3.27</v>
@@ -12711,7 +12714,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B97" s="18">
         <v>3.64</v>
@@ -12749,7 +12752,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B98" s="19"/>
       <c r="C98" s="19">
@@ -12777,7 +12780,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B99" s="21">
         <v>24.69</v>
@@ -12845,7 +12848,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B100" s="19"/>
       <c r="C100" s="19"/>
@@ -12875,7 +12878,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B101" s="17">
         <v>227.69</v>
@@ -12943,7 +12946,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B102" s="18">
         <v>49.75</v>
@@ -13011,7 +13014,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B103" s="23">
         <v>-0.24</v>
@@ -13079,7 +13082,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B104" s="19">
         <v>0.0</v>
@@ -13143,7 +13146,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B105" s="18">
         <v>75.79</v>
@@ -13211,7 +13214,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B106" s="19"/>
       <c r="C106" s="19"/>
@@ -13249,7 +13252,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B107" s="18">
         <v>12.44</v>
@@ -13299,7 +13302,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B108" s="19"/>
       <c r="C108" s="19"/>
@@ -13329,7 +13332,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B109" s="17">
         <v>137.74</v>
@@ -13427,7 +13430,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B111" s="17">
         <v>137.74</v>
@@ -13495,7 +13498,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B112" s="19"/>
       <c r="C112" s="19"/>
@@ -13525,7 +13528,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B113" s="17">
         <v>365.43</v>
@@ -13593,7 +13596,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B114" s="18">
         <v>3.13</v>
@@ -13661,7 +13664,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B115" s="18">
         <v>0.02</v>
@@ -13729,7 +13732,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B116" s="18">
         <v>3.15</v>
@@ -13797,7 +13800,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B117" s="19"/>
       <c r="C117" s="19"/>
@@ -13839,7 +13842,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B118" s="19"/>
       <c r="C118" s="19"/>
@@ -13877,7 +13880,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B119" s="19"/>
       <c r="C119" s="19"/>
@@ -13919,7 +13922,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B120" s="19"/>
       <c r="C120" s="19"/>
@@ -13961,7 +13964,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B121" s="19"/>
       <c r="C121" s="19"/>
@@ -13999,7 +14002,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B122" s="19"/>
       <c r="C122" s="19"/>
@@ -14037,7 +14040,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B123" s="19"/>
       <c r="C123" s="19"/>
@@ -14075,7 +14078,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B124" s="19"/>
       <c r="C124" s="19"/>
@@ -14107,7 +14110,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B125" s="18">
         <v>1.0</v>
@@ -14175,7 +14178,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B126" s="18">
         <v>3.13</v>
@@ -14243,7 +14246,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B127" s="18">
         <v>3.15</v>
@@ -14311,7 +14314,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B128" s="18">
         <v>0.02</v>
@@ -15270,7 +15273,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15643,67 +15646,67 @@
         <v>43</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -15776,7 +15779,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -15870,7 +15873,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
@@ -15910,7 +15913,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -15938,7 +15941,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
@@ -15980,7 +15983,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B23" s="18">
         <v>28.35</v>
@@ -16048,7 +16051,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B24" s="23">
         <v>-14.21</v>
@@ -16100,7 +16103,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
@@ -16190,7 +16193,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
@@ -16224,7 +16227,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
@@ -16254,7 +16257,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
@@ -16288,7 +16291,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
@@ -16318,7 +16321,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B31" s="23">
         <v>-13.48</v>
@@ -16378,7 +16381,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B32" s="23">
         <v>-6.37</v>
@@ -16438,7 +16441,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" s="23">
         <v>-27.86</v>
@@ -16484,7 +16487,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="19"/>
@@ -16530,7 +16533,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B35" s="23">
         <v>-11.97</v>
@@ -16598,7 +16601,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B36" s="19"/>
       <c r="C36" s="19"/>
@@ -16646,7 +16649,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B37" s="19"/>
       <c r="C37" s="19"/>
@@ -16694,7 +16697,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B38" s="19"/>
       <c r="C38" s="19"/>
@@ -16728,7 +16731,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B39" s="19"/>
       <c r="C39" s="19"/>
@@ -16758,7 +16761,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B40" s="19"/>
       <c r="C40" s="19"/>
@@ -16796,7 +16799,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B41" s="19"/>
       <c r="C41" s="19"/>
@@ -16838,7 +16841,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B42" s="18">
         <v>2.53</v>
@@ -16880,7 +16883,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B43" s="19"/>
       <c r="C43" s="19"/>
@@ -16910,7 +16913,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B44" s="23">
         <v>-7.19</v>
@@ -16952,7 +16955,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B45" s="19"/>
       <c r="C45" s="19"/>
@@ -16982,7 +16985,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
@@ -17010,7 +17013,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B47" s="19"/>
       <c r="C47" s="19"/>
@@ -17040,7 +17043,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B48" s="19"/>
       <c r="C48" s="19"/>
@@ -17074,7 +17077,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B49" s="25">
         <v>-50.2</v>
@@ -17142,7 +17145,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B50" s="19"/>
       <c r="C50" s="19"/>
@@ -17196,7 +17199,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B51" s="19"/>
       <c r="C51" s="19"/>
@@ -17276,7 +17279,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B53" s="23">
         <v>-0.33</v>
@@ -17344,7 +17347,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B54" s="23">
         <v>-7.99</v>
@@ -17412,7 +17415,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
@@ -17452,7 +17455,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B56" s="19"/>
       <c r="C56" s="19"/>
@@ -17494,7 +17497,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
@@ -17526,7 +17529,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B58" s="18">
         <v>2.95</v>
@@ -17562,7 +17565,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B59" s="23">
         <v>-4.04</v>
@@ -17592,7 +17595,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
@@ -17628,7 +17631,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
@@ -17658,7 +17661,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B62" s="19"/>
       <c r="C62" s="19"/>
@@ -17698,7 +17701,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B63" s="25">
         <v>-9.4</v>
@@ -17766,7 +17769,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B64" s="18">
         <v>13.45</v>
@@ -17834,7 +17837,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
@@ -17864,7 +17867,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B66" s="23">
         <v>-10.67</v>
@@ -17902,7 +17905,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B67" s="18">
         <v>65.14</v>
@@ -17944,7 +17947,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B68" s="19"/>
       <c r="C68" s="19"/>
@@ -17972,7 +17975,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B69" s="19"/>
       <c r="C69" s="19"/>
@@ -18014,7 +18017,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B70" s="19"/>
       <c r="C70" s="19"/>
@@ -18046,7 +18049,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B71" s="27">
         <v>-212.73</v>
@@ -18096,7 +18099,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B72" s="19"/>
       <c r="C72" s="19"/>
@@ -18136,7 +18139,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B73" s="19"/>
       <c r="C73" s="19"/>
@@ -18166,7 +18169,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
@@ -18204,7 +18207,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B75" s="29">
         <v>-144.81</v>
@@ -18272,7 +18275,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B76" s="19"/>
       <c r="C76" s="19"/>
@@ -18304,7 +18307,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
@@ -18336,7 +18339,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B78" s="19"/>
       <c r="C78" s="19"/>
@@ -18368,7 +18371,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B79" s="19"/>
       <c r="C79" s="19">
@@ -18434,7 +18437,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B80" s="15">
         <v>246.22</v>
@@ -18502,7 +18505,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B81" s="18">
         <v>39.2</v>
@@ -18570,7 +18573,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B82" s="27">
         <v>-204.42</v>
@@ -18622,7 +18625,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="16" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B83" s="29">
         <v>-204.42</v>
@@ -18690,7 +18693,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B84" s="19"/>
       <c r="C84" s="19"/>
@@ -18718,7 +18721,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B85" s="19"/>
       <c r="C85" s="19"/>
@@ -18746,7 +18749,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B86" s="19"/>
       <c r="C86" s="19"/>
@@ -18774,7 +18777,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B87" s="19"/>
       <c r="C87" s="19"/>
@@ -18806,7 +18809,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
@@ -18838,7 +18841,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
@@ -19808,7 +19811,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19980,28 +19983,28 @@
         <v>38</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -20466,7 +20469,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -20566,33 +20569,33 @@
         <v>69</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="30" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
@@ -20626,7 +20629,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="32" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B21" s="33">
         <v>462.82</v>
@@ -20718,7 +20721,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="32" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B22" s="33">
         <v>244.94</v>
@@ -20802,7 +20805,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="30" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="31"/>
@@ -20836,7 +20839,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="32" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B24" s="33">
         <v>403.96</v>
@@ -20928,7 +20931,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="32" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B25" s="33">
         <v>248.73</v>
@@ -21012,7 +21015,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="30" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
@@ -21046,7 +21049,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="32" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B27" s="33">
         <v>128.14</v>
@@ -21138,7 +21141,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="32" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B28" s="34">
         <v>79.69</v>
@@ -21222,7 +21225,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="30" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
@@ -21256,7 +21259,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="32" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B30" s="37">
         <v>-14.66</v>
@@ -21348,7 +21351,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="32" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B31" s="38">
         <v>0.14</v>
@@ -21432,7 +21435,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="30" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
@@ -21466,7 +21469,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="32" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B33" s="38">
         <v>6.16</v>
@@ -21558,7 +21561,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="32" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B34" s="38">
         <v>7.53</v>
@@ -21642,7 +21645,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B35" s="38">
         <v>6.16</v>
@@ -21734,7 +21737,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="32" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B36" s="38">
         <v>7.53</v>
@@ -21818,7 +21821,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="30" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
@@ -21852,7 +21855,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="32" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B38" s="34">
         <v>2.91</v>
@@ -21932,7 +21935,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="32" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B39" s="34">
         <v>1.1</v>
@@ -22004,7 +22007,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="30" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B40" s="31"/>
       <c r="C40" s="31"/>
@@ -22038,7 +22041,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="32" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B41" s="34">
         <v>4.13</v>
@@ -22130,7 +22133,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="32" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B42" s="34">
         <v>1.47</v>
@@ -22214,7 +22217,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="30" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -22248,7 +22251,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="32" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B44" s="34">
         <v>1.08</v>
@@ -22340,7 +22343,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="32" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B45" s="34">
         <v>0.56</v>
@@ -22424,7 +22427,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="30" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B46" s="31"/>
       <c r="C46" s="31"/>
@@ -22458,7 +22461,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="32" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B47" s="36"/>
       <c r="C47" s="33">
@@ -22532,7 +22535,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="32" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B48" s="33">
         <v>703.11</v>
@@ -22596,7 +22599,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="30" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B49" s="31"/>
       <c r="C49" s="31"/>
@@ -22630,7 +22633,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="32" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B50" s="34">
         <v>12.78</v>
@@ -22696,7 +22699,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="32" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B51" s="34">
         <v>8.18</v>
@@ -22756,7 +22759,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="30" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B52" s="31"/>
       <c r="C52" s="31"/>
@@ -22790,7 +22793,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="32" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B53" s="34">
         <v>18.83</v>
@@ -22864,7 +22867,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="32" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B54" s="34">
         <v>12.46</v>
@@ -22934,7 +22937,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="30" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B55" s="31"/>
       <c r="C55" s="31"/>
@@ -22968,7 +22971,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="32" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B56" s="34">
         <v>18.83</v>
@@ -23034,7 +23037,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="32" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B57" s="34">
         <v>1.1</v>
@@ -23118,7 +23121,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="30" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B58" s="31"/>
       <c r="C58" s="31"/>
@@ -23152,7 +23155,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="32" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B59" s="34">
         <v>38.02</v>
@@ -23224,7 +23227,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="32" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B60" s="35">
         <v>-9.09</v>
@@ -23274,7 +23277,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="30" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B61" s="31"/>
       <c r="C61" s="31"/>
@@ -23308,7 +23311,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="32" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B62" s="34">
         <v>1.24</v>
@@ -23400,7 +23403,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="32" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B63" s="34">
         <v>0.55</v>
@@ -23484,7 +23487,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="30" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B64" s="31"/>
       <c r="C64" s="31"/>
@@ -23518,7 +23521,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="32" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B65" s="34">
         <v>10.62</v>
@@ -23592,7 +23595,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="32" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B66" s="34">
         <v>5.78</v>
@@ -23658,7 +23661,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="30" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B67" s="31"/>
       <c r="C67" s="31"/>
@@ -23692,7 +23695,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="32" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B68" s="36"/>
       <c r="C68" s="34">
@@ -23772,7 +23775,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="32" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B69" s="34">
         <v>17.69</v>
@@ -23846,7 +23849,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="30" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B70" s="31"/>
       <c r="C70" s="31"/>
@@ -23880,7 +23883,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="32" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B71" s="36"/>
       <c r="C71" s="34">
@@ -23954,7 +23957,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="32" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B72" s="33">
         <v>785.49</v>
